--- a/regressoes/cdx_us_hy/excel/out/regression_with_signal_2025-08-04_11-52-31.xlsx
+++ b/regressoes/cdx_us_hy/excel/out/regression_with_signal_2025-08-04_11-52-31.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\assistente_pesquisa\pietcon.github.io\regressoes\cdx_us_hy\excel\out\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3D1A4B9-1B7E-4140-B7F3-750557077348}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1444" uniqueCount="484">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1651" uniqueCount="486">
   <si>
     <t>Signal</t>
   </si>
@@ -1466,13 +1472,19 @@
   </si>
   <si>
     <t>yes stat. resid</t>
+  </si>
+  <si>
+    <t>+</t>
+  </si>
+  <si>
+    <t>-</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1535,13 +1547,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1579,7 +1599,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -1613,6 +1633,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1647,9 +1668,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1822,11 +1844,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O208"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1873,7 +1895,10 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>484</v>
+      </c>
       <c r="B2" t="s">
         <v>15</v>
       </c>
@@ -1890,34 +1915,37 @@
         <v>479</v>
       </c>
       <c r="G2">
-        <v>0.011</v>
+        <v>1.0999999999999999E-2</v>
       </c>
       <c r="H2">
-        <v>0.0165</v>
+        <v>1.6500000000000001E-2</v>
       </c>
       <c r="I2">
-        <v>0.494</v>
+        <v>0.49399999999999999</v>
       </c>
       <c r="J2" t="s">
         <v>480</v>
       </c>
       <c r="K2">
-        <v>0.2373</v>
+        <v>0.23730000000000001</v>
       </c>
       <c r="L2" t="s">
         <v>482</v>
       </c>
       <c r="M2">
-        <v>0.0283</v>
+        <v>2.8299999999999999E-2</v>
       </c>
       <c r="N2">
-        <v>0.1934</v>
+        <v>0.19339999999999999</v>
       </c>
       <c r="O2">
-        <v>0.0063</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+        <v>6.3E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>485</v>
+      </c>
       <c r="B3" t="s">
         <v>16</v>
       </c>
@@ -1934,13 +1962,13 @@
         <v>479</v>
       </c>
       <c r="G3">
-        <v>0.012</v>
+        <v>1.2E-2</v>
       </c>
       <c r="H3">
-        <v>0.0163</v>
+        <v>1.6299999999999999E-2</v>
       </c>
       <c r="I3">
-        <v>0.5570000000000001</v>
+        <v>0.55700000000000005</v>
       </c>
       <c r="J3" t="s">
         <v>480</v>
@@ -1952,16 +1980,19 @@
         <v>482</v>
       </c>
       <c r="M3">
-        <v>0.0391</v>
+        <v>3.9100000000000003E-2</v>
       </c>
       <c r="N3">
-        <v>0.2309</v>
+        <v>0.23089999999999999</v>
       </c>
       <c r="O3">
-        <v>0.0013</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+        <v>1.2999999999999999E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>484</v>
+      </c>
       <c r="B4" t="s">
         <v>17</v>
       </c>
@@ -1978,34 +2009,37 @@
         <v>479</v>
       </c>
       <c r="G4">
-        <v>0.0113</v>
+        <v>1.1299999999999999E-2</v>
       </c>
       <c r="H4">
-        <v>0.0165</v>
+        <v>1.6500000000000001E-2</v>
       </c>
       <c r="I4">
-        <v>0.385</v>
+        <v>0.38500000000000001</v>
       </c>
       <c r="J4" t="s">
         <v>480</v>
       </c>
       <c r="K4">
-        <v>0.2327</v>
+        <v>0.23269999999999999</v>
       </c>
       <c r="L4" t="s">
         <v>482</v>
       </c>
       <c r="M4">
-        <v>0.0389</v>
+        <v>3.8899999999999997E-2</v>
       </c>
       <c r="N4">
-        <v>0.227</v>
+        <v>0.22700000000000001</v>
       </c>
       <c r="O4">
-        <v>0.0013</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
+        <v>1.2999999999999999E-3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>485</v>
+      </c>
       <c r="B5" t="s">
         <v>18</v>
       </c>
@@ -2022,19 +2056,19 @@
         <v>479</v>
       </c>
       <c r="G5">
-        <v>0.0179</v>
+        <v>1.7899999999999999E-2</v>
       </c>
       <c r="H5">
-        <v>0.0154</v>
+        <v>1.54E-2</v>
       </c>
       <c r="I5">
-        <v>0.423</v>
+        <v>0.42299999999999999</v>
       </c>
       <c r="J5" t="s">
         <v>480</v>
       </c>
       <c r="K5">
-        <v>0.2169</v>
+        <v>0.21690000000000001</v>
       </c>
       <c r="L5" t="s">
         <v>482</v>
@@ -2043,13 +2077,16 @@
         <v>0.1</v>
       </c>
       <c r="N5">
-        <v>0.3894</v>
+        <v>0.38940000000000002</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>484</v>
+      </c>
       <c r="B6" t="s">
         <v>19</v>
       </c>
@@ -2066,34 +2103,37 @@
         <v>479</v>
       </c>
       <c r="G6">
-        <v>0.0168</v>
+        <v>1.6799999999999999E-2</v>
       </c>
       <c r="H6">
-        <v>0.0163</v>
+        <v>1.6299999999999999E-2</v>
       </c>
       <c r="I6">
-        <v>0.319</v>
+        <v>0.31900000000000001</v>
       </c>
       <c r="J6" t="s">
         <v>480</v>
       </c>
       <c r="K6">
-        <v>0.1942</v>
+        <v>0.19420000000000001</v>
       </c>
       <c r="L6" t="s">
         <v>482</v>
       </c>
       <c r="M6">
-        <v>0.08309999999999999</v>
+        <v>8.3099999999999993E-2</v>
       </c>
       <c r="N6">
-        <v>0.3365</v>
+        <v>0.33650000000000002</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:15">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>485</v>
+      </c>
       <c r="B7" t="s">
         <v>20</v>
       </c>
@@ -2110,34 +2150,37 @@
         <v>479</v>
       </c>
       <c r="G7">
-        <v>0.0239</v>
+        <v>2.3900000000000001E-2</v>
       </c>
       <c r="H7">
-        <v>0.0292</v>
+        <v>2.92E-2</v>
       </c>
       <c r="I7">
-        <v>0.199</v>
+        <v>0.19900000000000001</v>
       </c>
       <c r="J7" t="s">
         <v>480</v>
       </c>
       <c r="K7">
-        <v>0.2246</v>
+        <v>0.22459999999999999</v>
       </c>
       <c r="L7" t="s">
         <v>482</v>
       </c>
       <c r="M7">
-        <v>0.0858</v>
+        <v>8.5800000000000001E-2</v>
       </c>
       <c r="N7">
-        <v>0.1906</v>
+        <v>0.19059999999999999</v>
       </c>
       <c r="O7">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>484</v>
+      </c>
       <c r="B8" t="s">
         <v>21</v>
       </c>
@@ -2154,34 +2197,37 @@
         <v>479</v>
       </c>
       <c r="G8">
-        <v>0.0136</v>
+        <v>1.3599999999999999E-2</v>
       </c>
       <c r="H8">
-        <v>0.0158</v>
+        <v>1.5800000000000002E-2</v>
       </c>
       <c r="I8">
-        <v>0.535</v>
+        <v>0.53500000000000003</v>
       </c>
       <c r="J8" t="s">
         <v>480</v>
       </c>
       <c r="K8">
-        <v>0.2197</v>
+        <v>0.21970000000000001</v>
       </c>
       <c r="L8" t="s">
         <v>482</v>
       </c>
       <c r="M8">
-        <v>0.0566</v>
+        <v>5.6599999999999998E-2</v>
       </c>
       <c r="N8">
-        <v>0.2866</v>
+        <v>0.28660000000000002</v>
       </c>
       <c r="O8">
-        <v>0.0001</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15">
+        <v>1E-4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>485</v>
+      </c>
       <c r="B9" t="s">
         <v>22</v>
       </c>
@@ -2198,10 +2244,10 @@
         <v>479</v>
       </c>
       <c r="G9">
-        <v>0.0026</v>
+        <v>2.5999999999999999E-3</v>
       </c>
       <c r="H9">
-        <v>0.0036</v>
+        <v>3.5999999999999999E-3</v>
       </c>
       <c r="I9">
         <v>0.122</v>
@@ -2216,7 +2262,7 @@
         <v>482</v>
       </c>
       <c r="M9">
-        <v>0.0751</v>
+        <v>7.51E-2</v>
       </c>
       <c r="N9">
         <v>1.4454</v>
@@ -2225,7 +2271,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:15">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>484</v>
+      </c>
       <c r="B10" t="s">
         <v>23</v>
       </c>
@@ -2242,10 +2291,10 @@
         <v>479</v>
       </c>
       <c r="G10">
-        <v>0.0046</v>
+        <v>4.5999999999999999E-3</v>
       </c>
       <c r="H10">
-        <v>0.0061</v>
+        <v>6.1000000000000004E-3</v>
       </c>
       <c r="I10">
         <v>0.219</v>
@@ -2254,22 +2303,25 @@
         <v>480</v>
       </c>
       <c r="K10">
-        <v>0.2451</v>
+        <v>0.24510000000000001</v>
       </c>
       <c r="L10" t="s">
         <v>482</v>
       </c>
       <c r="M10">
-        <v>0.0623</v>
+        <v>6.2300000000000001E-2</v>
       </c>
       <c r="N10">
-        <v>0.783</v>
+        <v>0.78300000000000003</v>
       </c>
       <c r="O10">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:15">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>485</v>
+      </c>
       <c r="B11" t="s">
         <v>24</v>
       </c>
@@ -2286,10 +2338,10 @@
         <v>479</v>
       </c>
       <c r="G11">
-        <v>0.015</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="H11">
-        <v>0.0171</v>
+        <v>1.7100000000000001E-2</v>
       </c>
       <c r="I11">
         <v>0.45</v>
@@ -2298,22 +2350,25 @@
         <v>480</v>
       </c>
       <c r="K11">
-        <v>0.2151</v>
+        <v>0.21510000000000001</v>
       </c>
       <c r="L11" t="s">
         <v>482</v>
       </c>
       <c r="M11">
-        <v>0.0548</v>
+        <v>5.4800000000000001E-2</v>
       </c>
       <c r="N11">
-        <v>0.2603</v>
+        <v>0.26029999999999998</v>
       </c>
       <c r="O11">
-        <v>0.0001</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15">
+        <v>1E-4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>484</v>
+      </c>
       <c r="B12" t="s">
         <v>25</v>
       </c>
@@ -2330,13 +2385,13 @@
         <v>479</v>
       </c>
       <c r="G12">
-        <v>0.0171</v>
+        <v>1.7100000000000001E-2</v>
       </c>
       <c r="H12">
-        <v>0.0164</v>
+        <v>1.6400000000000001E-2</v>
       </c>
       <c r="I12">
-        <v>0.409</v>
+        <v>0.40899999999999997</v>
       </c>
       <c r="J12" t="s">
         <v>480</v>
@@ -2348,16 +2403,19 @@
         <v>482</v>
       </c>
       <c r="M12">
-        <v>0.0813</v>
+        <v>8.1299999999999997E-2</v>
       </c>
       <c r="N12">
-        <v>0.3292</v>
+        <v>0.32919999999999999</v>
       </c>
       <c r="O12">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:15">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>485</v>
+      </c>
       <c r="B13" t="s">
         <v>26</v>
       </c>
@@ -2374,10 +2432,10 @@
         <v>479</v>
       </c>
       <c r="G13">
-        <v>0.016</v>
+        <v>1.6E-2</v>
       </c>
       <c r="H13">
-        <v>0.017</v>
+        <v>1.7000000000000001E-2</v>
       </c>
       <c r="I13">
         <v>0.499</v>
@@ -2386,22 +2444,25 @@
         <v>480</v>
       </c>
       <c r="K13">
-        <v>0.2052</v>
+        <v>0.20519999999999999</v>
       </c>
       <c r="L13" t="s">
         <v>482</v>
       </c>
       <c r="M13">
-        <v>0.0788</v>
+        <v>7.8799999999999995E-2</v>
       </c>
       <c r="N13">
-        <v>0.3131</v>
+        <v>0.31309999999999999</v>
       </c>
       <c r="O13">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:15">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>484</v>
+      </c>
       <c r="B14" t="s">
         <v>27</v>
       </c>
@@ -2418,34 +2479,37 @@
         <v>479</v>
       </c>
       <c r="G14">
-        <v>0.0255</v>
+        <v>2.5499999999999998E-2</v>
       </c>
       <c r="H14">
-        <v>0.0151</v>
+        <v>1.5100000000000001E-2</v>
       </c>
       <c r="I14">
-        <v>0.279</v>
+        <v>0.27900000000000003</v>
       </c>
       <c r="J14" t="s">
         <v>480</v>
       </c>
       <c r="K14">
-        <v>0.2023</v>
+        <v>0.20230000000000001</v>
       </c>
       <c r="L14" t="s">
         <v>482</v>
       </c>
       <c r="M14">
-        <v>0.1461</v>
+        <v>0.14610000000000001</v>
       </c>
       <c r="N14">
-        <v>0.4799</v>
+        <v>0.47989999999999999</v>
       </c>
       <c r="O14">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:15">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>485</v>
+      </c>
       <c r="B15" t="s">
         <v>28</v>
       </c>
@@ -2462,10 +2526,10 @@
         <v>479</v>
       </c>
       <c r="G15">
-        <v>0.0232</v>
+        <v>2.3199999999999998E-2</v>
       </c>
       <c r="H15">
-        <v>0.017</v>
+        <v>1.7000000000000001E-2</v>
       </c>
       <c r="I15">
         <v>0.497</v>
@@ -2474,7 +2538,7 @@
         <v>480</v>
       </c>
       <c r="K15">
-        <v>0.1746</v>
+        <v>0.17460000000000001</v>
       </c>
       <c r="L15" t="s">
         <v>482</v>
@@ -2489,7 +2553,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:15">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>484</v>
+      </c>
       <c r="B16" t="s">
         <v>29</v>
       </c>
@@ -2506,10 +2573,10 @@
         <v>479</v>
       </c>
       <c r="G16">
-        <v>0.0319</v>
+        <v>3.1899999999999998E-2</v>
       </c>
       <c r="H16">
-        <v>0.0295</v>
+        <v>2.9499999999999998E-2</v>
       </c>
       <c r="I16">
         <v>0.249</v>
@@ -2518,13 +2585,13 @@
         <v>480</v>
       </c>
       <c r="K16">
-        <v>0.2285</v>
+        <v>0.22850000000000001</v>
       </c>
       <c r="L16" t="s">
         <v>482</v>
       </c>
       <c r="M16">
-        <v>0.09619999999999999</v>
+        <v>9.6199999999999994E-2</v>
       </c>
       <c r="N16">
         <v>0.2001</v>
@@ -2533,7 +2600,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:15">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>485</v>
+      </c>
       <c r="B17" t="s">
         <v>30</v>
       </c>
@@ -2550,34 +2620,37 @@
         <v>479</v>
       </c>
       <c r="G17">
-        <v>0.019</v>
+        <v>1.9E-2</v>
       </c>
       <c r="H17">
-        <v>0.0159</v>
+        <v>1.5900000000000001E-2</v>
       </c>
       <c r="I17">
-        <v>0.481</v>
+        <v>0.48099999999999998</v>
       </c>
       <c r="J17" t="s">
         <v>480</v>
       </c>
       <c r="K17">
-        <v>0.1937</v>
+        <v>0.19370000000000001</v>
       </c>
       <c r="L17" t="s">
         <v>482</v>
       </c>
       <c r="M17">
-        <v>0.099</v>
+        <v>9.9000000000000005E-2</v>
       </c>
       <c r="N17">
-        <v>0.3751</v>
+        <v>0.37509999999999999</v>
       </c>
       <c r="O17">
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="2:15">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>484</v>
+      </c>
       <c r="B18" t="s">
         <v>31</v>
       </c>
@@ -2594,10 +2667,10 @@
         <v>479</v>
       </c>
       <c r="G18">
-        <v>0.004</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="H18">
-        <v>0.0045</v>
+        <v>4.4999999999999997E-3</v>
       </c>
       <c r="I18">
         <v>0.25</v>
@@ -2606,22 +2679,25 @@
         <v>480</v>
       </c>
       <c r="K18">
-        <v>0.0489</v>
+        <v>4.8899999999999999E-2</v>
       </c>
       <c r="L18" t="s">
         <v>483</v>
       </c>
       <c r="M18">
-        <v>0.0543</v>
+        <v>5.4300000000000001E-2</v>
       </c>
       <c r="N18">
-        <v>0.986</v>
+        <v>0.98599999999999999</v>
       </c>
       <c r="O18">
-        <v>0.0001</v>
-      </c>
-    </row>
-    <row r="19" spans="2:15">
+        <v>1E-4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>485</v>
+      </c>
       <c r="B19" t="s">
         <v>32</v>
       </c>
@@ -2638,34 +2714,37 @@
         <v>479</v>
       </c>
       <c r="G19">
-        <v>0.007</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="H19">
-        <v>0.0076</v>
+        <v>7.6E-3</v>
       </c>
       <c r="I19">
-        <v>0.228</v>
+        <v>0.22800000000000001</v>
       </c>
       <c r="J19" t="s">
         <v>480</v>
       </c>
       <c r="K19">
-        <v>0.0466</v>
+        <v>4.6600000000000003E-2</v>
       </c>
       <c r="L19" t="s">
         <v>483</v>
       </c>
       <c r="M19">
-        <v>0.0412</v>
+        <v>4.1200000000000001E-2</v>
       </c>
       <c r="N19">
-        <v>0.5084</v>
+        <v>0.50839999999999996</v>
       </c>
       <c r="O19">
-        <v>0.0009</v>
-      </c>
-    </row>
-    <row r="20" spans="2:15">
+        <v>8.9999999999999998E-4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>484</v>
+      </c>
       <c r="B20" t="s">
         <v>33</v>
       </c>
@@ -2682,34 +2761,37 @@
         <v>479</v>
       </c>
       <c r="G20">
-        <v>0.0205</v>
+        <v>2.0500000000000001E-2</v>
       </c>
       <c r="H20">
-        <v>0.0169</v>
+        <v>1.6899999999999998E-2</v>
       </c>
       <c r="I20">
-        <v>0.393</v>
+        <v>0.39300000000000002</v>
       </c>
       <c r="J20" t="s">
         <v>480</v>
       </c>
       <c r="K20">
-        <v>0.1906</v>
+        <v>0.19059999999999999</v>
       </c>
       <c r="L20" t="s">
         <v>482</v>
       </c>
       <c r="M20">
-        <v>0.0774</v>
+        <v>7.7399999999999997E-2</v>
       </c>
       <c r="N20">
-        <v>0.3128</v>
+        <v>0.31280000000000002</v>
       </c>
       <c r="O20">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="2:15">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>485</v>
+      </c>
       <c r="B21" t="s">
         <v>34</v>
       </c>
@@ -2726,10 +2808,10 @@
         <v>479</v>
       </c>
       <c r="G21">
-        <v>0.0237</v>
+        <v>2.3699999999999999E-2</v>
       </c>
       <c r="H21">
-        <v>0.0159</v>
+        <v>1.5900000000000001E-2</v>
       </c>
       <c r="I21">
         <v>0.439</v>
@@ -2747,13 +2829,16 @@
         <v>0.1124</v>
       </c>
       <c r="N21">
-        <v>0.4005</v>
+        <v>0.40050000000000002</v>
       </c>
       <c r="O21">
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="2:15">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>484</v>
+      </c>
       <c r="B22" t="s">
         <v>35</v>
       </c>
@@ -2770,19 +2855,19 @@
         <v>479</v>
       </c>
       <c r="G22">
-        <v>0.0223</v>
+        <v>2.23E-2</v>
       </c>
       <c r="H22">
-        <v>0.0167</v>
+        <v>1.67E-2</v>
       </c>
       <c r="I22">
-        <v>0.323</v>
+        <v>0.32300000000000001</v>
       </c>
       <c r="J22" t="s">
         <v>480</v>
       </c>
       <c r="K22">
-        <v>0.1766</v>
+        <v>0.17660000000000001</v>
       </c>
       <c r="L22" t="s">
         <v>482</v>
@@ -2797,7 +2882,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="2:15">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>485</v>
+      </c>
       <c r="B23" t="s">
         <v>36</v>
       </c>
@@ -2814,25 +2902,25 @@
         <v>479</v>
       </c>
       <c r="G23">
-        <v>0.0337</v>
+        <v>3.3700000000000001E-2</v>
       </c>
       <c r="H23">
-        <v>0.014</v>
+        <v>1.4E-2</v>
       </c>
       <c r="I23">
-        <v>0.411</v>
+        <v>0.41099999999999998</v>
       </c>
       <c r="J23" t="s">
         <v>480</v>
       </c>
       <c r="K23">
-        <v>0.1811</v>
+        <v>0.18110000000000001</v>
       </c>
       <c r="L23" t="s">
         <v>482</v>
       </c>
       <c r="M23">
-        <v>0.1662</v>
+        <v>0.16619999999999999</v>
       </c>
       <c r="N23">
         <v>0.5524</v>
@@ -2841,7 +2929,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="2:15">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>484</v>
+      </c>
       <c r="B24" t="s">
         <v>37</v>
       </c>
@@ -2858,34 +2949,37 @@
         <v>479</v>
       </c>
       <c r="G24">
-        <v>0.0308</v>
+        <v>3.0800000000000001E-2</v>
       </c>
       <c r="H24">
-        <v>0.0163</v>
+        <v>1.6299999999999999E-2</v>
       </c>
       <c r="I24">
-        <v>0.5679999999999999</v>
+        <v>0.56799999999999995</v>
       </c>
       <c r="J24" t="s">
         <v>480</v>
       </c>
       <c r="K24">
-        <v>0.1727</v>
+        <v>0.17269999999999999</v>
       </c>
       <c r="L24" t="s">
         <v>482</v>
       </c>
       <c r="M24">
-        <v>0.1408</v>
+        <v>0.14080000000000001</v>
       </c>
       <c r="N24">
-        <v>0.4369</v>
+        <v>0.43690000000000001</v>
       </c>
       <c r="O24">
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="2:15">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>485</v>
+      </c>
       <c r="B25" t="s">
         <v>38</v>
       </c>
@@ -2902,10 +2996,10 @@
         <v>479</v>
       </c>
       <c r="G25">
-        <v>0.0385</v>
+        <v>3.85E-2</v>
       </c>
       <c r="H25">
-        <v>0.0244</v>
+        <v>2.4400000000000002E-2</v>
       </c>
       <c r="I25">
         <v>0.185</v>
@@ -2914,7 +3008,7 @@
         <v>480</v>
       </c>
       <c r="K25">
-        <v>0.2318</v>
+        <v>0.23180000000000001</v>
       </c>
       <c r="L25" t="s">
         <v>482</v>
@@ -2923,13 +3017,16 @@
         <v>0.1057</v>
       </c>
       <c r="N25">
-        <v>0.2532</v>
+        <v>0.25319999999999998</v>
       </c>
       <c r="O25">
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="2:15">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>484</v>
+      </c>
       <c r="B26" t="s">
         <v>39</v>
       </c>
@@ -2946,19 +3043,19 @@
         <v>479</v>
       </c>
       <c r="G26">
-        <v>0.0256</v>
+        <v>2.5600000000000001E-2</v>
       </c>
       <c r="H26">
-        <v>0.0155</v>
+        <v>1.55E-2</v>
       </c>
       <c r="I26">
-        <v>0.347</v>
+        <v>0.34699999999999998</v>
       </c>
       <c r="J26" t="s">
         <v>480</v>
       </c>
       <c r="K26">
-        <v>0.168</v>
+        <v>0.16800000000000001</v>
       </c>
       <c r="L26" t="s">
         <v>482</v>
@@ -2967,13 +3064,16 @@
         <v>0.1242</v>
       </c>
       <c r="N26">
-        <v>0.4322</v>
+        <v>0.43219999999999997</v>
       </c>
       <c r="O26">
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="2:15">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>485</v>
+      </c>
       <c r="B27" t="s">
         <v>40</v>
       </c>
@@ -2990,34 +3090,37 @@
         <v>479</v>
       </c>
       <c r="G27">
-        <v>0.0052</v>
+        <v>5.1999999999999998E-3</v>
       </c>
       <c r="H27">
-        <v>0.0044</v>
+        <v>4.4000000000000003E-3</v>
       </c>
       <c r="I27">
-        <v>0.333</v>
+        <v>0.33300000000000002</v>
       </c>
       <c r="J27" t="s">
         <v>480</v>
       </c>
       <c r="K27">
-        <v>0.0511</v>
+        <v>5.11E-2</v>
       </c>
       <c r="L27" t="s">
         <v>483</v>
       </c>
       <c r="M27">
-        <v>0.0336</v>
+        <v>3.3599999999999998E-2</v>
       </c>
       <c r="N27">
-        <v>0.7957</v>
+        <v>0.79569999999999996</v>
       </c>
       <c r="O27">
-        <v>0.0029</v>
-      </c>
-    </row>
-    <row r="28" spans="2:15">
+        <v>2.8999999999999998E-3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>484</v>
+      </c>
       <c r="B28" t="s">
         <v>41</v>
       </c>
@@ -3034,34 +3137,37 @@
         <v>479</v>
       </c>
       <c r="G28">
-        <v>0.008999999999999999</v>
+        <v>8.9999999999999993E-3</v>
       </c>
       <c r="H28">
-        <v>0.0076</v>
+        <v>7.6E-3</v>
       </c>
       <c r="I28">
-        <v>0.405</v>
+        <v>0.40500000000000003</v>
       </c>
       <c r="J28" t="s">
         <v>480</v>
       </c>
       <c r="K28">
-        <v>0.0472</v>
+        <v>4.7199999999999999E-2</v>
       </c>
       <c r="L28" t="s">
         <v>483</v>
       </c>
       <c r="M28">
-        <v>0.0206</v>
+        <v>2.06E-2</v>
       </c>
       <c r="N28">
-        <v>0.3585</v>
+        <v>0.35849999999999999</v>
       </c>
       <c r="O28">
-        <v>0.0202</v>
-      </c>
-    </row>
-    <row r="29" spans="2:15">
+        <v>2.0199999999999999E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>485</v>
+      </c>
       <c r="B29" t="s">
         <v>42</v>
       </c>
@@ -3078,10 +3184,10 @@
         <v>479</v>
       </c>
       <c r="G29">
-        <v>0.0176</v>
+        <v>1.7600000000000001E-2</v>
       </c>
       <c r="H29">
-        <v>0.0145</v>
+        <v>1.4500000000000001E-2</v>
       </c>
       <c r="I29">
         <v>0.185</v>
@@ -3090,22 +3196,25 @@
         <v>480</v>
       </c>
       <c r="K29">
-        <v>0.0357</v>
+        <v>3.5700000000000003E-2</v>
       </c>
       <c r="L29" t="s">
         <v>483</v>
       </c>
       <c r="M29">
-        <v>0.0377</v>
+        <v>3.7699999999999997E-2</v>
       </c>
       <c r="N29">
-        <v>-0.2541</v>
+        <v>-0.25409999999999999</v>
       </c>
       <c r="O29">
-        <v>0.0016</v>
-      </c>
-    </row>
-    <row r="30" spans="2:15">
+        <v>1.6000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>484</v>
+      </c>
       <c r="B30" t="s">
         <v>43</v>
       </c>
@@ -3122,10 +3231,10 @@
         <v>479</v>
       </c>
       <c r="G30">
-        <v>0.0236</v>
+        <v>2.3599999999999999E-2</v>
       </c>
       <c r="H30">
-        <v>0.0124</v>
+        <v>1.24E-2</v>
       </c>
       <c r="I30">
         <v>0.31</v>
@@ -3134,22 +3243,25 @@
         <v>480</v>
       </c>
       <c r="K30">
-        <v>0.0554</v>
+        <v>5.5399999999999998E-2</v>
       </c>
       <c r="L30" t="s">
         <v>483</v>
       </c>
       <c r="M30">
-        <v>0.0135</v>
+        <v>1.35E-2</v>
       </c>
       <c r="N30">
-        <v>-0.1781</v>
+        <v>-0.17810000000000001</v>
       </c>
       <c r="O30">
-        <v>0.0602</v>
-      </c>
-    </row>
-    <row r="31" spans="2:15">
+        <v>6.0199999999999997E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>485</v>
+      </c>
       <c r="B31" t="s">
         <v>44</v>
       </c>
@@ -3166,34 +3278,37 @@
         <v>479</v>
       </c>
       <c r="G31">
-        <v>0.0297</v>
+        <v>2.9700000000000001E-2</v>
       </c>
       <c r="H31">
-        <v>0.0112</v>
+        <v>1.12E-2</v>
       </c>
       <c r="I31">
-        <v>0.29</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="J31" t="s">
         <v>480</v>
       </c>
       <c r="K31">
-        <v>0.0626</v>
+        <v>6.2600000000000003E-2</v>
       </c>
       <c r="L31" t="s">
         <v>483</v>
       </c>
       <c r="M31">
-        <v>0.0003</v>
+        <v>2.9999999999999997E-4</v>
       </c>
       <c r="N31">
-        <v>0.027</v>
+        <v>2.7E-2</v>
       </c>
       <c r="O31">
         <v>0.7974</v>
       </c>
     </row>
-    <row r="32" spans="2:15">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>484</v>
+      </c>
       <c r="B32" t="s">
         <v>45</v>
       </c>
@@ -3210,34 +3325,37 @@
         <v>479</v>
       </c>
       <c r="G32">
-        <v>0.0033</v>
+        <v>3.3E-3</v>
       </c>
       <c r="H32">
-        <v>0.0044</v>
+        <v>4.4000000000000003E-3</v>
       </c>
       <c r="I32">
-        <v>0.508</v>
+        <v>0.50800000000000001</v>
       </c>
       <c r="J32" t="s">
         <v>480</v>
       </c>
       <c r="K32">
-        <v>0.2256</v>
+        <v>0.22559999999999999</v>
       </c>
       <c r="L32" t="s">
         <v>482</v>
       </c>
       <c r="M32">
-        <v>0.0588</v>
+        <v>5.8799999999999998E-2</v>
       </c>
       <c r="N32">
-        <v>1.0579</v>
+        <v>1.0579000000000001</v>
       </c>
       <c r="O32">
-        <v>0.0001</v>
-      </c>
-    </row>
-    <row r="33" spans="2:15">
+        <v>1E-4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>485</v>
+      </c>
       <c r="B33" t="s">
         <v>46</v>
       </c>
@@ -3254,34 +3372,37 @@
         <v>479</v>
       </c>
       <c r="G33">
-        <v>0.0033</v>
+        <v>3.3E-3</v>
       </c>
       <c r="H33">
-        <v>0.0044</v>
+        <v>4.4000000000000003E-3</v>
       </c>
       <c r="I33">
-        <v>0.508</v>
+        <v>0.50800000000000001</v>
       </c>
       <c r="J33" t="s">
         <v>480</v>
       </c>
       <c r="K33">
-        <v>0.2256</v>
+        <v>0.22559999999999999</v>
       </c>
       <c r="L33" t="s">
         <v>482</v>
       </c>
       <c r="M33">
-        <v>0.0588</v>
+        <v>5.8799999999999998E-2</v>
       </c>
       <c r="N33">
-        <v>1.0579</v>
+        <v>1.0579000000000001</v>
       </c>
       <c r="O33">
-        <v>0.0001</v>
-      </c>
-    </row>
-    <row r="34" spans="2:15">
+        <v>1E-4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>484</v>
+      </c>
       <c r="B34" t="s">
         <v>47</v>
       </c>
@@ -3298,34 +3419,37 @@
         <v>479</v>
       </c>
       <c r="G34">
-        <v>0.0077</v>
+        <v>7.7000000000000002E-3</v>
       </c>
       <c r="H34">
-        <v>0.0062</v>
+        <v>6.1999999999999998E-3</v>
       </c>
       <c r="I34">
-        <v>0.575</v>
+        <v>0.57499999999999996</v>
       </c>
       <c r="J34" t="s">
         <v>480</v>
       </c>
       <c r="K34">
-        <v>0.1846</v>
+        <v>0.18459999999999999</v>
       </c>
       <c r="L34" t="s">
         <v>482</v>
       </c>
       <c r="M34">
-        <v>0.081</v>
+        <v>8.1000000000000003E-2</v>
       </c>
       <c r="N34">
-        <v>0.8662</v>
+        <v>0.86619999999999997</v>
       </c>
       <c r="O34">
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="2:15">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>485</v>
+      </c>
       <c r="B35" t="s">
         <v>48</v>
       </c>
@@ -3342,34 +3466,37 @@
         <v>479</v>
       </c>
       <c r="G35">
-        <v>0.0066</v>
+        <v>6.6E-3</v>
       </c>
       <c r="H35">
-        <v>0.0124</v>
+        <v>1.24E-2</v>
       </c>
       <c r="I35">
-        <v>0.198</v>
+        <v>0.19800000000000001</v>
       </c>
       <c r="J35" t="s">
         <v>480</v>
       </c>
       <c r="K35">
-        <v>0.0012</v>
+        <v>1.1999999999999999E-3</v>
       </c>
       <c r="L35" t="s">
         <v>483</v>
       </c>
       <c r="M35">
-        <v>0.209</v>
+        <v>0.20899999999999999</v>
       </c>
       <c r="N35">
-        <v>-0.7023</v>
+        <v>-0.70230000000000004</v>
       </c>
       <c r="O35">
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="2:15">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>484</v>
+      </c>
       <c r="B36" t="s">
         <v>49</v>
       </c>
@@ -3386,34 +3513,37 @@
         <v>479</v>
       </c>
       <c r="G36">
-        <v>0.0086</v>
+        <v>8.6E-3</v>
       </c>
       <c r="H36">
-        <v>0.0106</v>
+        <v>1.06E-2</v>
       </c>
       <c r="I36">
-        <v>0.457</v>
+        <v>0.45700000000000002</v>
       </c>
       <c r="J36" t="s">
         <v>480</v>
       </c>
       <c r="K36">
-        <v>0.0015</v>
+        <v>1.5E-3</v>
       </c>
       <c r="L36" t="s">
         <v>483</v>
       </c>
       <c r="M36">
-        <v>0.2704</v>
+        <v>0.27039999999999997</v>
       </c>
       <c r="N36">
-        <v>-0.9356</v>
+        <v>-0.93559999999999999</v>
       </c>
       <c r="O36">
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="2:15">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>485</v>
+      </c>
       <c r="B37" t="s">
         <v>50</v>
       </c>
@@ -3430,25 +3560,25 @@
         <v>479</v>
       </c>
       <c r="G37">
-        <v>0.0092</v>
+        <v>9.1999999999999998E-3</v>
       </c>
       <c r="H37">
-        <v>0.0086</v>
+        <v>8.6E-3</v>
       </c>
       <c r="I37">
-        <v>0.545</v>
+        <v>0.54500000000000004</v>
       </c>
       <c r="J37" t="s">
         <v>480</v>
       </c>
       <c r="K37">
-        <v>0.0044</v>
+        <v>4.4000000000000003E-3</v>
       </c>
       <c r="L37" t="s">
         <v>483</v>
       </c>
       <c r="M37">
-        <v>0.2851</v>
+        <v>0.28510000000000002</v>
       </c>
       <c r="N37">
         <v>-1.1854</v>
@@ -3457,7 +3587,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="2:15">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>484</v>
+      </c>
       <c r="B38" t="s">
         <v>51</v>
       </c>
@@ -3474,34 +3607,37 @@
         <v>479</v>
       </c>
       <c r="G38">
-        <v>0.0037</v>
+        <v>3.7000000000000002E-3</v>
       </c>
       <c r="H38">
-        <v>0.0038</v>
+        <v>3.8E-3</v>
       </c>
       <c r="I38">
-        <v>0.048</v>
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="J38" t="s">
         <v>481</v>
       </c>
       <c r="K38">
-        <v>0.0049</v>
+        <v>4.8999999999999998E-3</v>
       </c>
       <c r="L38" t="s">
         <v>483</v>
       </c>
       <c r="M38">
-        <v>0.4281</v>
+        <v>0.42809999999999998</v>
       </c>
       <c r="N38">
-        <v>3.2954</v>
+        <v>3.2953999999999999</v>
       </c>
       <c r="O38">
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="2:15">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>485</v>
+      </c>
       <c r="B39" t="s">
         <v>52</v>
       </c>
@@ -3518,34 +3654,37 @@
         <v>479</v>
       </c>
       <c r="G39">
-        <v>0.0037</v>
+        <v>3.7000000000000002E-3</v>
       </c>
       <c r="H39">
-        <v>0.0037</v>
+        <v>3.7000000000000002E-3</v>
       </c>
       <c r="I39">
-        <v>0.098</v>
+        <v>9.8000000000000004E-2</v>
       </c>
       <c r="J39" t="s">
         <v>481</v>
       </c>
       <c r="K39">
-        <v>0.1272</v>
+        <v>0.12720000000000001</v>
       </c>
       <c r="L39" t="s">
         <v>483</v>
       </c>
       <c r="M39">
-        <v>0.2672</v>
+        <v>0.26719999999999999</v>
       </c>
       <c r="N39">
-        <v>2.6403</v>
+        <v>2.6402999999999999</v>
       </c>
       <c r="O39">
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="2:15">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>484</v>
+      </c>
       <c r="B40" t="s">
         <v>53</v>
       </c>
@@ -3562,10 +3701,10 @@
         <v>479</v>
       </c>
       <c r="G40">
-        <v>0.0122</v>
+        <v>1.2200000000000001E-2</v>
       </c>
       <c r="H40">
-        <v>0.009299999999999999</v>
+        <v>9.2999999999999992E-3</v>
       </c>
       <c r="I40">
         <v>0.158</v>
@@ -3574,7 +3713,7 @@
         <v>480</v>
       </c>
       <c r="K40">
-        <v>0.0146</v>
+        <v>1.46E-2</v>
       </c>
       <c r="L40" t="s">
         <v>483</v>
@@ -3583,13 +3722,16 @@
         <v>0.1052</v>
       </c>
       <c r="N40">
-        <v>0.6604</v>
+        <v>0.66039999999999999</v>
       </c>
       <c r="O40">
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="2:15">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>485</v>
+      </c>
       <c r="B41" t="s">
         <v>54</v>
       </c>
@@ -3606,10 +3748,10 @@
         <v>479</v>
       </c>
       <c r="G41">
-        <v>0.009599999999999999</v>
+        <v>9.5999999999999992E-3</v>
       </c>
       <c r="H41">
-        <v>0.0062</v>
+        <v>6.1999999999999998E-3</v>
       </c>
       <c r="I41">
         <v>0.314</v>
@@ -3618,22 +3760,25 @@
         <v>480</v>
       </c>
       <c r="K41">
-        <v>0.0479</v>
+        <v>4.7899999999999998E-2</v>
       </c>
       <c r="L41" t="s">
         <v>483</v>
       </c>
       <c r="M41">
-        <v>0.1001</v>
+        <v>0.10009999999999999</v>
       </c>
       <c r="N41">
-        <v>0.9665</v>
+        <v>0.96650000000000003</v>
       </c>
       <c r="O41">
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="2:15">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>484</v>
+      </c>
       <c r="B42" t="s">
         <v>55</v>
       </c>
@@ -3647,13 +3792,13 @@
         <v>479</v>
       </c>
       <c r="G42">
-        <v>-0.0076</v>
+        <v>-7.6E-3</v>
       </c>
       <c r="H42">
-        <v>0.0142</v>
+        <v>1.4200000000000001E-2</v>
       </c>
       <c r="I42">
-        <v>0.117</v>
+        <v>0.11700000000000001</v>
       </c>
       <c r="J42" t="s">
         <v>481</v>
@@ -3665,16 +3810,19 @@
         <v>482</v>
       </c>
       <c r="M42">
-        <v>0.0215</v>
+        <v>2.1499999999999998E-2</v>
       </c>
       <c r="N42">
-        <v>-0.1965</v>
+        <v>-0.19650000000000001</v>
       </c>
       <c r="O42">
-        <v>0.0174</v>
-      </c>
-    </row>
-    <row r="43" spans="2:15">
+        <v>1.7399999999999999E-2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>485</v>
+      </c>
       <c r="B43" t="s">
         <v>56</v>
       </c>
@@ -3691,34 +3839,37 @@
         <v>479</v>
       </c>
       <c r="G43">
-        <v>0.0228</v>
+        <v>2.2800000000000001E-2</v>
       </c>
       <c r="H43">
-        <v>0.0033</v>
+        <v>3.3E-3</v>
       </c>
       <c r="I43">
-        <v>0.046</v>
+        <v>4.5999999999999999E-2</v>
       </c>
       <c r="J43" t="s">
         <v>481</v>
       </c>
       <c r="K43">
-        <v>0.2658</v>
+        <v>0.26579999999999998</v>
       </c>
       <c r="L43" t="s">
         <v>482</v>
       </c>
       <c r="M43">
-        <v>0.0029</v>
+        <v>2.8999999999999998E-3</v>
       </c>
       <c r="N43">
-        <v>0.3083</v>
+        <v>0.30830000000000002</v>
       </c>
       <c r="O43">
-        <v>0.3844</v>
-      </c>
-    </row>
-    <row r="44" spans="2:15">
+        <v>0.38440000000000002</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>484</v>
+      </c>
       <c r="B44" t="s">
         <v>57</v>
       </c>
@@ -3735,10 +3886,10 @@
         <v>479</v>
       </c>
       <c r="G44">
-        <v>0.0141</v>
+        <v>1.41E-2</v>
       </c>
       <c r="H44">
-        <v>0.016</v>
+        <v>1.6E-2</v>
       </c>
       <c r="I44">
         <v>0.155</v>
@@ -3747,22 +3898,25 @@
         <v>480</v>
       </c>
       <c r="K44">
-        <v>0.2692</v>
+        <v>0.26919999999999999</v>
       </c>
       <c r="L44" t="s">
         <v>482</v>
       </c>
       <c r="M44">
-        <v>0.0485</v>
+        <v>4.8500000000000001E-2</v>
       </c>
       <c r="N44">
-        <v>-0.2622</v>
+        <v>-0.26219999999999999</v>
       </c>
       <c r="O44">
-        <v>0.0003</v>
-      </c>
-    </row>
-    <row r="45" spans="2:15">
+        <v>2.9999999999999997E-4</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>485</v>
+      </c>
       <c r="B45" t="s">
         <v>58</v>
       </c>
@@ -3779,34 +3933,37 @@
         <v>479</v>
       </c>
       <c r="G45">
-        <v>0.0134</v>
+        <v>1.34E-2</v>
       </c>
       <c r="H45">
-        <v>0.0157</v>
+        <v>1.5699999999999999E-2</v>
       </c>
       <c r="I45">
-        <v>0.059</v>
+        <v>5.8999999999999997E-2</v>
       </c>
       <c r="J45" t="s">
         <v>481</v>
       </c>
       <c r="K45">
-        <v>0.0331</v>
+        <v>3.3099999999999997E-2</v>
       </c>
       <c r="L45" t="s">
         <v>483</v>
       </c>
       <c r="M45">
-        <v>0.0561</v>
+        <v>5.6099999999999997E-2</v>
       </c>
       <c r="N45">
-        <v>-0.2874</v>
+        <v>-0.28739999999999999</v>
       </c>
       <c r="O45">
-        <v>0.0001</v>
-      </c>
-    </row>
-    <row r="46" spans="2:15">
+        <v>1E-4</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>484</v>
+      </c>
       <c r="B46" t="s">
         <v>59</v>
       </c>
@@ -3823,34 +3980,37 @@
         <v>479</v>
       </c>
       <c r="G46">
-        <v>0.0157</v>
+        <v>1.5699999999999999E-2</v>
       </c>
       <c r="H46">
-        <v>0.0162</v>
+        <v>1.6199999999999999E-2</v>
       </c>
       <c r="I46">
-        <v>0.064</v>
+        <v>6.4000000000000001E-2</v>
       </c>
       <c r="J46" t="s">
         <v>481</v>
       </c>
       <c r="K46">
-        <v>0.0297</v>
+        <v>2.9700000000000001E-2</v>
       </c>
       <c r="L46" t="s">
         <v>483</v>
       </c>
       <c r="M46">
-        <v>0.0398</v>
+        <v>3.9800000000000002E-2</v>
       </c>
       <c r="N46">
-        <v>-0.2333</v>
+        <v>-0.23330000000000001</v>
       </c>
       <c r="O46">
-        <v>0.0012</v>
-      </c>
-    </row>
-    <row r="47" spans="2:15">
+        <v>1.1999999999999999E-3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>485</v>
+      </c>
       <c r="B47" t="s">
         <v>60</v>
       </c>
@@ -3867,34 +4027,37 @@
         <v>479</v>
       </c>
       <c r="G47">
-        <v>0.0146</v>
+        <v>1.46E-2</v>
       </c>
       <c r="H47">
-        <v>0.016</v>
+        <v>1.6E-2</v>
       </c>
       <c r="I47">
-        <v>0.036</v>
+        <v>3.5999999999999997E-2</v>
       </c>
       <c r="J47" t="s">
         <v>481</v>
       </c>
       <c r="K47">
-        <v>0.0311</v>
+        <v>3.1099999999999999E-2</v>
       </c>
       <c r="L47" t="s">
         <v>483</v>
       </c>
       <c r="M47">
-        <v>0.0477</v>
+        <v>4.7699999999999999E-2</v>
       </c>
       <c r="N47">
-        <v>-0.2592</v>
+        <v>-0.25919999999999999</v>
       </c>
       <c r="O47">
-        <v>0.0004</v>
-      </c>
-    </row>
-    <row r="48" spans="2:15">
+        <v>4.0000000000000002E-4</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>484</v>
+      </c>
       <c r="B48" t="s">
         <v>61</v>
       </c>
@@ -3911,10 +4074,10 @@
         <v>479</v>
       </c>
       <c r="G48">
-        <v>0.0167</v>
+        <v>1.67E-2</v>
       </c>
       <c r="H48">
-        <v>0.0148</v>
+        <v>1.4800000000000001E-2</v>
       </c>
       <c r="I48">
         <v>0.44</v>
@@ -3923,22 +4086,25 @@
         <v>480</v>
       </c>
       <c r="K48">
-        <v>0.0354</v>
+        <v>3.5400000000000001E-2</v>
       </c>
       <c r="L48" t="s">
         <v>483</v>
       </c>
       <c r="M48">
-        <v>0.0194</v>
+        <v>1.9400000000000001E-2</v>
       </c>
       <c r="N48">
-        <v>-0.1786</v>
+        <v>-0.17860000000000001</v>
       </c>
       <c r="O48">
-        <v>0.0243</v>
-      </c>
-    </row>
-    <row r="49" spans="2:15">
+        <v>2.4299999999999999E-2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>485</v>
+      </c>
       <c r="B49" t="s">
         <v>62</v>
       </c>
@@ -3955,10 +4121,10 @@
         <v>479</v>
       </c>
       <c r="G49">
-        <v>0.0094</v>
+        <v>9.4000000000000004E-3</v>
       </c>
       <c r="H49">
-        <v>0.0107</v>
+        <v>1.0699999999999999E-2</v>
       </c>
       <c r="I49">
         <v>0.184</v>
@@ -3973,16 +4139,19 @@
         <v>482</v>
       </c>
       <c r="M49">
-        <v>0.0359</v>
+        <v>3.5900000000000001E-2</v>
       </c>
       <c r="N49">
-        <v>0.335</v>
+        <v>0.33500000000000002</v>
       </c>
       <c r="O49">
-        <v>0.0021</v>
-      </c>
-    </row>
-    <row r="50" spans="2:15">
+        <v>2.0999999999999999E-3</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>484</v>
+      </c>
       <c r="B50" t="s">
         <v>63</v>
       </c>
@@ -3999,10 +4168,10 @@
         <v>479</v>
       </c>
       <c r="G50">
-        <v>-0.005</v>
+        <v>-5.0000000000000001E-3</v>
       </c>
       <c r="H50">
-        <v>0.0091</v>
+        <v>9.1000000000000004E-3</v>
       </c>
       <c r="I50">
         <v>0.23</v>
@@ -4011,22 +4180,25 @@
         <v>480</v>
       </c>
       <c r="K50">
-        <v>0.0166</v>
+        <v>1.66E-2</v>
       </c>
       <c r="L50" t="s">
         <v>483</v>
       </c>
       <c r="M50">
-        <v>0.4116</v>
+        <v>0.41160000000000002</v>
       </c>
       <c r="N50">
-        <v>0.8782</v>
+        <v>0.87819999999999998</v>
       </c>
       <c r="O50">
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="2:15">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>485</v>
+      </c>
       <c r="B51" t="s">
         <v>64</v>
       </c>
@@ -4043,34 +4215,37 @@
         <v>479</v>
       </c>
       <c r="G51">
-        <v>-0.0194</v>
+        <v>-1.9400000000000001E-2</v>
       </c>
       <c r="H51">
-        <v>0.015</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="I51">
-        <v>0.034</v>
+        <v>3.4000000000000002E-2</v>
       </c>
       <c r="J51" t="s">
         <v>481</v>
       </c>
       <c r="K51">
-        <v>0.0264</v>
+        <v>2.64E-2</v>
       </c>
       <c r="L51" t="s">
         <v>483</v>
       </c>
       <c r="M51">
-        <v>0.0412</v>
+        <v>4.1200000000000001E-2</v>
       </c>
       <c r="N51">
-        <v>0.2569</v>
+        <v>0.25690000000000002</v>
       </c>
       <c r="O51">
-        <v>0.0009</v>
-      </c>
-    </row>
-    <row r="52" spans="2:15">
+        <v>8.9999999999999998E-4</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>484</v>
+      </c>
       <c r="B52" t="s">
         <v>65</v>
       </c>
@@ -4087,10 +4262,10 @@
         <v>479</v>
       </c>
       <c r="G52">
-        <v>-0.0178</v>
+        <v>-1.78E-2</v>
       </c>
       <c r="H52">
-        <v>0.0158</v>
+        <v>1.5800000000000002E-2</v>
       </c>
       <c r="I52">
         <v>0.06</v>
@@ -4099,22 +4274,25 @@
         <v>481</v>
       </c>
       <c r="K52">
-        <v>0.031</v>
+        <v>3.1E-2</v>
       </c>
       <c r="L52" t="s">
         <v>483</v>
       </c>
       <c r="M52">
-        <v>0.0377</v>
+        <v>3.7699999999999997E-2</v>
       </c>
       <c r="N52">
-        <v>0.2333</v>
+        <v>0.23330000000000001</v>
       </c>
       <c r="O52">
-        <v>0.0016</v>
-      </c>
-    </row>
-    <row r="53" spans="2:15">
+        <v>1.6000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>485</v>
+      </c>
       <c r="B53" t="s">
         <v>66</v>
       </c>
@@ -4131,10 +4309,10 @@
         <v>479</v>
       </c>
       <c r="G53">
-        <v>-0.0074</v>
+        <v>-7.4000000000000003E-3</v>
       </c>
       <c r="H53">
-        <v>0.0127</v>
+        <v>1.2699999999999999E-2</v>
       </c>
       <c r="I53">
         <v>0.111</v>
@@ -4143,7 +4321,7 @@
         <v>481</v>
       </c>
       <c r="K53">
-        <v>0.0806</v>
+        <v>8.0600000000000005E-2</v>
       </c>
       <c r="L53" t="s">
         <v>483</v>
@@ -4152,13 +4330,16 @@
         <v>0.1421</v>
       </c>
       <c r="N53">
-        <v>0.5636</v>
+        <v>0.56359999999999999</v>
       </c>
       <c r="O53">
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="2:15">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>484</v>
+      </c>
       <c r="B54" t="s">
         <v>67</v>
       </c>
@@ -4175,34 +4356,37 @@
         <v>479</v>
       </c>
       <c r="G54">
-        <v>-0.0068</v>
+        <v>-6.7999999999999996E-3</v>
       </c>
       <c r="H54">
-        <v>0.0133</v>
+        <v>1.3299999999999999E-2</v>
       </c>
       <c r="I54">
-        <v>0.057</v>
+        <v>5.7000000000000002E-2</v>
       </c>
       <c r="J54" t="s">
         <v>481</v>
       </c>
       <c r="K54">
-        <v>0.0888</v>
+        <v>8.8800000000000004E-2</v>
       </c>
       <c r="L54" t="s">
         <v>483</v>
       </c>
       <c r="M54">
-        <v>0.1456</v>
+        <v>0.14560000000000001</v>
       </c>
       <c r="N54">
-        <v>0.546</v>
+        <v>0.54600000000000004</v>
       </c>
       <c r="O54">
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="2:15">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>485</v>
+      </c>
       <c r="B55" t="s">
         <v>68</v>
       </c>
@@ -4219,34 +4403,37 @@
         <v>479</v>
       </c>
       <c r="G55">
-        <v>-0.0133</v>
+        <v>-1.3299999999999999E-2</v>
       </c>
       <c r="H55">
-        <v>0.0119</v>
+        <v>1.1900000000000001E-2</v>
       </c>
       <c r="I55">
-        <v>0.019</v>
+        <v>1.9E-2</v>
       </c>
       <c r="J55" t="s">
         <v>481</v>
       </c>
       <c r="K55">
-        <v>0.0116</v>
+        <v>1.1599999999999999E-2</v>
       </c>
       <c r="L55" t="s">
         <v>483</v>
       </c>
       <c r="M55">
-        <v>0.1078</v>
+        <v>0.10780000000000001</v>
       </c>
       <c r="N55">
-        <v>0.5224</v>
+        <v>0.52239999999999998</v>
       </c>
       <c r="O55">
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="2:15">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>484</v>
+      </c>
       <c r="B56" t="s">
         <v>69</v>
       </c>
@@ -4263,19 +4450,19 @@
         <v>479</v>
       </c>
       <c r="G56">
-        <v>-0.0123</v>
+        <v>-1.23E-2</v>
       </c>
       <c r="H56">
-        <v>0.0126</v>
+        <v>1.26E-2</v>
       </c>
       <c r="I56">
-        <v>0.045</v>
+        <v>4.4999999999999998E-2</v>
       </c>
       <c r="J56" t="s">
         <v>481</v>
       </c>
       <c r="K56">
-        <v>0.0181</v>
+        <v>1.8100000000000002E-2</v>
       </c>
       <c r="L56" t="s">
         <v>483</v>
@@ -4290,7 +4477,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="2:15">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>485</v>
+      </c>
       <c r="B57" t="s">
         <v>70</v>
       </c>
@@ -4307,10 +4497,10 @@
         <v>479</v>
       </c>
       <c r="G57">
-        <v>0.0016</v>
+        <v>1.6000000000000001E-3</v>
       </c>
       <c r="H57">
-        <v>0.0078</v>
+        <v>7.7999999999999996E-3</v>
       </c>
       <c r="I57">
         <v>0.246</v>
@@ -4319,13 +4509,13 @@
         <v>480</v>
       </c>
       <c r="K57">
-        <v>0.2478</v>
+        <v>0.24779999999999999</v>
       </c>
       <c r="L57" t="s">
         <v>482</v>
       </c>
       <c r="M57">
-        <v>0.0029</v>
+        <v>2.8999999999999998E-3</v>
       </c>
       <c r="N57">
         <v>0.1318</v>
@@ -4334,7 +4524,10 @@
         <v>0.3841</v>
       </c>
     </row>
-    <row r="58" spans="2:15">
+    <row r="58" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>484</v>
+      </c>
       <c r="B58" t="s">
         <v>71</v>
       </c>
@@ -4351,34 +4544,37 @@
         <v>479</v>
       </c>
       <c r="G58">
-        <v>0.0031</v>
+        <v>3.0999999999999999E-3</v>
       </c>
       <c r="H58">
-        <v>0.009299999999999999</v>
+        <v>9.2999999999999992E-3</v>
       </c>
       <c r="I58">
-        <v>0.146</v>
+        <v>0.14599999999999999</v>
       </c>
       <c r="J58" t="s">
         <v>481</v>
       </c>
       <c r="K58">
-        <v>0.2433</v>
+        <v>0.24329999999999999</v>
       </c>
       <c r="L58" t="s">
         <v>482</v>
       </c>
       <c r="M58">
-        <v>0.0022</v>
+        <v>2.2000000000000001E-3</v>
       </c>
       <c r="N58">
-        <v>0.09710000000000001</v>
+        <v>9.7100000000000006E-2</v>
       </c>
       <c r="O58">
-        <v>0.445</v>
-      </c>
-    </row>
-    <row r="59" spans="2:15">
+        <v>0.44500000000000001</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>485</v>
+      </c>
       <c r="B59" t="s">
         <v>72</v>
       </c>
@@ -4395,34 +4591,37 @@
         <v>479</v>
       </c>
       <c r="G59">
-        <v>0.0015</v>
+        <v>1.5E-3</v>
       </c>
       <c r="H59">
-        <v>0.0048</v>
+        <v>4.7999999999999996E-3</v>
       </c>
       <c r="I59">
-        <v>0.027</v>
+        <v>2.7E-2</v>
       </c>
       <c r="J59" t="s">
         <v>481</v>
       </c>
       <c r="K59">
-        <v>0.0847</v>
+        <v>8.4699999999999998E-2</v>
       </c>
       <c r="L59" t="s">
         <v>483</v>
       </c>
       <c r="M59">
-        <v>0.0252</v>
+        <v>2.52E-2</v>
       </c>
       <c r="N59">
-        <v>-0.6246</v>
+        <v>-0.62460000000000004</v>
       </c>
       <c r="O59">
         <v>0.01</v>
       </c>
     </row>
-    <row r="60" spans="2:15">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>484</v>
+      </c>
       <c r="B60" t="s">
         <v>73</v>
       </c>
@@ -4439,13 +4638,13 @@
         <v>479</v>
       </c>
       <c r="G60">
-        <v>0.0021</v>
+        <v>2.0999999999999999E-3</v>
       </c>
       <c r="H60">
-        <v>0.0061</v>
+        <v>6.1000000000000004E-3</v>
       </c>
       <c r="I60">
-        <v>0.027</v>
+        <v>2.7E-2</v>
       </c>
       <c r="J60" t="s">
         <v>481</v>
@@ -4457,16 +4656,19 @@
         <v>483</v>
       </c>
       <c r="M60">
-        <v>0.0062</v>
+        <v>6.1999999999999998E-3</v>
       </c>
       <c r="N60">
-        <v>-0.2439</v>
+        <v>-0.24390000000000001</v>
       </c>
       <c r="O60">
-        <v>0.2033</v>
-      </c>
-    </row>
-    <row r="61" spans="2:15">
+        <v>0.20330000000000001</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>485</v>
+      </c>
       <c r="B61" t="s">
         <v>74</v>
       </c>
@@ -4483,34 +4685,37 @@
         <v>479</v>
       </c>
       <c r="G61">
-        <v>0.0015</v>
+        <v>1.5E-3</v>
       </c>
       <c r="H61">
-        <v>0.006</v>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="I61">
-        <v>0.041</v>
+        <v>4.1000000000000002E-2</v>
       </c>
       <c r="J61" t="s">
         <v>481</v>
       </c>
       <c r="K61">
-        <v>0.0489</v>
+        <v>4.8899999999999999E-2</v>
       </c>
       <c r="L61" t="s">
         <v>483</v>
       </c>
       <c r="M61">
-        <v>0.0008</v>
+        <v>8.0000000000000004E-4</v>
       </c>
       <c r="N61">
-        <v>-0.0912</v>
+        <v>-9.1200000000000003E-2</v>
       </c>
       <c r="O61">
-        <v>0.6429</v>
-      </c>
-    </row>
-    <row r="62" spans="2:15">
+        <v>0.64290000000000003</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>484</v>
+      </c>
       <c r="B62" t="s">
         <v>75</v>
       </c>
@@ -4527,19 +4732,19 @@
         <v>479</v>
       </c>
       <c r="G62">
-        <v>0.0026</v>
+        <v>2.5999999999999999E-3</v>
       </c>
       <c r="H62">
-        <v>0.0074</v>
+        <v>7.4000000000000003E-3</v>
       </c>
       <c r="I62">
-        <v>0.08500000000000001</v>
+        <v>8.5000000000000006E-2</v>
       </c>
       <c r="J62" t="s">
         <v>481</v>
       </c>
       <c r="K62">
-        <v>0.2536</v>
+        <v>0.25359999999999999</v>
       </c>
       <c r="L62" t="s">
         <v>482</v>
@@ -4548,13 +4753,16 @@
         <v>0</v>
       </c>
       <c r="N62">
-        <v>-0.0072</v>
+        <v>-7.1999999999999998E-3</v>
       </c>
       <c r="O62">
-        <v>0.9643</v>
-      </c>
-    </row>
-    <row r="63" spans="2:15">
+        <v>0.96430000000000005</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>485</v>
+      </c>
       <c r="B63" t="s">
         <v>76</v>
       </c>
@@ -4571,10 +4779,10 @@
         <v>479</v>
       </c>
       <c r="G63">
-        <v>0.0033</v>
+        <v>3.3E-3</v>
       </c>
       <c r="H63">
-        <v>0.0105</v>
+        <v>1.0500000000000001E-2</v>
       </c>
       <c r="I63">
         <v>0.154</v>
@@ -4583,22 +4791,25 @@
         <v>480</v>
       </c>
       <c r="K63">
-        <v>0.2108</v>
+        <v>0.21079999999999999</v>
       </c>
       <c r="L63" t="s">
         <v>482</v>
       </c>
       <c r="M63">
-        <v>0.0169</v>
+        <v>1.6899999999999998E-2</v>
       </c>
       <c r="N63">
-        <v>0.2362</v>
+        <v>0.23619999999999999</v>
       </c>
       <c r="O63">
-        <v>0.0355</v>
-      </c>
-    </row>
-    <row r="64" spans="2:15">
+        <v>3.5499999999999997E-2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>484</v>
+      </c>
       <c r="B64" t="s">
         <v>77</v>
       </c>
@@ -4615,34 +4826,37 @@
         <v>479</v>
       </c>
       <c r="G64">
-        <v>0.0048</v>
+        <v>4.7999999999999996E-3</v>
       </c>
       <c r="H64">
-        <v>0.0116</v>
+        <v>1.1599999999999999E-2</v>
       </c>
       <c r="I64">
-        <v>0.413</v>
+        <v>0.41299999999999998</v>
       </c>
       <c r="J64" t="s">
         <v>480</v>
       </c>
       <c r="K64">
-        <v>0.2201</v>
+        <v>0.22009999999999999</v>
       </c>
       <c r="L64" t="s">
         <v>482</v>
       </c>
       <c r="M64">
-        <v>0.0142</v>
+        <v>1.4200000000000001E-2</v>
       </c>
       <c r="N64">
         <v>0.1953</v>
       </c>
       <c r="O64">
-        <v>0.0543</v>
-      </c>
-    </row>
-    <row r="65" spans="2:15">
+        <v>5.4300000000000001E-2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>485</v>
+      </c>
       <c r="B65" t="s">
         <v>78</v>
       </c>
@@ -4659,34 +4873,37 @@
         <v>479</v>
       </c>
       <c r="G65">
-        <v>0.002</v>
+        <v>2E-3</v>
       </c>
       <c r="H65">
-        <v>0.0066</v>
+        <v>6.6E-3</v>
       </c>
       <c r="I65">
-        <v>0.004</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="J65" t="s">
         <v>481</v>
       </c>
       <c r="K65">
-        <v>0.2523</v>
+        <v>0.25230000000000002</v>
       </c>
       <c r="L65" t="s">
         <v>482</v>
       </c>
       <c r="M65">
-        <v>0.0005999999999999999</v>
+        <v>5.9999999999999995E-4</v>
       </c>
       <c r="N65">
-        <v>0.0679</v>
+        <v>6.7900000000000002E-2</v>
       </c>
       <c r="O65">
-        <v>0.705</v>
-      </c>
-    </row>
-    <row r="66" spans="2:15">
+        <v>0.70499999999999996</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>484</v>
+      </c>
       <c r="B66" t="s">
         <v>79</v>
       </c>
@@ -4703,34 +4920,37 @@
         <v>479</v>
       </c>
       <c r="G66">
-        <v>0.0026</v>
+        <v>2.5999999999999999E-3</v>
       </c>
       <c r="H66">
-        <v>0.0075</v>
+        <v>7.4999999999999997E-3</v>
       </c>
       <c r="I66">
-        <v>0.025</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J66" t="s">
         <v>481</v>
       </c>
       <c r="K66">
-        <v>0.237</v>
+        <v>0.23699999999999999</v>
       </c>
       <c r="L66" t="s">
         <v>482</v>
       </c>
       <c r="M66">
-        <v>0.0034</v>
+        <v>3.3999999999999998E-3</v>
       </c>
       <c r="N66">
         <v>0.1472</v>
       </c>
       <c r="O66">
-        <v>0.3484</v>
-      </c>
-    </row>
-    <row r="67" spans="2:15">
+        <v>0.34839999999999999</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>485</v>
+      </c>
       <c r="B67" t="s">
         <v>80</v>
       </c>
@@ -4747,34 +4967,37 @@
         <v>479</v>
       </c>
       <c r="G67">
-        <v>0.0027</v>
+        <v>2.7000000000000001E-3</v>
       </c>
       <c r="H67">
-        <v>0.0081</v>
+        <v>8.0999999999999996E-3</v>
       </c>
       <c r="I67">
-        <v>0.181</v>
+        <v>0.18099999999999999</v>
       </c>
       <c r="J67" t="s">
         <v>480</v>
       </c>
       <c r="K67">
-        <v>0.2182</v>
+        <v>0.21820000000000001</v>
       </c>
       <c r="L67" t="s">
         <v>482</v>
       </c>
       <c r="M67">
-        <v>0.008800000000000001</v>
+        <v>8.8000000000000005E-3</v>
       </c>
       <c r="N67">
-        <v>0.2196</v>
+        <v>0.21959999999999999</v>
       </c>
       <c r="O67">
-        <v>0.1306</v>
-      </c>
-    </row>
-    <row r="68" spans="2:15">
+        <v>0.13059999999999999</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>484</v>
+      </c>
       <c r="B68" t="s">
         <v>81</v>
       </c>
@@ -4791,34 +5014,37 @@
         <v>479</v>
       </c>
       <c r="G68">
-        <v>0.0037</v>
+        <v>3.7000000000000002E-3</v>
       </c>
       <c r="H68">
-        <v>0.0091</v>
+        <v>9.1000000000000004E-3</v>
       </c>
       <c r="I68">
-        <v>0.074</v>
+        <v>7.3999999999999996E-2</v>
       </c>
       <c r="J68" t="s">
         <v>481</v>
       </c>
       <c r="K68">
-        <v>0.2212</v>
+        <v>0.22120000000000001</v>
       </c>
       <c r="L68" t="s">
         <v>482</v>
       </c>
       <c r="M68">
-        <v>0.009900000000000001</v>
+        <v>9.9000000000000008E-3</v>
       </c>
       <c r="N68">
         <v>0.2077</v>
       </c>
       <c r="O68">
-        <v>0.1073</v>
-      </c>
-    </row>
-    <row r="69" spans="2:15">
+        <v>0.10730000000000001</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>485</v>
+      </c>
       <c r="B69" t="s">
         <v>82</v>
       </c>
@@ -4835,19 +5061,22 @@
         <v>479</v>
       </c>
       <c r="G69">
-        <v>0.0077</v>
+        <v>7.7000000000000002E-3</v>
       </c>
       <c r="H69">
-        <v>0.0033</v>
+        <v>3.3E-3</v>
       </c>
       <c r="I69">
-        <v>0.057</v>
+        <v>5.7000000000000002E-2</v>
       </c>
       <c r="J69" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="70" spans="2:15">
+    <row r="70" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>484</v>
+      </c>
       <c r="B70" t="s">
         <v>83</v>
       </c>
@@ -4864,19 +5093,22 @@
         <v>479</v>
       </c>
       <c r="G70">
-        <v>0.0446</v>
+        <v>4.4600000000000001E-2</v>
       </c>
       <c r="H70">
-        <v>0.019</v>
+        <v>1.9E-2</v>
       </c>
       <c r="I70">
-        <v>0.043</v>
+        <v>4.2999999999999997E-2</v>
       </c>
       <c r="J70" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="71" spans="2:15">
+    <row r="71" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>485</v>
+      </c>
       <c r="B71" t="s">
         <v>84</v>
       </c>
@@ -4893,25 +5125,25 @@
         <v>479</v>
       </c>
       <c r="G71">
-        <v>0.0076</v>
+        <v>7.6E-3</v>
       </c>
       <c r="H71">
-        <v>0.0036</v>
+        <v>3.5999999999999999E-3</v>
       </c>
       <c r="I71">
-        <v>0.051</v>
+        <v>5.0999999999999997E-2</v>
       </c>
       <c r="J71" t="s">
         <v>481</v>
       </c>
       <c r="K71">
-        <v>0.4961</v>
+        <v>0.49609999999999999</v>
       </c>
       <c r="L71" t="s">
         <v>482</v>
       </c>
       <c r="M71">
-        <v>0.5646</v>
+        <v>0.56459999999999999</v>
       </c>
       <c r="N71">
         <v>3.9819</v>
@@ -4920,7 +5152,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="2:15">
+    <row r="72" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>484</v>
+      </c>
       <c r="B72" t="s">
         <v>85</v>
       </c>
@@ -4937,19 +5172,19 @@
         <v>479</v>
       </c>
       <c r="G72">
-        <v>0.0373</v>
+        <v>3.73E-2</v>
       </c>
       <c r="H72">
-        <v>0.0157</v>
+        <v>1.5699999999999999E-2</v>
       </c>
       <c r="I72">
-        <v>0.025</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J72" t="s">
         <v>481</v>
       </c>
       <c r="K72">
-        <v>0.3027</v>
+        <v>0.30270000000000002</v>
       </c>
       <c r="L72" t="s">
         <v>482</v>
@@ -4958,13 +5193,16 @@
         <v>0.8629</v>
       </c>
       <c r="N72">
-        <v>1.1606</v>
+        <v>1.1606000000000001</v>
       </c>
       <c r="O72">
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="2:15">
+    <row r="73" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>485</v>
+      </c>
       <c r="B73" t="s">
         <v>86</v>
       </c>
@@ -4981,34 +5219,37 @@
         <v>479</v>
       </c>
       <c r="G73">
-        <v>0.0195</v>
+        <v>1.95E-2</v>
       </c>
       <c r="H73">
-        <v>0.0081</v>
+        <v>8.0999999999999996E-3</v>
       </c>
       <c r="I73">
-        <v>0.001</v>
+        <v>1E-3</v>
       </c>
       <c r="J73" t="s">
         <v>481</v>
       </c>
       <c r="K73">
-        <v>0.179</v>
+        <v>0.17899999999999999</v>
       </c>
       <c r="L73" t="s">
         <v>482</v>
       </c>
       <c r="M73">
-        <v>0.601</v>
+        <v>0.60099999999999998</v>
       </c>
       <c r="N73">
-        <v>1.8157</v>
+        <v>1.8157000000000001</v>
       </c>
       <c r="O73">
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="2:15">
+    <row r="74" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>484</v>
+      </c>
       <c r="B74" t="s">
         <v>87</v>
       </c>
@@ -5025,13 +5266,13 @@
         <v>479</v>
       </c>
       <c r="G74">
-        <v>0.023</v>
+        <v>2.3E-2</v>
       </c>
       <c r="H74">
-        <v>0.008999999999999999</v>
+        <v>8.9999999999999993E-3</v>
       </c>
       <c r="I74">
-        <v>0.002</v>
+        <v>2E-3</v>
       </c>
       <c r="J74" t="s">
         <v>481</v>
@@ -5052,7 +5293,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="2:15">
+    <row r="75" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>485</v>
+      </c>
       <c r="B75" t="s">
         <v>88</v>
       </c>
@@ -5069,34 +5313,37 @@
         <v>479</v>
       </c>
       <c r="G75">
-        <v>0.6162</v>
+        <v>0.61619999999999997</v>
       </c>
       <c r="H75">
-        <v>0.1592</v>
+        <v>0.15920000000000001</v>
       </c>
       <c r="I75">
-        <v>0.021</v>
+        <v>2.1000000000000001E-2</v>
       </c>
       <c r="J75" t="s">
         <v>481</v>
       </c>
       <c r="K75">
-        <v>0.0617</v>
+        <v>6.1699999999999998E-2</v>
       </c>
       <c r="L75" t="s">
         <v>483</v>
       </c>
       <c r="M75">
-        <v>0.423</v>
+        <v>0.42299999999999999</v>
       </c>
       <c r="N75">
-        <v>0.0776</v>
+        <v>7.7600000000000002E-2</v>
       </c>
       <c r="O75">
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="2:15">
+    <row r="76" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>484</v>
+      </c>
       <c r="B76" t="s">
         <v>89</v>
       </c>
@@ -5113,25 +5360,25 @@
         <v>479</v>
       </c>
       <c r="G76">
-        <v>0.009599999999999999</v>
+        <v>9.5999999999999992E-3</v>
       </c>
       <c r="H76">
-        <v>0.0025</v>
+        <v>2.5000000000000001E-3</v>
       </c>
       <c r="I76">
-        <v>0.003</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="J76" t="s">
         <v>481</v>
       </c>
       <c r="K76">
-        <v>0.0059</v>
+        <v>5.8999999999999999E-3</v>
       </c>
       <c r="L76" t="s">
         <v>483</v>
       </c>
       <c r="M76">
-        <v>0.7111</v>
+        <v>0.71109999999999995</v>
       </c>
       <c r="N76">
         <v>6.4116</v>
@@ -5140,7 +5387,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="2:15">
+    <row r="77" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>485</v>
+      </c>
       <c r="B77" t="s">
         <v>90</v>
       </c>
@@ -5157,34 +5407,37 @@
         <v>479</v>
       </c>
       <c r="G77">
-        <v>0.1786</v>
+        <v>0.17860000000000001</v>
       </c>
       <c r="H77">
-        <v>0.0393</v>
+        <v>3.9300000000000002E-2</v>
       </c>
       <c r="I77">
-        <v>0.333</v>
+        <v>0.33300000000000002</v>
       </c>
       <c r="J77" t="s">
         <v>480</v>
       </c>
       <c r="K77">
-        <v>0.0207</v>
+        <v>2.07E-2</v>
       </c>
       <c r="L77" t="s">
         <v>483</v>
       </c>
       <c r="M77">
-        <v>0.1403</v>
+        <v>0.14030000000000001</v>
       </c>
       <c r="N77">
-        <v>-0.1809</v>
+        <v>-0.18090000000000001</v>
       </c>
       <c r="O77">
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="2:15">
+    <row r="78" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>484</v>
+      </c>
       <c r="B78" t="s">
         <v>91</v>
       </c>
@@ -5201,10 +5454,10 @@
         <v>479</v>
       </c>
       <c r="G78">
-        <v>0.1738</v>
+        <v>0.17380000000000001</v>
       </c>
       <c r="H78">
-        <v>0.037</v>
+        <v>3.6999999999999998E-2</v>
       </c>
       <c r="I78">
         <v>0.12</v>
@@ -5213,22 +5466,25 @@
         <v>481</v>
       </c>
       <c r="K78">
-        <v>0.0057</v>
+        <v>5.7000000000000002E-3</v>
       </c>
       <c r="L78" t="s">
         <v>483</v>
       </c>
       <c r="M78">
-        <v>0.3063</v>
+        <v>0.30630000000000002</v>
       </c>
       <c r="N78">
-        <v>-0.2844</v>
+        <v>-0.28439999999999999</v>
       </c>
       <c r="O78">
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="2:15">
+    <row r="79" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>485</v>
+      </c>
       <c r="B79" t="s">
         <v>92</v>
       </c>
@@ -5251,28 +5507,31 @@
         <v>0.1318</v>
       </c>
       <c r="I79">
-        <v>0.634</v>
+        <v>0.63400000000000001</v>
       </c>
       <c r="J79" t="s">
         <v>480</v>
       </c>
       <c r="K79">
-        <v>0.0469</v>
+        <v>4.6899999999999997E-2</v>
       </c>
       <c r="L79" t="s">
         <v>483</v>
       </c>
       <c r="M79">
-        <v>0.0002</v>
+        <v>2.0000000000000001E-4</v>
       </c>
       <c r="N79">
-        <v>-0.0018</v>
+        <v>-1.8E-3</v>
       </c>
       <c r="O79">
         <v>0.8427</v>
       </c>
     </row>
-    <row r="80" spans="2:15">
+    <row r="80" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>484</v>
+      </c>
       <c r="B80" t="s">
         <v>93</v>
       </c>
@@ -5289,7 +5548,7 @@
         <v>479</v>
       </c>
       <c r="G80">
-        <v>0.1624</v>
+        <v>0.16239999999999999</v>
       </c>
       <c r="H80">
         <v>0.1152</v>
@@ -5301,7 +5560,7 @@
         <v>480</v>
       </c>
       <c r="K80">
-        <v>0.0463</v>
+        <v>4.6300000000000001E-2</v>
       </c>
       <c r="L80" t="s">
         <v>483</v>
@@ -5310,13 +5569,16 @@
         <v>0</v>
       </c>
       <c r="N80">
-        <v>0.001</v>
+        <v>1E-3</v>
       </c>
       <c r="O80">
         <v>0.9254</v>
       </c>
     </row>
-    <row r="81" spans="2:15">
+    <row r="81" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>485</v>
+      </c>
       <c r="B81" t="s">
         <v>94</v>
       </c>
@@ -5333,13 +5595,13 @@
         <v>479</v>
       </c>
       <c r="G81">
-        <v>0.0861</v>
+        <v>8.6099999999999996E-2</v>
       </c>
       <c r="H81">
         <v>0.1119</v>
       </c>
       <c r="I81">
-        <v>0.911</v>
+        <v>0.91100000000000003</v>
       </c>
       <c r="J81" t="s">
         <v>480</v>
@@ -5351,16 +5613,19 @@
         <v>482</v>
       </c>
       <c r="M81">
-        <v>0.0677</v>
+        <v>6.7699999999999996E-2</v>
       </c>
       <c r="N81">
-        <v>-0.0442</v>
+        <v>-4.4200000000000003E-2</v>
       </c>
       <c r="O81">
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="2:15">
+    <row r="82" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>484</v>
+      </c>
       <c r="B82" t="s">
         <v>95</v>
       </c>
@@ -5377,34 +5642,37 @@
         <v>479</v>
       </c>
       <c r="G82">
-        <v>0.0056</v>
+        <v>5.5999999999999999E-3</v>
       </c>
       <c r="H82">
-        <v>0.0089</v>
+        <v>8.8999999999999999E-3</v>
       </c>
       <c r="I82">
-        <v>0.861</v>
+        <v>0.86099999999999999</v>
       </c>
       <c r="J82" t="s">
         <v>480</v>
       </c>
       <c r="K82">
-        <v>0.2458</v>
+        <v>0.24579999999999999</v>
       </c>
       <c r="L82" t="s">
         <v>482</v>
       </c>
       <c r="M82">
-        <v>0.0495</v>
+        <v>4.9500000000000002E-2</v>
       </c>
       <c r="N82">
         <v>-0.4743</v>
       </c>
       <c r="O82">
-        <v>0.0003</v>
-      </c>
-    </row>
-    <row r="83" spans="2:15">
+        <v>2.9999999999999997E-4</v>
+      </c>
+    </row>
+    <row r="83" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>485</v>
+      </c>
       <c r="B83" t="s">
         <v>96</v>
       </c>
@@ -5421,34 +5689,37 @@
         <v>479</v>
       </c>
       <c r="G83">
-        <v>0.1866</v>
+        <v>0.18659999999999999</v>
       </c>
       <c r="H83">
-        <v>0.1335</v>
+        <v>0.13350000000000001</v>
       </c>
       <c r="I83">
-        <v>0.023</v>
+        <v>2.3E-2</v>
       </c>
       <c r="J83" t="s">
         <v>481</v>
       </c>
       <c r="K83">
-        <v>0.0315</v>
+        <v>3.15E-2</v>
       </c>
       <c r="L83" t="s">
         <v>483</v>
       </c>
       <c r="M83">
-        <v>0.0505</v>
+        <v>5.0500000000000003E-2</v>
       </c>
       <c r="N83">
-        <v>-0.032</v>
+        <v>-3.2000000000000001E-2</v>
       </c>
       <c r="O83">
-        <v>0.0002</v>
-      </c>
-    </row>
-    <row r="84" spans="2:15">
+        <v>2.0000000000000001E-4</v>
+      </c>
+    </row>
+    <row r="84" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>484</v>
+      </c>
       <c r="B84" t="s">
         <v>97</v>
       </c>
@@ -5465,10 +5736,10 @@
         <v>479</v>
       </c>
       <c r="G84">
-        <v>-0.0251</v>
+        <v>-2.5100000000000001E-2</v>
       </c>
       <c r="H84">
-        <v>0.0547</v>
+        <v>5.4699999999999999E-2</v>
       </c>
       <c r="I84">
         <v>0.999</v>
@@ -5483,16 +5754,19 @@
         <v>482</v>
       </c>
       <c r="M84">
-        <v>0.014</v>
+        <v>1.4E-2</v>
       </c>
       <c r="N84">
-        <v>0.0411</v>
+        <v>4.1099999999999998E-2</v>
       </c>
       <c r="O84">
-        <v>0.0556</v>
-      </c>
-    </row>
-    <row r="85" spans="2:15">
+        <v>5.5599999999999997E-2</v>
+      </c>
+    </row>
+    <row r="85" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>485</v>
+      </c>
       <c r="B85" t="s">
         <v>98</v>
       </c>
@@ -5506,10 +5780,10 @@
         <v>479</v>
       </c>
       <c r="G85">
-        <v>-0.0523</v>
+        <v>-5.2299999999999999E-2</v>
       </c>
       <c r="H85">
-        <v>0.039</v>
+        <v>3.9E-2</v>
       </c>
       <c r="I85">
         <v>0.186</v>
@@ -5518,22 +5792,25 @@
         <v>480</v>
       </c>
       <c r="K85">
-        <v>0.0144</v>
+        <v>1.44E-2</v>
       </c>
       <c r="L85" t="s">
         <v>483</v>
       </c>
       <c r="M85">
-        <v>0.0104</v>
+        <v>1.04E-2</v>
       </c>
       <c r="N85">
-        <v>-0.0497</v>
+        <v>-4.9700000000000001E-2</v>
       </c>
       <c r="O85">
-        <v>0.099</v>
-      </c>
-    </row>
-    <row r="86" spans="2:15">
+        <v>9.9000000000000005E-2</v>
+      </c>
+    </row>
+    <row r="86" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>484</v>
+      </c>
       <c r="B86" t="s">
         <v>99</v>
       </c>
@@ -5547,34 +5824,37 @@
         <v>479</v>
       </c>
       <c r="G86">
-        <v>-0.0366</v>
+        <v>-3.6600000000000001E-2</v>
       </c>
       <c r="H86">
-        <v>0.0384</v>
+        <v>3.8399999999999997E-2</v>
       </c>
       <c r="I86">
-        <v>0.142</v>
+        <v>0.14199999999999999</v>
       </c>
       <c r="J86" t="s">
         <v>481</v>
       </c>
       <c r="K86">
-        <v>0.0154</v>
+        <v>1.54E-2</v>
       </c>
       <c r="L86" t="s">
         <v>483</v>
       </c>
       <c r="M86">
-        <v>0.0095</v>
+        <v>9.4999999999999998E-3</v>
       </c>
       <c r="N86">
-        <v>-0.0483</v>
+        <v>-4.8300000000000003E-2</v>
       </c>
       <c r="O86">
-        <v>0.1155</v>
-      </c>
-    </row>
-    <row r="87" spans="2:15">
+        <v>0.11550000000000001</v>
+      </c>
+    </row>
+    <row r="87" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>485</v>
+      </c>
       <c r="B87" t="s">
         <v>100</v>
       </c>
@@ -5591,10 +5871,10 @@
         <v>479</v>
       </c>
       <c r="G87">
-        <v>-0.0016</v>
+        <v>-1.6000000000000001E-3</v>
       </c>
       <c r="H87">
-        <v>0.011</v>
+        <v>1.0999999999999999E-2</v>
       </c>
       <c r="I87">
         <v>0</v>
@@ -5603,22 +5883,25 @@
         <v>481</v>
       </c>
       <c r="K87">
-        <v>0.0014</v>
+        <v>1.4E-3</v>
       </c>
       <c r="L87" t="s">
         <v>483</v>
       </c>
       <c r="M87">
-        <v>0.3757</v>
+        <v>0.37569999999999998</v>
       </c>
       <c r="N87">
-        <v>-1.0577</v>
+        <v>-1.0577000000000001</v>
       </c>
       <c r="O87">
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="2:15">
+    <row r="88" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>484</v>
+      </c>
       <c r="B88" t="s">
         <v>101</v>
       </c>
@@ -5635,10 +5918,10 @@
         <v>479</v>
       </c>
       <c r="G88">
-        <v>0.0001</v>
+        <v>1E-4</v>
       </c>
       <c r="H88">
-        <v>0.0098</v>
+        <v>9.7999999999999997E-3</v>
       </c>
       <c r="I88">
         <v>0</v>
@@ -5653,16 +5936,19 @@
         <v>482</v>
       </c>
       <c r="M88">
-        <v>0.4697</v>
+        <v>0.46970000000000001</v>
       </c>
       <c r="N88">
-        <v>-1.3241</v>
+        <v>-1.3241000000000001</v>
       </c>
       <c r="O88">
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="2:15">
+    <row r="89" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>485</v>
+      </c>
       <c r="B89" t="s">
         <v>102</v>
       </c>
@@ -5679,10 +5965,10 @@
         <v>479</v>
       </c>
       <c r="G89">
-        <v>-0.002</v>
+        <v>-2E-3</v>
       </c>
       <c r="H89">
-        <v>0.0113</v>
+        <v>1.1299999999999999E-2</v>
       </c>
       <c r="I89">
         <v>0</v>
@@ -5691,22 +5977,25 @@
         <v>481</v>
       </c>
       <c r="K89">
-        <v>0.0011</v>
+        <v>1.1000000000000001E-3</v>
       </c>
       <c r="L89" t="s">
         <v>483</v>
       </c>
       <c r="M89">
-        <v>0.3517</v>
+        <v>0.35170000000000001</v>
       </c>
       <c r="N89">
-        <v>-0.9962</v>
+        <v>-0.99619999999999997</v>
       </c>
       <c r="O89">
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="2:15">
+    <row r="90" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>484</v>
+      </c>
       <c r="B90" t="s">
         <v>103</v>
       </c>
@@ -5723,34 +6012,37 @@
         <v>479</v>
       </c>
       <c r="G90">
-        <v>-0.002</v>
+        <v>-2E-3</v>
       </c>
       <c r="H90">
-        <v>0.0119</v>
+        <v>1.1900000000000001E-2</v>
       </c>
       <c r="I90">
-        <v>0.005</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="J90" t="s">
         <v>481</v>
       </c>
       <c r="K90">
-        <v>0.3441</v>
+        <v>0.34410000000000002</v>
       </c>
       <c r="L90" t="s">
         <v>482</v>
       </c>
       <c r="M90">
-        <v>0.3596</v>
+        <v>0.35959999999999998</v>
       </c>
       <c r="N90">
-        <v>-0.9542</v>
+        <v>-0.95420000000000005</v>
       </c>
       <c r="O90">
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="2:15">
+    <row r="91" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>485</v>
+      </c>
       <c r="B91" t="s">
         <v>104</v>
       </c>
@@ -5767,10 +6059,10 @@
         <v>479</v>
       </c>
       <c r="G91">
-        <v>-0.0003</v>
+        <v>-2.9999999999999997E-4</v>
       </c>
       <c r="H91">
-        <v>0.011</v>
+        <v>1.0999999999999999E-2</v>
       </c>
       <c r="I91">
         <v>0</v>
@@ -5779,7 +6071,7 @@
         <v>481</v>
       </c>
       <c r="K91">
-        <v>0.3747</v>
+        <v>0.37469999999999998</v>
       </c>
       <c r="L91" t="s">
         <v>482</v>
@@ -5788,13 +6080,16 @@
         <v>0.4577</v>
       </c>
       <c r="N91">
-        <v>-1.1719</v>
+        <v>-1.1718999999999999</v>
       </c>
       <c r="O91">
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="2:15">
+    <row r="92" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>484</v>
+      </c>
       <c r="B92" t="s">
         <v>105</v>
       </c>
@@ -5811,10 +6106,10 @@
         <v>479</v>
       </c>
       <c r="G92">
-        <v>-0.0025</v>
+        <v>-2.5000000000000001E-3</v>
       </c>
       <c r="H92">
-        <v>0.0129</v>
+        <v>1.29E-2</v>
       </c>
       <c r="I92">
         <v>0</v>
@@ -5823,22 +6118,25 @@
         <v>481</v>
       </c>
       <c r="K92">
-        <v>0.0569</v>
+        <v>5.6899999999999999E-2</v>
       </c>
       <c r="L92" t="s">
         <v>483</v>
       </c>
       <c r="M92">
-        <v>0.2796</v>
+        <v>0.27960000000000002</v>
       </c>
       <c r="N92">
-        <v>-0.7815</v>
+        <v>-0.78149999999999997</v>
       </c>
       <c r="O92">
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="2:15">
+    <row r="93" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>485</v>
+      </c>
       <c r="B93" t="s">
         <v>106</v>
       </c>
@@ -5855,25 +6153,25 @@
         <v>479</v>
       </c>
       <c r="G93">
-        <v>0.0023</v>
+        <v>2.3E-3</v>
       </c>
       <c r="H93">
-        <v>0.008500000000000001</v>
+        <v>8.5000000000000006E-3</v>
       </c>
       <c r="I93">
-        <v>0.005</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="J93" t="s">
         <v>481</v>
       </c>
       <c r="K93">
-        <v>0.0863</v>
+        <v>8.6300000000000002E-2</v>
       </c>
       <c r="L93" t="s">
         <v>483</v>
       </c>
       <c r="M93">
-        <v>0.4139</v>
+        <v>0.41389999999999999</v>
       </c>
       <c r="N93">
         <v>-1.4373</v>
@@ -5882,7 +6180,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="2:15">
+    <row r="94" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>484</v>
+      </c>
       <c r="B94" t="s">
         <v>107</v>
       </c>
@@ -5899,25 +6200,25 @@
         <v>479</v>
       </c>
       <c r="G94">
-        <v>0.0009</v>
+        <v>8.9999999999999998E-4</v>
       </c>
       <c r="H94">
-        <v>0.0111</v>
+        <v>1.11E-2</v>
       </c>
       <c r="I94">
-        <v>0.008</v>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="J94" t="s">
         <v>481</v>
       </c>
       <c r="K94">
-        <v>0.0062</v>
+        <v>6.1999999999999998E-3</v>
       </c>
       <c r="L94" t="s">
         <v>483</v>
       </c>
       <c r="M94">
-        <v>0.5908</v>
+        <v>0.59079999999999999</v>
       </c>
       <c r="N94">
         <v>-1.3167</v>
@@ -5926,7 +6227,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="2:15">
+    <row r="95" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>485</v>
+      </c>
       <c r="B95" t="s">
         <v>108</v>
       </c>
@@ -5943,10 +6247,10 @@
         <v>479</v>
       </c>
       <c r="G95">
-        <v>-0.0033</v>
+        <v>-3.3E-3</v>
       </c>
       <c r="H95">
-        <v>0.0118</v>
+        <v>1.18E-2</v>
       </c>
       <c r="I95">
         <v>0.498</v>
@@ -5955,22 +6259,25 @@
         <v>480</v>
       </c>
       <c r="K95">
-        <v>0.0327</v>
+        <v>3.27E-2</v>
       </c>
       <c r="L95" t="s">
         <v>483</v>
       </c>
       <c r="M95">
-        <v>0.0001</v>
+        <v>1E-4</v>
       </c>
       <c r="N95">
-        <v>-0.0192</v>
+        <v>-1.9199999999999998E-2</v>
       </c>
       <c r="O95">
-        <v>0.8483000000000001</v>
-      </c>
-    </row>
-    <row r="96" spans="2:15">
+        <v>0.84830000000000005</v>
+      </c>
+    </row>
+    <row r="96" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>484</v>
+      </c>
       <c r="B96" t="s">
         <v>109</v>
       </c>
@@ -5987,34 +6294,37 @@
         <v>479</v>
       </c>
       <c r="G96">
-        <v>0.0074</v>
+        <v>7.4000000000000003E-3</v>
       </c>
       <c r="H96">
-        <v>0.0237</v>
+        <v>2.3699999999999999E-2</v>
       </c>
       <c r="I96">
-        <v>0.978</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="J96" t="s">
         <v>480</v>
       </c>
       <c r="K96">
-        <v>0.015</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="L96" t="s">
         <v>483</v>
       </c>
       <c r="M96">
-        <v>0.0852</v>
+        <v>8.5199999999999998E-2</v>
       </c>
       <c r="N96">
-        <v>0.0992</v>
+        <v>9.9199999999999997E-2</v>
       </c>
       <c r="O96">
-        <v>0.0005999999999999999</v>
-      </c>
-    </row>
-    <row r="97" spans="2:15">
+        <v>5.9999999999999995E-4</v>
+      </c>
+    </row>
+    <row r="97" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>485</v>
+      </c>
       <c r="B97" t="s">
         <v>110</v>
       </c>
@@ -6031,10 +6341,10 @@
         <v>479</v>
       </c>
       <c r="G97">
-        <v>0.0007</v>
+        <v>6.9999999999999999E-4</v>
       </c>
       <c r="H97">
-        <v>0.009599999999999999</v>
+        <v>9.5999999999999992E-3</v>
       </c>
       <c r="I97">
         <v>0</v>
@@ -6043,22 +6353,25 @@
         <v>481</v>
       </c>
       <c r="K97">
-        <v>0.197</v>
+        <v>0.19700000000000001</v>
       </c>
       <c r="L97" t="s">
         <v>482</v>
       </c>
       <c r="M97">
-        <v>0.0317</v>
+        <v>3.1699999999999999E-2</v>
       </c>
       <c r="N97">
-        <v>-0.3516</v>
+        <v>-0.35160000000000002</v>
       </c>
       <c r="O97">
-        <v>0.0038</v>
-      </c>
-    </row>
-    <row r="98" spans="2:15">
+        <v>3.8E-3</v>
+      </c>
+    </row>
+    <row r="98" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>484</v>
+      </c>
       <c r="B98" t="s">
         <v>111</v>
       </c>
@@ -6075,10 +6388,10 @@
         <v>479</v>
       </c>
       <c r="G98">
-        <v>0.0003</v>
+        <v>2.9999999999999997E-4</v>
       </c>
       <c r="H98">
-        <v>0.0145</v>
+        <v>1.4500000000000001E-2</v>
       </c>
       <c r="I98">
         <v>0</v>
@@ -6087,22 +6400,25 @@
         <v>481</v>
       </c>
       <c r="K98">
-        <v>0.0575</v>
+        <v>5.7500000000000002E-2</v>
       </c>
       <c r="L98" t="s">
         <v>483</v>
       </c>
       <c r="M98">
-        <v>0.0474</v>
+        <v>4.7399999999999998E-2</v>
       </c>
       <c r="N98">
         <v>-0.2853</v>
       </c>
       <c r="O98">
-        <v>0.0004</v>
-      </c>
-    </row>
-    <row r="99" spans="2:15">
+        <v>4.0000000000000002E-4</v>
+      </c>
+    </row>
+    <row r="99" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>485</v>
+      </c>
       <c r="B99" t="s">
         <v>112</v>
       </c>
@@ -6119,10 +6435,10 @@
         <v>479</v>
       </c>
       <c r="G99">
-        <v>0.0033</v>
+        <v>3.3E-3</v>
       </c>
       <c r="H99">
-        <v>0.0201</v>
+        <v>2.01E-2</v>
       </c>
       <c r="I99">
         <v>0</v>
@@ -6137,16 +6453,19 @@
         <v>482</v>
       </c>
       <c r="M99">
-        <v>0.0174</v>
+        <v>1.7399999999999999E-2</v>
       </c>
       <c r="N99">
         <v>-0.1245</v>
       </c>
       <c r="O99">
-        <v>0.0326</v>
-      </c>
-    </row>
-    <row r="100" spans="2:15">
+        <v>3.2599999999999997E-2</v>
+      </c>
+    </row>
+    <row r="100" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>484</v>
+      </c>
       <c r="B100" t="s">
         <v>113</v>
       </c>
@@ -6163,10 +6482,10 @@
         <v>479</v>
       </c>
       <c r="G100">
-        <v>0.0005</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="H100">
-        <v>0.0234</v>
+        <v>2.3400000000000001E-2</v>
       </c>
       <c r="I100">
         <v>0</v>
@@ -6175,22 +6494,25 @@
         <v>481</v>
       </c>
       <c r="K100">
-        <v>0.0595</v>
+        <v>5.9499999999999997E-2</v>
       </c>
       <c r="L100" t="s">
         <v>483</v>
       </c>
       <c r="M100">
-        <v>0.0329</v>
+        <v>3.2899999999999999E-2</v>
       </c>
       <c r="N100">
-        <v>-0.147</v>
+        <v>-0.14699999999999999</v>
       </c>
       <c r="O100">
-        <v>0.0032</v>
-      </c>
-    </row>
-    <row r="101" spans="2:15">
+        <v>3.2000000000000002E-3</v>
+      </c>
+    </row>
+    <row r="101" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>485</v>
+      </c>
       <c r="B101" t="s">
         <v>114</v>
       </c>
@@ -6207,10 +6529,10 @@
         <v>479</v>
       </c>
       <c r="G101">
-        <v>0.0007</v>
+        <v>6.9999999999999999E-4</v>
       </c>
       <c r="H101">
-        <v>0.0184</v>
+        <v>1.84E-2</v>
       </c>
       <c r="I101">
         <v>0</v>
@@ -6219,22 +6541,25 @@
         <v>481</v>
       </c>
       <c r="K101">
-        <v>0.206</v>
+        <v>0.20599999999999999</v>
       </c>
       <c r="L101" t="s">
         <v>482</v>
       </c>
       <c r="M101">
-        <v>0.0048</v>
+        <v>4.7999999999999996E-3</v>
       </c>
       <c r="N101">
-        <v>-0.07140000000000001</v>
+        <v>-7.1400000000000005E-2</v>
       </c>
       <c r="O101">
         <v>0.2636</v>
       </c>
     </row>
-    <row r="102" spans="2:15">
+    <row r="102" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>484</v>
+      </c>
       <c r="B102" t="s">
         <v>115</v>
       </c>
@@ -6251,19 +6576,19 @@
         <v>479</v>
       </c>
       <c r="G102">
-        <v>0.0019</v>
+        <v>1.9E-3</v>
       </c>
       <c r="H102">
-        <v>0.0127</v>
+        <v>1.2699999999999999E-2</v>
       </c>
       <c r="I102">
-        <v>0.002</v>
+        <v>2E-3</v>
       </c>
       <c r="J102" t="s">
         <v>481</v>
       </c>
       <c r="K102">
-        <v>0.07099999999999999</v>
+        <v>7.0999999999999994E-2</v>
       </c>
       <c r="L102" t="s">
         <v>483</v>
@@ -6272,13 +6597,16 @@
         <v>0.1138</v>
       </c>
       <c r="N102">
-        <v>-0.5034999999999999</v>
+        <v>-0.50349999999999995</v>
       </c>
       <c r="O102">
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="2:15">
+    <row r="103" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>485</v>
+      </c>
       <c r="B103" t="s">
         <v>116</v>
       </c>
@@ -6295,10 +6623,10 @@
         <v>479</v>
       </c>
       <c r="G103">
-        <v>0.0008</v>
+        <v>8.0000000000000004E-4</v>
       </c>
       <c r="H103">
-        <v>0.0218</v>
+        <v>2.18E-2</v>
       </c>
       <c r="I103">
         <v>0</v>
@@ -6313,16 +6641,19 @@
         <v>483</v>
       </c>
       <c r="M103">
-        <v>0.227</v>
+        <v>0.22700000000000001</v>
       </c>
       <c r="N103">
-        <v>-0.4159</v>
+        <v>-0.41589999999999999</v>
       </c>
       <c r="O103">
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="2:15">
+    <row r="104" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>484</v>
+      </c>
       <c r="B104" t="s">
         <v>117</v>
       </c>
@@ -6339,34 +6670,37 @@
         <v>479</v>
       </c>
       <c r="G104">
-        <v>0.0103</v>
+        <v>1.03E-2</v>
       </c>
       <c r="H104">
-        <v>0.0246</v>
+        <v>2.46E-2</v>
       </c>
       <c r="I104">
-        <v>0.014</v>
+        <v>1.4E-2</v>
       </c>
       <c r="J104" t="s">
         <v>481</v>
       </c>
       <c r="K104">
-        <v>0.0876</v>
+        <v>8.7599999999999997E-2</v>
       </c>
       <c r="L104" t="s">
         <v>483</v>
       </c>
       <c r="M104">
-        <v>0.1611</v>
+        <v>0.16109999999999999</v>
       </c>
       <c r="N104">
-        <v>-0.3093</v>
+        <v>-0.30930000000000002</v>
       </c>
       <c r="O104">
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="2:15">
+    <row r="105" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>485</v>
+      </c>
       <c r="B105" t="s">
         <v>118</v>
       </c>
@@ -6383,10 +6717,10 @@
         <v>479</v>
       </c>
       <c r="G105">
-        <v>0.0013</v>
+        <v>1.2999999999999999E-3</v>
       </c>
       <c r="H105">
-        <v>0.0309</v>
+        <v>3.09E-2</v>
       </c>
       <c r="I105">
         <v>0</v>
@@ -6395,7 +6729,7 @@
         <v>481</v>
       </c>
       <c r="K105">
-        <v>0.1833</v>
+        <v>0.18329999999999999</v>
       </c>
       <c r="L105" t="s">
         <v>482</v>
@@ -6404,13 +6738,16 @@
         <v>0.1993</v>
       </c>
       <c r="N105">
-        <v>-0.2748</v>
+        <v>-0.27479999999999999</v>
       </c>
       <c r="O105">
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="2:15">
+    <row r="106" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>484</v>
+      </c>
       <c r="B106" t="s">
         <v>119</v>
       </c>
@@ -6427,19 +6764,19 @@
         <v>479</v>
       </c>
       <c r="G106">
-        <v>0.002</v>
+        <v>2E-3</v>
       </c>
       <c r="H106">
-        <v>0.0179</v>
+        <v>1.7899999999999999E-2</v>
       </c>
       <c r="I106">
-        <v>0.004</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="J106" t="s">
         <v>481</v>
       </c>
       <c r="K106">
-        <v>0.269</v>
+        <v>0.26900000000000002</v>
       </c>
       <c r="L106" t="s">
         <v>482</v>
@@ -6451,10 +6788,13 @@
         <v>-0.26</v>
       </c>
       <c r="O106">
-        <v>0.0001</v>
-      </c>
-    </row>
-    <row r="107" spans="2:15">
+        <v>1E-4</v>
+      </c>
+    </row>
+    <row r="107" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>485</v>
+      </c>
       <c r="B107" t="s">
         <v>120</v>
       </c>
@@ -6471,19 +6811,19 @@
         <v>479</v>
       </c>
       <c r="G107">
-        <v>0.0036</v>
+        <v>3.5999999999999999E-3</v>
       </c>
       <c r="H107">
-        <v>0.0156</v>
+        <v>1.5599999999999999E-2</v>
       </c>
       <c r="I107">
-        <v>0.001</v>
+        <v>1E-3</v>
       </c>
       <c r="J107" t="s">
         <v>481</v>
       </c>
       <c r="K107">
-        <v>0.1999</v>
+        <v>0.19989999999999999</v>
       </c>
       <c r="L107" t="s">
         <v>482</v>
@@ -6492,13 +6832,16 @@
         <v>0.1431</v>
       </c>
       <c r="N107">
-        <v>-0.4594</v>
+        <v>-0.45939999999999998</v>
       </c>
       <c r="O107">
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="2:15">
+    <row r="108" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>484</v>
+      </c>
       <c r="B108" t="s">
         <v>121</v>
       </c>
@@ -6515,34 +6858,37 @@
         <v>479</v>
       </c>
       <c r="G108">
-        <v>0.0013</v>
+        <v>1.2999999999999999E-3</v>
       </c>
       <c r="H108">
-        <v>0.0293</v>
+        <v>2.93E-2</v>
       </c>
       <c r="I108">
-        <v>0.004</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="J108" t="s">
         <v>481</v>
       </c>
       <c r="K108">
-        <v>0.2325</v>
+        <v>0.23250000000000001</v>
       </c>
       <c r="L108" t="s">
         <v>482</v>
       </c>
       <c r="M108">
-        <v>0.3511</v>
+        <v>0.35110000000000002</v>
       </c>
       <c r="N108">
-        <v>-0.3835</v>
+        <v>-0.38350000000000001</v>
       </c>
       <c r="O108">
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="2:15">
+    <row r="109" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>485</v>
+      </c>
       <c r="B109" t="s">
         <v>122</v>
       </c>
@@ -6559,34 +6905,37 @@
         <v>479</v>
       </c>
       <c r="G109">
-        <v>0.0205</v>
+        <v>2.0500000000000001E-2</v>
       </c>
       <c r="H109">
-        <v>0.0285</v>
+        <v>2.8500000000000001E-2</v>
       </c>
       <c r="I109">
-        <v>0.005</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="J109" t="s">
         <v>481</v>
       </c>
       <c r="K109">
-        <v>0.3257</v>
+        <v>0.32569999999999999</v>
       </c>
       <c r="L109" t="s">
         <v>482</v>
       </c>
       <c r="M109">
-        <v>0.3723</v>
+        <v>0.37230000000000002</v>
       </c>
       <c r="N109">
-        <v>-0.4066</v>
+        <v>-0.40660000000000002</v>
       </c>
       <c r="O109">
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="2:15">
+    <row r="110" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>484</v>
+      </c>
       <c r="B110" t="s">
         <v>123</v>
       </c>
@@ -6603,10 +6952,10 @@
         <v>479</v>
       </c>
       <c r="G110">
-        <v>0.0026</v>
+        <v>2.5999999999999999E-3</v>
       </c>
       <c r="H110">
-        <v>0.0385</v>
+        <v>3.85E-2</v>
       </c>
       <c r="I110">
         <v>0</v>
@@ -6615,22 +6964,25 @@
         <v>481</v>
       </c>
       <c r="K110">
-        <v>0.2832</v>
+        <v>0.28320000000000001</v>
       </c>
       <c r="L110" t="s">
         <v>482</v>
       </c>
       <c r="M110">
-        <v>0.3143</v>
+        <v>0.31430000000000002</v>
       </c>
       <c r="N110">
-        <v>-0.2769</v>
+        <v>-0.27689999999999998</v>
       </c>
       <c r="O110">
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="2:15">
+    <row r="111" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>485</v>
+      </c>
       <c r="B111" t="s">
         <v>124</v>
       </c>
@@ -6647,13 +6999,13 @@
         <v>479</v>
       </c>
       <c r="G111">
-        <v>0.0041</v>
+        <v>4.1000000000000003E-3</v>
       </c>
       <c r="H111">
-        <v>0.0153</v>
+        <v>1.5299999999999999E-2</v>
       </c>
       <c r="I111">
-        <v>0.004</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="J111" t="s">
         <v>481</v>
@@ -6665,16 +7017,19 @@
         <v>482</v>
       </c>
       <c r="M111">
-        <v>0.2106</v>
+        <v>0.21060000000000001</v>
       </c>
       <c r="N111">
-        <v>-0.5713</v>
+        <v>-0.57130000000000003</v>
       </c>
       <c r="O111">
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="2:15">
+    <row r="112" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
+        <v>484</v>
+      </c>
       <c r="B112" t="s">
         <v>125</v>
       </c>
@@ -6691,25 +7046,25 @@
         <v>479</v>
       </c>
       <c r="G112">
-        <v>0.0068</v>
+        <v>6.7999999999999996E-3</v>
       </c>
       <c r="H112">
-        <v>0.0216</v>
+        <v>2.1600000000000001E-2</v>
       </c>
       <c r="I112">
-        <v>0.007</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="J112" t="s">
         <v>481</v>
       </c>
       <c r="K112">
-        <v>0.0131</v>
+        <v>1.3100000000000001E-2</v>
       </c>
       <c r="L112" t="s">
         <v>483</v>
       </c>
       <c r="M112">
-        <v>0.0644</v>
+        <v>6.4399999999999999E-2</v>
       </c>
       <c r="N112">
         <v>-0.223</v>
@@ -6718,7 +7073,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="2:15">
+    <row r="113" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
+        <v>485</v>
+      </c>
       <c r="B113" t="s">
         <v>126</v>
       </c>
@@ -6735,19 +7093,19 @@
         <v>479</v>
       </c>
       <c r="G113">
-        <v>0.0019</v>
+        <v>1.9E-3</v>
       </c>
       <c r="H113">
-        <v>0.0426</v>
+        <v>4.2599999999999999E-2</v>
       </c>
       <c r="I113">
-        <v>0.001</v>
+        <v>1E-3</v>
       </c>
       <c r="J113" t="s">
         <v>481</v>
       </c>
       <c r="K113">
-        <v>0.0017</v>
+        <v>1.6999999999999999E-3</v>
       </c>
       <c r="L113" t="s">
         <v>483</v>
@@ -6762,7 +7120,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="2:15">
+    <row r="114" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
+        <v>484</v>
+      </c>
       <c r="B114" t="s">
         <v>127</v>
       </c>
@@ -6779,13 +7140,13 @@
         <v>479</v>
       </c>
       <c r="G114">
-        <v>0.041</v>
+        <v>4.1000000000000002E-2</v>
       </c>
       <c r="H114">
-        <v>0.0411</v>
+        <v>4.1099999999999998E-2</v>
       </c>
       <c r="I114">
-        <v>0.006</v>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="J114" t="s">
         <v>481</v>
@@ -6797,16 +7158,19 @@
         <v>483</v>
       </c>
       <c r="M114">
-        <v>0.2035</v>
+        <v>0.20349999999999999</v>
       </c>
       <c r="N114">
-        <v>-0.2086</v>
+        <v>-0.20860000000000001</v>
       </c>
       <c r="O114">
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="2:15">
+    <row r="115" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
+        <v>485</v>
+      </c>
       <c r="B115" t="s">
         <v>128</v>
       </c>
@@ -6823,10 +7187,10 @@
         <v>479</v>
       </c>
       <c r="G115">
-        <v>0.0058</v>
+        <v>5.7999999999999996E-3</v>
       </c>
       <c r="H115">
-        <v>0.0481</v>
+        <v>4.8099999999999997E-2</v>
       </c>
       <c r="I115">
         <v>0</v>
@@ -6850,7 +7214,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="2:15">
+    <row r="116" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
+        <v>484</v>
+      </c>
       <c r="B116" t="s">
         <v>129</v>
       </c>
@@ -6867,10 +7234,10 @@
         <v>479</v>
       </c>
       <c r="G116">
-        <v>0.009299999999999999</v>
+        <v>9.2999999999999992E-3</v>
       </c>
       <c r="H116">
-        <v>0.0176</v>
+        <v>1.7600000000000001E-2</v>
       </c>
       <c r="I116">
         <v>0.224</v>
@@ -6879,22 +7246,25 @@
         <v>480</v>
       </c>
       <c r="K116">
-        <v>0.0054</v>
+        <v>5.4000000000000003E-3</v>
       </c>
       <c r="L116" t="s">
         <v>483</v>
       </c>
       <c r="M116">
-        <v>0.2325</v>
+        <v>0.23250000000000001</v>
       </c>
       <c r="N116">
-        <v>-0.5208</v>
+        <v>-0.52080000000000004</v>
       </c>
       <c r="O116">
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="2:15">
+    <row r="117" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
+        <v>485</v>
+      </c>
       <c r="B117" t="s">
         <v>130</v>
       </c>
@@ -6911,13 +7281,13 @@
         <v>479</v>
       </c>
       <c r="G117">
-        <v>0.0055</v>
+        <v>5.4999999999999997E-3</v>
       </c>
       <c r="H117">
-        <v>0.0101</v>
+        <v>1.01E-2</v>
       </c>
       <c r="I117">
-        <v>0.068</v>
+        <v>6.8000000000000005E-2</v>
       </c>
       <c r="J117" t="s">
         <v>481</v>
@@ -6929,7 +7299,7 @@
         <v>482</v>
       </c>
       <c r="M117">
-        <v>0.0056</v>
+        <v>5.5999999999999999E-3</v>
       </c>
       <c r="N117">
         <v>-0.1406</v>
@@ -6938,7 +7308,10 @@
         <v>0.2276</v>
       </c>
     </row>
-    <row r="118" spans="2:15">
+    <row r="118" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
+        <v>484</v>
+      </c>
       <c r="B118" t="s">
         <v>131</v>
       </c>
@@ -6955,34 +7328,37 @@
         <v>479</v>
       </c>
       <c r="G118">
-        <v>0.0133</v>
+        <v>1.3299999999999999E-2</v>
       </c>
       <c r="H118">
-        <v>0.0145</v>
+        <v>1.4500000000000001E-2</v>
       </c>
       <c r="I118">
-        <v>0.035</v>
+        <v>3.5000000000000003E-2</v>
       </c>
       <c r="J118" t="s">
         <v>481</v>
       </c>
       <c r="K118">
-        <v>0.0186</v>
+        <v>1.8599999999999998E-2</v>
       </c>
       <c r="L118" t="s">
         <v>483</v>
       </c>
       <c r="M118">
-        <v>0.022</v>
+        <v>2.1999999999999999E-2</v>
       </c>
       <c r="N118">
         <v>0.1951</v>
       </c>
       <c r="O118">
-        <v>0.0162</v>
-      </c>
-    </row>
-    <row r="119" spans="2:15">
+        <v>1.6199999999999999E-2</v>
+      </c>
+    </row>
+    <row r="119" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
+        <v>485</v>
+      </c>
       <c r="B119" t="s">
         <v>132</v>
       </c>
@@ -6999,34 +7375,37 @@
         <v>479</v>
       </c>
       <c r="G119">
-        <v>0.0161</v>
+        <v>1.61E-2</v>
       </c>
       <c r="H119">
-        <v>0.0164</v>
+        <v>1.6400000000000001E-2</v>
       </c>
       <c r="I119">
-        <v>0.028</v>
+        <v>2.8000000000000001E-2</v>
       </c>
       <c r="J119" t="s">
         <v>481</v>
       </c>
       <c r="K119">
-        <v>0.0262</v>
+        <v>2.6200000000000001E-2</v>
       </c>
       <c r="L119" t="s">
         <v>483</v>
       </c>
       <c r="M119">
-        <v>0.0026</v>
+        <v>2.5999999999999999E-3</v>
       </c>
       <c r="N119">
-        <v>0.0585</v>
+        <v>5.8500000000000003E-2</v>
       </c>
       <c r="O119">
         <v>0.4143</v>
       </c>
     </row>
-    <row r="120" spans="2:15">
+    <row r="120" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
+        <v>484</v>
+      </c>
       <c r="B120" t="s">
         <v>133</v>
       </c>
@@ -7043,10 +7422,10 @@
         <v>479</v>
       </c>
       <c r="G120">
-        <v>0.0193</v>
+        <v>1.9300000000000001E-2</v>
       </c>
       <c r="H120">
-        <v>0.0207</v>
+        <v>2.07E-2</v>
       </c>
       <c r="I120">
         <v>0.04</v>
@@ -7055,22 +7434,25 @@
         <v>481</v>
       </c>
       <c r="K120">
-        <v>0.0205</v>
+        <v>2.0500000000000001E-2</v>
       </c>
       <c r="L120" t="s">
         <v>483</v>
       </c>
       <c r="M120">
-        <v>0.0055</v>
+        <v>5.4999999999999997E-3</v>
       </c>
       <c r="N120">
-        <v>0.0682</v>
+        <v>6.8199999999999997E-2</v>
       </c>
       <c r="O120">
         <v>0.2316</v>
       </c>
     </row>
-    <row r="121" spans="2:15">
+    <row r="121" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
+        <v>485</v>
+      </c>
       <c r="B121" t="s">
         <v>134</v>
       </c>
@@ -7087,34 +7469,37 @@
         <v>479</v>
       </c>
       <c r="G121">
-        <v>0.0098</v>
+        <v>9.7999999999999997E-3</v>
       </c>
       <c r="H121">
-        <v>0.0145</v>
+        <v>1.4500000000000001E-2</v>
       </c>
       <c r="I121">
-        <v>0.018</v>
+        <v>1.7999999999999999E-2</v>
       </c>
       <c r="J121" t="s">
         <v>481</v>
       </c>
       <c r="K121">
-        <v>0.2434</v>
+        <v>0.24340000000000001</v>
       </c>
       <c r="L121" t="s">
         <v>482</v>
       </c>
       <c r="M121">
-        <v>0.0177</v>
+        <v>1.77E-2</v>
       </c>
       <c r="N121">
         <v>-0.1741</v>
       </c>
       <c r="O121">
-        <v>0.0315</v>
-      </c>
-    </row>
-    <row r="122" spans="2:15">
+        <v>3.15E-2</v>
+      </c>
+    </row>
+    <row r="122" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
+        <v>484</v>
+      </c>
       <c r="B122" t="s">
         <v>135</v>
       </c>
@@ -7131,13 +7516,13 @@
         <v>479</v>
       </c>
       <c r="G122">
-        <v>0.0065</v>
+        <v>6.4999999999999997E-3</v>
       </c>
       <c r="H122">
-        <v>0.0075</v>
+        <v>7.4999999999999997E-3</v>
       </c>
       <c r="I122">
-        <v>0.762</v>
+        <v>0.76200000000000001</v>
       </c>
       <c r="J122" t="s">
         <v>480</v>
@@ -7149,16 +7534,19 @@
         <v>482</v>
       </c>
       <c r="M122">
-        <v>0.0005</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="N122">
-        <v>-0.057</v>
+        <v>-5.7000000000000002E-2</v>
       </c>
       <c r="O122">
-        <v>0.7175</v>
-      </c>
-    </row>
-    <row r="123" spans="2:15">
+        <v>0.71750000000000003</v>
+      </c>
+    </row>
+    <row r="123" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A123" t="s">
+        <v>485</v>
+      </c>
       <c r="B123" t="s">
         <v>136</v>
       </c>
@@ -7175,34 +7563,37 @@
         <v>479</v>
       </c>
       <c r="G123">
-        <v>0.0156</v>
+        <v>1.5599999999999999E-2</v>
       </c>
       <c r="H123">
-        <v>0.0104</v>
+        <v>1.04E-2</v>
       </c>
       <c r="I123">
-        <v>0.431</v>
+        <v>0.43099999999999999</v>
       </c>
       <c r="J123" t="s">
         <v>480</v>
       </c>
       <c r="K123">
-        <v>0.0185</v>
+        <v>1.8499999999999999E-2</v>
       </c>
       <c r="L123" t="s">
         <v>483</v>
       </c>
       <c r="M123">
-        <v>0.0479</v>
+        <v>4.7899999999999998E-2</v>
       </c>
       <c r="N123">
-        <v>0.3981</v>
+        <v>0.39810000000000001</v>
       </c>
       <c r="O123">
-        <v>0.0004</v>
-      </c>
-    </row>
-    <row r="124" spans="2:15">
+        <v>4.0000000000000002E-4</v>
+      </c>
+    </row>
+    <row r="124" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A124" t="s">
+        <v>484</v>
+      </c>
       <c r="B124" t="s">
         <v>137</v>
       </c>
@@ -7219,34 +7610,37 @@
         <v>479</v>
       </c>
       <c r="G124">
-        <v>0.0167</v>
+        <v>1.67E-2</v>
       </c>
       <c r="H124">
-        <v>0.0119</v>
+        <v>1.1900000000000001E-2</v>
       </c>
       <c r="I124">
-        <v>0.648</v>
+        <v>0.64800000000000002</v>
       </c>
       <c r="J124" t="s">
         <v>480</v>
       </c>
       <c r="K124">
-        <v>0.0221</v>
+        <v>2.2100000000000002E-2</v>
       </c>
       <c r="L124" t="s">
         <v>483</v>
       </c>
       <c r="M124">
-        <v>0.0121</v>
+        <v>1.21E-2</v>
       </c>
       <c r="N124">
-        <v>0.1751</v>
+        <v>0.17510000000000001</v>
       </c>
       <c r="O124">
-        <v>0.0761</v>
-      </c>
-    </row>
-    <row r="125" spans="2:15">
+        <v>7.6100000000000001E-2</v>
+      </c>
+    </row>
+    <row r="125" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A125" t="s">
+        <v>485</v>
+      </c>
       <c r="B125" t="s">
         <v>138</v>
       </c>
@@ -7263,34 +7657,37 @@
         <v>479</v>
       </c>
       <c r="G125">
-        <v>0.0208</v>
+        <v>2.0799999999999999E-2</v>
       </c>
       <c r="H125">
-        <v>0.0149</v>
+        <v>1.49E-2</v>
       </c>
       <c r="I125">
-        <v>0.674</v>
+        <v>0.67400000000000004</v>
       </c>
       <c r="J125" t="s">
         <v>480</v>
       </c>
       <c r="K125">
-        <v>0.0188</v>
+        <v>1.8800000000000001E-2</v>
       </c>
       <c r="L125" t="s">
         <v>483</v>
       </c>
       <c r="M125">
-        <v>0.0121</v>
+        <v>1.21E-2</v>
       </c>
       <c r="N125">
         <v>0.1401</v>
       </c>
       <c r="O125">
-        <v>0.0757</v>
-      </c>
-    </row>
-    <row r="126" spans="2:15">
+        <v>7.5700000000000003E-2</v>
+      </c>
+    </row>
+    <row r="126" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
+        <v>484</v>
+      </c>
       <c r="B126" t="s">
         <v>139</v>
       </c>
@@ -7307,10 +7704,10 @@
         <v>479</v>
       </c>
       <c r="G126">
-        <v>0.0101</v>
+        <v>1.01E-2</v>
       </c>
       <c r="H126">
-        <v>0.0111</v>
+        <v>1.11E-2</v>
       </c>
       <c r="I126">
         <v>0.83</v>
@@ -7319,13 +7716,13 @@
         <v>480</v>
       </c>
       <c r="K126">
-        <v>0.2799</v>
+        <v>0.27989999999999998</v>
       </c>
       <c r="L126" t="s">
         <v>482</v>
       </c>
       <c r="M126">
-        <v>0.0074</v>
+        <v>7.4000000000000003E-3</v>
       </c>
       <c r="N126">
         <v>-0.1532</v>
@@ -7334,7 +7731,10 @@
         <v>0.191</v>
       </c>
     </row>
-    <row r="127" spans="2:15">
+    <row r="127" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A127" t="s">
+        <v>485</v>
+      </c>
       <c r="B127" t="s">
         <v>140</v>
       </c>
@@ -7351,34 +7751,37 @@
         <v>479</v>
       </c>
       <c r="G127">
-        <v>1.1604</v>
+        <v>1.1604000000000001</v>
       </c>
       <c r="H127">
-        <v>0.3302</v>
+        <v>0.33019999999999999</v>
       </c>
       <c r="I127">
-        <v>0.423</v>
+        <v>0.42299999999999999</v>
       </c>
       <c r="J127" t="s">
         <v>480</v>
       </c>
       <c r="K127">
-        <v>0.2653</v>
+        <v>0.26529999999999998</v>
       </c>
       <c r="L127" t="s">
         <v>482</v>
       </c>
       <c r="M127">
-        <v>0.0278</v>
+        <v>2.7799999999999998E-2</v>
       </c>
       <c r="N127">
-        <v>0.009599999999999999</v>
+        <v>9.5999999999999992E-3</v>
       </c>
       <c r="O127">
-        <v>0.0068</v>
-      </c>
-    </row>
-    <row r="128" spans="2:15">
+        <v>6.7999999999999996E-3</v>
+      </c>
+    </row>
+    <row r="128" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
+        <v>484</v>
+      </c>
       <c r="B128" t="s">
         <v>141</v>
       </c>
@@ -7398,7 +7801,7 @@
         <v>1.1329</v>
       </c>
       <c r="H128">
-        <v>0.198</v>
+        <v>0.19800000000000001</v>
       </c>
       <c r="I128">
         <v>0.83</v>
@@ -7413,16 +7816,19 @@
         <v>482</v>
       </c>
       <c r="M128">
-        <v>0.0026</v>
+        <v>2.5999999999999999E-3</v>
       </c>
       <c r="N128">
-        <v>0.0049</v>
+        <v>4.8999999999999998E-3</v>
       </c>
       <c r="O128">
-        <v>0.4125</v>
-      </c>
-    </row>
-    <row r="129" spans="2:15">
+        <v>0.41249999999999998</v>
+      </c>
+    </row>
+    <row r="129" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
+        <v>485</v>
+      </c>
       <c r="B129" t="s">
         <v>142</v>
       </c>
@@ -7439,13 +7845,13 @@
         <v>479</v>
       </c>
       <c r="G129">
-        <v>1.0428</v>
+        <v>1.0427999999999999</v>
       </c>
       <c r="H129">
-        <v>0.1969</v>
+        <v>0.19689999999999999</v>
       </c>
       <c r="I129">
-        <v>0.014</v>
+        <v>1.4E-2</v>
       </c>
       <c r="J129" t="s">
         <v>481</v>
@@ -7457,16 +7863,19 @@
         <v>482</v>
       </c>
       <c r="M129">
-        <v>0.0012</v>
+        <v>1.1999999999999999E-3</v>
       </c>
       <c r="N129">
-        <v>0.0034</v>
+        <v>3.3999999999999998E-3</v>
       </c>
       <c r="O129">
-        <v>0.5732</v>
-      </c>
-    </row>
-    <row r="130" spans="2:15">
+        <v>0.57320000000000004</v>
+      </c>
+    </row>
+    <row r="130" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
+        <v>484</v>
+      </c>
       <c r="B130" t="s">
         <v>143</v>
       </c>
@@ -7483,13 +7892,13 @@
         <v>479</v>
       </c>
       <c r="G130">
-        <v>0.9887</v>
+        <v>0.98870000000000002</v>
       </c>
       <c r="H130">
-        <v>0.3758</v>
+        <v>0.37580000000000002</v>
       </c>
       <c r="I130">
-        <v>0.235</v>
+        <v>0.23499999999999999</v>
       </c>
       <c r="J130" t="s">
         <v>480</v>
@@ -7501,16 +7910,19 @@
         <v>482</v>
       </c>
       <c r="M130">
-        <v>0.0784</v>
+        <v>7.8399999999999997E-2</v>
       </c>
       <c r="N130">
-        <v>0.0142</v>
+        <v>1.4200000000000001E-2</v>
       </c>
       <c r="O130">
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="2:15">
+    <row r="131" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A131" t="s">
+        <v>485</v>
+      </c>
       <c r="B131" t="s">
         <v>144</v>
       </c>
@@ -7527,10 +7939,10 @@
         <v>479</v>
       </c>
       <c r="G131">
-        <v>0.9308999999999999</v>
+        <v>0.93089999999999995</v>
       </c>
       <c r="H131">
-        <v>0.2216</v>
+        <v>0.22159999999999999</v>
       </c>
       <c r="I131">
         <v>0.752</v>
@@ -7539,7 +7951,7 @@
         <v>480</v>
       </c>
       <c r="K131">
-        <v>0.297</v>
+        <v>0.29699999999999999</v>
       </c>
       <c r="L131" t="s">
         <v>482</v>
@@ -7548,13 +7960,16 @@
         <v>0.1153</v>
       </c>
       <c r="N131">
-        <v>0.0291</v>
+        <v>2.9100000000000001E-2</v>
       </c>
       <c r="O131">
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="2:15">
+    <row r="132" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A132" t="s">
+        <v>484</v>
+      </c>
       <c r="B132" t="s">
         <v>145</v>
       </c>
@@ -7571,19 +7986,19 @@
         <v>479</v>
       </c>
       <c r="G132">
-        <v>1.1588</v>
+        <v>1.1588000000000001</v>
       </c>
       <c r="H132">
         <v>0.1862</v>
       </c>
       <c r="I132">
-        <v>0.553</v>
+        <v>0.55300000000000005</v>
       </c>
       <c r="J132" t="s">
         <v>480</v>
       </c>
       <c r="K132">
-        <v>0.2408</v>
+        <v>0.24079999999999999</v>
       </c>
       <c r="L132" t="s">
         <v>482</v>
@@ -7592,13 +8007,16 @@
         <v>0.1704</v>
       </c>
       <c r="N132">
-        <v>0.0421</v>
+        <v>4.2099999999999999E-2</v>
       </c>
       <c r="O132">
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="2:15">
+    <row r="133" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
+        <v>485</v>
+      </c>
       <c r="B133" t="s">
         <v>146</v>
       </c>
@@ -7615,13 +8033,13 @@
         <v>479</v>
       </c>
       <c r="G133">
-        <v>1.1179</v>
+        <v>1.1178999999999999</v>
       </c>
       <c r="H133">
-        <v>0.1034</v>
+        <v>0.10340000000000001</v>
       </c>
       <c r="I133">
-        <v>0.859</v>
+        <v>0.85899999999999999</v>
       </c>
       <c r="J133" t="s">
         <v>480</v>
@@ -7633,16 +8051,19 @@
         <v>482</v>
       </c>
       <c r="M133">
-        <v>0.0362</v>
+        <v>3.6200000000000003E-2</v>
       </c>
       <c r="N133">
-        <v>0.0349</v>
+        <v>3.49E-2</v>
       </c>
       <c r="O133">
-        <v>0.002</v>
-      </c>
-    </row>
-    <row r="134" spans="2:15">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="134" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
+        <v>484</v>
+      </c>
       <c r="B134" t="s">
         <v>147</v>
       </c>
@@ -7659,7 +8080,7 @@
         <v>479</v>
       </c>
       <c r="G134">
-        <v>1.0153</v>
+        <v>1.0153000000000001</v>
       </c>
       <c r="H134">
         <v>0.1067</v>
@@ -7671,22 +8092,25 @@
         <v>481</v>
       </c>
       <c r="K134">
-        <v>0.2207</v>
+        <v>0.22070000000000001</v>
       </c>
       <c r="L134" t="s">
         <v>482</v>
       </c>
       <c r="M134">
-        <v>0.0827</v>
+        <v>8.2699999999999996E-2</v>
       </c>
       <c r="N134">
-        <v>0.0512</v>
+        <v>5.1200000000000002E-2</v>
       </c>
       <c r="O134">
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="2:15">
+    <row r="135" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
+        <v>485</v>
+      </c>
       <c r="B135" t="s">
         <v>148</v>
       </c>
@@ -7703,34 +8127,37 @@
         <v>479</v>
       </c>
       <c r="G135">
-        <v>0.9903</v>
+        <v>0.99029999999999996</v>
       </c>
       <c r="H135">
-        <v>0.2184</v>
+        <v>0.21840000000000001</v>
       </c>
       <c r="I135">
-        <v>0.459</v>
+        <v>0.45900000000000002</v>
       </c>
       <c r="J135" t="s">
         <v>480</v>
       </c>
       <c r="K135">
-        <v>0.2578</v>
+        <v>0.25779999999999997</v>
       </c>
       <c r="L135" t="s">
         <v>482</v>
       </c>
       <c r="M135">
-        <v>0.1314</v>
+        <v>0.13139999999999999</v>
       </c>
       <c r="N135">
-        <v>0.0316</v>
+        <v>3.1600000000000003E-2</v>
       </c>
       <c r="O135">
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="2:15">
+    <row r="136" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A136" t="s">
+        <v>484</v>
+      </c>
       <c r="B136" t="s">
         <v>149</v>
       </c>
@@ -7747,34 +8174,37 @@
         <v>479</v>
       </c>
       <c r="G136">
-        <v>0.9177999999999999</v>
+        <v>0.91779999999999995</v>
       </c>
       <c r="H136">
-        <v>0.1422</v>
+        <v>0.14219999999999999</v>
       </c>
       <c r="I136">
-        <v>0.463</v>
+        <v>0.46300000000000002</v>
       </c>
       <c r="J136" t="s">
         <v>480</v>
       </c>
       <c r="K136">
-        <v>0.2592</v>
+        <v>0.25919999999999999</v>
       </c>
       <c r="L136" t="s">
         <v>482</v>
       </c>
       <c r="M136">
-        <v>0.1233</v>
+        <v>0.12330000000000001</v>
       </c>
       <c r="N136">
-        <v>0.047</v>
+        <v>4.7E-2</v>
       </c>
       <c r="O136">
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="2:15">
+    <row r="137" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A137" t="s">
+        <v>485</v>
+      </c>
       <c r="B137" t="s">
         <v>150</v>
       </c>
@@ -7791,10 +8221,10 @@
         <v>479</v>
       </c>
       <c r="G137">
-        <v>0.6467000000000001</v>
+        <v>0.64670000000000005</v>
       </c>
       <c r="H137">
-        <v>0.2783</v>
+        <v>0.27829999999999999</v>
       </c>
       <c r="I137">
         <v>0.193</v>
@@ -7803,22 +8233,25 @@
         <v>480</v>
       </c>
       <c r="K137">
-        <v>0.0018</v>
+        <v>1.8E-3</v>
       </c>
       <c r="L137" t="s">
         <v>483</v>
       </c>
       <c r="M137">
-        <v>0.1889</v>
+        <v>0.18890000000000001</v>
       </c>
       <c r="N137">
-        <v>0.0297</v>
+        <v>2.9700000000000001E-2</v>
       </c>
       <c r="O137">
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="2:15">
+    <row r="138" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A138" t="s">
+        <v>484</v>
+      </c>
       <c r="B138" t="s">
         <v>151</v>
       </c>
@@ -7838,16 +8271,16 @@
         <v>0.31</v>
       </c>
       <c r="H138">
-        <v>0.2126</v>
+        <v>0.21260000000000001</v>
       </c>
       <c r="I138">
-        <v>0.361</v>
+        <v>0.36099999999999999</v>
       </c>
       <c r="J138" t="s">
         <v>480</v>
       </c>
       <c r="K138">
-        <v>0.2328</v>
+        <v>0.23280000000000001</v>
       </c>
       <c r="L138" t="s">
         <v>482</v>
@@ -7856,13 +8289,16 @@
         <v>0</v>
       </c>
       <c r="N138">
-        <v>-0.0002</v>
+        <v>-2.0000000000000001E-4</v>
       </c>
       <c r="O138">
-        <v>0.9754</v>
-      </c>
-    </row>
-    <row r="139" spans="2:15">
+        <v>0.97540000000000004</v>
+      </c>
+    </row>
+    <row r="139" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A139" t="s">
+        <v>485</v>
+      </c>
       <c r="B139" t="s">
         <v>152</v>
       </c>
@@ -7879,34 +8315,37 @@
         <v>479</v>
       </c>
       <c r="G139">
-        <v>0.2692</v>
+        <v>0.26919999999999999</v>
       </c>
       <c r="H139">
         <v>0.1951</v>
       </c>
       <c r="I139">
-        <v>0.148</v>
+        <v>0.14799999999999999</v>
       </c>
       <c r="J139" t="s">
         <v>481</v>
       </c>
       <c r="K139">
-        <v>0.0186</v>
+        <v>1.8599999999999998E-2</v>
       </c>
       <c r="L139" t="s">
         <v>483</v>
       </c>
       <c r="M139">
-        <v>0.0298</v>
+        <v>2.98E-2</v>
       </c>
       <c r="N139">
-        <v>0.0168</v>
+        <v>1.6799999999999999E-2</v>
       </c>
       <c r="O139">
-        <v>0.0051</v>
-      </c>
-    </row>
-    <row r="140" spans="2:15">
+        <v>5.1000000000000004E-3</v>
+      </c>
+    </row>
+    <row r="140" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A140" t="s">
+        <v>484</v>
+      </c>
       <c r="B140" t="s">
         <v>153</v>
       </c>
@@ -7929,28 +8368,31 @@
         <v>0.309</v>
       </c>
       <c r="I140">
-        <v>0.041</v>
+        <v>4.1000000000000002E-2</v>
       </c>
       <c r="J140" t="s">
         <v>481</v>
       </c>
       <c r="K140">
-        <v>0.0834</v>
+        <v>8.3400000000000002E-2</v>
       </c>
       <c r="L140" t="s">
         <v>483</v>
       </c>
       <c r="M140">
-        <v>0.0606</v>
+        <v>6.0600000000000001E-2</v>
       </c>
       <c r="N140">
-        <v>0.0151</v>
+        <v>1.5100000000000001E-2</v>
       </c>
       <c r="O140">
-        <v>0.0001</v>
-      </c>
-    </row>
-    <row r="141" spans="2:15">
+        <v>1E-4</v>
+      </c>
+    </row>
+    <row r="141" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A141" t="s">
+        <v>485</v>
+      </c>
       <c r="B141" t="s">
         <v>154</v>
       </c>
@@ -7967,10 +8409,10 @@
         <v>479</v>
       </c>
       <c r="G141">
-        <v>0.3053</v>
+        <v>0.30530000000000002</v>
       </c>
       <c r="H141">
-        <v>0.2206</v>
+        <v>0.22059999999999999</v>
       </c>
       <c r="I141">
         <v>0.08</v>
@@ -7985,16 +8427,19 @@
         <v>482</v>
       </c>
       <c r="M141">
-        <v>0.0232</v>
+        <v>2.3199999999999998E-2</v>
       </c>
       <c r="N141">
-        <v>0.0131</v>
+        <v>1.3100000000000001E-2</v>
       </c>
       <c r="O141">
-        <v>0.0137</v>
-      </c>
-    </row>
-    <row r="142" spans="2:15">
+        <v>1.37E-2</v>
+      </c>
+    </row>
+    <row r="142" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A142" t="s">
+        <v>484</v>
+      </c>
       <c r="B142" t="s">
         <v>155</v>
       </c>
@@ -8011,34 +8456,37 @@
         <v>479</v>
       </c>
       <c r="G142">
-        <v>0.7526</v>
+        <v>0.75260000000000005</v>
       </c>
       <c r="H142">
-        <v>0.2252</v>
+        <v>0.22520000000000001</v>
       </c>
       <c r="I142">
-        <v>0.427</v>
+        <v>0.42699999999999999</v>
       </c>
       <c r="J142" t="s">
         <v>480</v>
       </c>
       <c r="K142">
-        <v>0.1437</v>
+        <v>0.14369999999999999</v>
       </c>
       <c r="L142" t="s">
         <v>483</v>
       </c>
       <c r="M142">
-        <v>0.07770000000000001</v>
+        <v>7.7700000000000005E-2</v>
       </c>
       <c r="N142">
-        <v>0.0235</v>
+        <v>2.35E-2</v>
       </c>
       <c r="O142">
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="2:15">
+    <row r="143" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A143" t="s">
+        <v>485</v>
+      </c>
       <c r="B143" t="s">
         <v>156</v>
       </c>
@@ -8055,34 +8503,37 @@
         <v>479</v>
       </c>
       <c r="G143">
-        <v>0.3759</v>
+        <v>0.37590000000000001</v>
       </c>
       <c r="H143">
-        <v>0.1949</v>
+        <v>0.19489999999999999</v>
       </c>
       <c r="I143">
-        <v>0.644</v>
+        <v>0.64400000000000002</v>
       </c>
       <c r="J143" t="s">
         <v>480</v>
       </c>
       <c r="K143">
-        <v>0.234</v>
+        <v>0.23400000000000001</v>
       </c>
       <c r="L143" t="s">
         <v>482</v>
       </c>
       <c r="M143">
-        <v>0.0001</v>
+        <v>1E-4</v>
       </c>
       <c r="N143">
-        <v>-0.0012</v>
+        <v>-1.1999999999999999E-3</v>
       </c>
       <c r="O143">
-        <v>0.846</v>
-      </c>
-    </row>
-    <row r="144" spans="2:15">
+        <v>0.84599999999999997</v>
+      </c>
+    </row>
+    <row r="144" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A144" t="s">
+        <v>484</v>
+      </c>
       <c r="B144" t="s">
         <v>157</v>
       </c>
@@ -8099,34 +8550,37 @@
         <v>479</v>
       </c>
       <c r="G144">
-        <v>0.3321</v>
+        <v>0.33210000000000001</v>
       </c>
       <c r="H144">
-        <v>0.1917</v>
+        <v>0.19170000000000001</v>
       </c>
       <c r="I144">
-        <v>0.605</v>
+        <v>0.60499999999999998</v>
       </c>
       <c r="J144" t="s">
         <v>480</v>
       </c>
       <c r="K144">
-        <v>0.0196</v>
+        <v>1.9599999999999999E-2</v>
       </c>
       <c r="L144" t="s">
         <v>483</v>
       </c>
       <c r="M144">
-        <v>0.0149</v>
+        <v>1.49E-2</v>
       </c>
       <c r="N144">
-        <v>0.0121</v>
+        <v>1.21E-2</v>
       </c>
       <c r="O144">
-        <v>0.0482</v>
-      </c>
-    </row>
-    <row r="145" spans="2:15">
+        <v>4.82E-2</v>
+      </c>
+    </row>
+    <row r="145" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A145" t="s">
+        <v>485</v>
+      </c>
       <c r="B145" t="s">
         <v>158</v>
       </c>
@@ -8143,13 +8597,13 @@
         <v>479</v>
       </c>
       <c r="G145">
-        <v>0.5953000000000001</v>
+        <v>0.59530000000000005</v>
       </c>
       <c r="H145">
         <v>0.2626</v>
       </c>
       <c r="I145">
-        <v>0.589</v>
+        <v>0.58899999999999997</v>
       </c>
       <c r="J145" t="s">
         <v>480</v>
@@ -8161,16 +8615,19 @@
         <v>482</v>
       </c>
       <c r="M145">
-        <v>0.0149</v>
+        <v>1.49E-2</v>
       </c>
       <c r="N145">
-        <v>0.008800000000000001</v>
+        <v>8.8000000000000005E-3</v>
       </c>
       <c r="O145">
-        <v>0.0492</v>
-      </c>
-    </row>
-    <row r="146" spans="2:15">
+        <v>4.9200000000000001E-2</v>
+      </c>
+    </row>
+    <row r="146" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A146" t="s">
+        <v>484</v>
+      </c>
       <c r="B146" t="s">
         <v>159</v>
       </c>
@@ -8193,28 +8650,31 @@
         <v>0.1774</v>
       </c>
       <c r="I146">
-        <v>0.524</v>
+        <v>0.52400000000000002</v>
       </c>
       <c r="J146" t="s">
         <v>480</v>
       </c>
       <c r="K146">
-        <v>0.2578</v>
+        <v>0.25779999999999997</v>
       </c>
       <c r="L146" t="s">
         <v>482</v>
       </c>
       <c r="M146">
-        <v>0.0128</v>
+        <v>1.2800000000000001E-2</v>
       </c>
       <c r="N146">
-        <v>0.0121</v>
+        <v>1.21E-2</v>
       </c>
       <c r="O146">
-        <v>0.0683</v>
-      </c>
-    </row>
-    <row r="147" spans="2:15">
+        <v>6.83E-2</v>
+      </c>
+    </row>
+    <row r="147" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A147" t="s">
+        <v>485</v>
+      </c>
       <c r="B147" t="s">
         <v>160</v>
       </c>
@@ -8228,34 +8688,37 @@
         <v>479</v>
       </c>
       <c r="G147">
-        <v>0.0005</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="H147">
-        <v>0.0095</v>
+        <v>9.4999999999999998E-3</v>
       </c>
       <c r="I147">
-        <v>0.015</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="J147" t="s">
         <v>481</v>
       </c>
       <c r="K147">
-        <v>0.0203</v>
+        <v>2.0299999999999999E-2</v>
       </c>
       <c r="L147" t="s">
         <v>483</v>
       </c>
       <c r="M147">
-        <v>0.5593</v>
+        <v>0.55930000000000002</v>
       </c>
       <c r="N147">
-        <v>1.5128</v>
+        <v>1.5127999999999999</v>
       </c>
       <c r="O147">
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="2:15">
+    <row r="148" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A148" t="s">
+        <v>484</v>
+      </c>
       <c r="B148" t="s">
         <v>161</v>
       </c>
@@ -8269,25 +8732,25 @@
         <v>479</v>
       </c>
       <c r="G148">
-        <v>0.0007</v>
+        <v>6.9999999999999999E-4</v>
       </c>
       <c r="H148">
-        <v>0.009599999999999999</v>
+        <v>9.5999999999999992E-3</v>
       </c>
       <c r="I148">
-        <v>0.003</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="J148" t="s">
         <v>481</v>
       </c>
       <c r="K148">
-        <v>0.041</v>
+        <v>4.1000000000000002E-2</v>
       </c>
       <c r="L148" t="s">
         <v>483</v>
       </c>
       <c r="M148">
-        <v>0.4851</v>
+        <v>0.48509999999999998</v>
       </c>
       <c r="N148">
         <v>1.3892</v>
@@ -8296,7 +8759,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="2:15">
+    <row r="149" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A149" t="s">
+        <v>485</v>
+      </c>
       <c r="B149" t="s">
         <v>162</v>
       </c>
@@ -8310,34 +8776,37 @@
         <v>479</v>
       </c>
       <c r="G149">
-        <v>-0.0008</v>
+        <v>-8.0000000000000004E-4</v>
       </c>
       <c r="H149">
-        <v>0.0102</v>
+        <v>1.0200000000000001E-2</v>
       </c>
       <c r="I149">
-        <v>0.035</v>
+        <v>3.5000000000000003E-2</v>
       </c>
       <c r="J149" t="s">
         <v>481</v>
       </c>
       <c r="K149">
-        <v>0.0862</v>
+        <v>8.6199999999999999E-2</v>
       </c>
       <c r="L149" t="s">
         <v>483</v>
       </c>
       <c r="M149">
-        <v>0.3646</v>
+        <v>0.36459999999999998</v>
       </c>
       <c r="N149">
-        <v>-1.1317</v>
+        <v>-1.1316999999999999</v>
       </c>
       <c r="O149">
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="2:15">
+    <row r="150" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A150" t="s">
+        <v>484</v>
+      </c>
       <c r="B150" t="s">
         <v>163</v>
       </c>
@@ -8351,25 +8820,25 @@
         <v>479</v>
       </c>
       <c r="G150">
-        <v>-0.001</v>
+        <v>-1E-3</v>
       </c>
       <c r="H150">
-        <v>0.0101</v>
+        <v>1.01E-2</v>
       </c>
       <c r="I150">
-        <v>0.056</v>
+        <v>5.6000000000000001E-2</v>
       </c>
       <c r="J150" t="s">
         <v>481</v>
       </c>
       <c r="K150">
-        <v>0.0222</v>
+        <v>2.2200000000000001E-2</v>
       </c>
       <c r="L150" t="s">
         <v>483</v>
       </c>
       <c r="M150">
-        <v>0.4197</v>
+        <v>0.41970000000000002</v>
       </c>
       <c r="N150">
         <v>-1.2323</v>
@@ -8378,7 +8847,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="2:15">
+    <row r="151" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A151" t="s">
+        <v>485</v>
+      </c>
       <c r="B151" t="s">
         <v>164</v>
       </c>
@@ -8392,19 +8864,19 @@
         <v>479</v>
       </c>
       <c r="G151">
-        <v>-0.0001</v>
+        <v>-1E-4</v>
       </c>
       <c r="H151">
-        <v>0.0107</v>
+        <v>1.0699999999999999E-2</v>
       </c>
       <c r="I151">
-        <v>0.047</v>
+        <v>4.7E-2</v>
       </c>
       <c r="J151" t="s">
         <v>481</v>
       </c>
       <c r="K151">
-        <v>0.0044</v>
+        <v>4.4000000000000003E-3</v>
       </c>
       <c r="L151" t="s">
         <v>483</v>
@@ -8413,13 +8885,16 @@
         <v>0.3271</v>
       </c>
       <c r="N151">
-        <v>1.0191</v>
+        <v>1.0190999999999999</v>
       </c>
       <c r="O151">
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="2:15">
+    <row r="152" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A152" t="s">
+        <v>484</v>
+      </c>
       <c r="B152" t="s">
         <v>165</v>
       </c>
@@ -8433,25 +8908,25 @@
         <v>479</v>
       </c>
       <c r="G152">
-        <v>0.0007</v>
+        <v>6.9999999999999999E-4</v>
       </c>
       <c r="H152">
-        <v>0.0116</v>
+        <v>1.1599999999999999E-2</v>
       </c>
       <c r="I152">
-        <v>0.017</v>
+        <v>1.7000000000000001E-2</v>
       </c>
       <c r="J152" t="s">
         <v>481</v>
       </c>
       <c r="K152">
-        <v>0.0034</v>
+        <v>3.3999999999999998E-3</v>
       </c>
       <c r="L152" t="s">
         <v>483</v>
       </c>
       <c r="M152">
-        <v>0.3482</v>
+        <v>0.34820000000000001</v>
       </c>
       <c r="N152">
         <v>0.97</v>
@@ -8460,7 +8935,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="2:15">
+    <row r="153" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A153" t="s">
+        <v>485</v>
+      </c>
       <c r="B153" t="s">
         <v>166</v>
       </c>
@@ -8480,10 +8958,10 @@
         <v>0.38</v>
       </c>
       <c r="H153">
-        <v>0.0428</v>
+        <v>4.2799999999999998E-2</v>
       </c>
       <c r="I153">
-        <v>0.462</v>
+        <v>0.46200000000000002</v>
       </c>
       <c r="J153" t="s">
         <v>480</v>
@@ -8495,7 +8973,7 @@
         <v>482</v>
       </c>
       <c r="M153">
-        <v>0.08890000000000001</v>
+        <v>8.8900000000000007E-2</v>
       </c>
       <c r="N153">
         <v>0.1323</v>
@@ -8504,7 +8982,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="2:15">
+    <row r="154" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A154" t="s">
+        <v>484</v>
+      </c>
       <c r="B154" t="s">
         <v>167</v>
       </c>
@@ -8521,10 +9002,10 @@
         <v>479</v>
       </c>
       <c r="G154">
-        <v>0.2322</v>
+        <v>0.23219999999999999</v>
       </c>
       <c r="H154">
-        <v>0.046</v>
+        <v>4.5999999999999999E-2</v>
       </c>
       <c r="I154">
         <v>0.91</v>
@@ -8533,7 +9014,7 @@
         <v>480</v>
       </c>
       <c r="K154">
-        <v>0.0121</v>
+        <v>1.21E-2</v>
       </c>
       <c r="L154" t="s">
         <v>483</v>
@@ -8548,7 +9029,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="2:15">
+    <row r="155" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A155" t="s">
+        <v>485</v>
+      </c>
       <c r="B155" t="s">
         <v>168</v>
       </c>
@@ -8568,31 +9052,34 @@
         <v>0.1769</v>
       </c>
       <c r="H155">
-        <v>0.018</v>
+        <v>1.7999999999999999E-2</v>
       </c>
       <c r="I155">
-        <v>0.035</v>
+        <v>3.5000000000000003E-2</v>
       </c>
       <c r="J155" t="s">
         <v>481</v>
       </c>
       <c r="K155">
-        <v>0.2153</v>
+        <v>0.21529999999999999</v>
       </c>
       <c r="L155" t="s">
         <v>482</v>
       </c>
       <c r="M155">
-        <v>0.0004</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="N155">
-        <v>0.0219</v>
+        <v>2.1899999999999999E-2</v>
       </c>
       <c r="O155">
-        <v>0.7386</v>
-      </c>
-    </row>
-    <row r="156" spans="2:15">
+        <v>0.73860000000000003</v>
+      </c>
+    </row>
+    <row r="156" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A156" t="s">
+        <v>484</v>
+      </c>
       <c r="B156" t="s">
         <v>169</v>
       </c>
@@ -8609,13 +9096,13 @@
         <v>479</v>
       </c>
       <c r="G156">
-        <v>0.1365</v>
+        <v>0.13650000000000001</v>
       </c>
       <c r="H156">
-        <v>0.0137</v>
+        <v>1.37E-2</v>
       </c>
       <c r="I156">
-        <v>0.029</v>
+        <v>2.9000000000000001E-2</v>
       </c>
       <c r="J156" t="s">
         <v>481</v>
@@ -8627,16 +9114,19 @@
         <v>482</v>
       </c>
       <c r="M156">
-        <v>0.0424</v>
+        <v>4.24E-2</v>
       </c>
       <c r="N156">
-        <v>0.2862</v>
+        <v>0.28620000000000001</v>
       </c>
       <c r="O156">
-        <v>0.0008</v>
-      </c>
-    </row>
-    <row r="157" spans="2:15">
+        <v>8.0000000000000004E-4</v>
+      </c>
+    </row>
+    <row r="157" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A157" t="s">
+        <v>485</v>
+      </c>
       <c r="B157" t="s">
         <v>170</v>
       </c>
@@ -8653,10 +9143,10 @@
         <v>479</v>
       </c>
       <c r="G157">
-        <v>0.6868</v>
+        <v>0.68679999999999997</v>
       </c>
       <c r="H157">
-        <v>0.0469</v>
+        <v>4.6899999999999997E-2</v>
       </c>
       <c r="I157">
         <v>0.5</v>
@@ -8665,22 +9155,25 @@
         <v>480</v>
       </c>
       <c r="K157">
-        <v>0.0169</v>
+        <v>1.6899999999999998E-2</v>
       </c>
       <c r="L157" t="s">
         <v>483</v>
       </c>
       <c r="M157">
-        <v>0.0053</v>
+        <v>5.3E-3</v>
       </c>
       <c r="N157">
-        <v>-0.0294</v>
+        <v>-2.9399999999999999E-2</v>
       </c>
       <c r="O157">
-        <v>0.2415</v>
-      </c>
-    </row>
-    <row r="158" spans="2:15">
+        <v>0.24149999999999999</v>
+      </c>
+    </row>
+    <row r="158" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A158" t="s">
+        <v>484</v>
+      </c>
       <c r="B158" t="s">
         <v>171</v>
       </c>
@@ -8697,34 +9190,37 @@
         <v>479</v>
       </c>
       <c r="G158">
-        <v>0.6103</v>
+        <v>0.61029999999999995</v>
       </c>
       <c r="H158">
-        <v>0.0472</v>
+        <v>4.7199999999999999E-2</v>
       </c>
       <c r="I158">
-        <v>0.5620000000000001</v>
+        <v>0.56200000000000006</v>
       </c>
       <c r="J158" t="s">
         <v>480</v>
       </c>
       <c r="K158">
-        <v>0.0191</v>
+        <v>1.9099999999999999E-2</v>
       </c>
       <c r="L158" t="s">
         <v>483</v>
       </c>
       <c r="M158">
-        <v>0.0132</v>
+        <v>1.32E-2</v>
       </c>
       <c r="N158">
-        <v>-0.0462</v>
+        <v>-4.6199999999999998E-2</v>
       </c>
       <c r="O158">
-        <v>0.06370000000000001</v>
-      </c>
-    </row>
-    <row r="159" spans="2:15">
+        <v>6.3700000000000007E-2</v>
+      </c>
+    </row>
+    <row r="159" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A159" t="s">
+        <v>485</v>
+      </c>
       <c r="B159" t="s">
         <v>172</v>
       </c>
@@ -8741,13 +9237,13 @@
         <v>479</v>
       </c>
       <c r="G159">
-        <v>0.5169</v>
+        <v>0.51690000000000003</v>
       </c>
       <c r="H159">
-        <v>0.0268</v>
+        <v>2.6800000000000001E-2</v>
       </c>
       <c r="I159">
-        <v>0.167</v>
+        <v>0.16700000000000001</v>
       </c>
       <c r="J159" t="s">
         <v>480</v>
@@ -8759,16 +9255,19 @@
         <v>483</v>
       </c>
       <c r="M159">
-        <v>0.096</v>
+        <v>9.6000000000000002E-2</v>
       </c>
       <c r="N159">
-        <v>0.2197</v>
+        <v>0.21970000000000001</v>
       </c>
       <c r="O159">
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="2:15">
+    <row r="160" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A160" t="s">
+        <v>484</v>
+      </c>
       <c r="B160" t="s">
         <v>173</v>
       </c>
@@ -8785,34 +9284,37 @@
         <v>479</v>
       </c>
       <c r="G160">
-        <v>0.7774</v>
+        <v>0.77739999999999998</v>
       </c>
       <c r="H160">
-        <v>0.0391</v>
+        <v>3.9100000000000003E-2</v>
       </c>
       <c r="I160">
-        <v>0.517</v>
+        <v>0.51700000000000002</v>
       </c>
       <c r="J160" t="s">
         <v>480</v>
       </c>
       <c r="K160">
-        <v>0.0114</v>
+        <v>1.14E-2</v>
       </c>
       <c r="L160" t="s">
         <v>483</v>
       </c>
       <c r="M160">
-        <v>0.1553</v>
+        <v>0.15529999999999999</v>
       </c>
       <c r="N160">
-        <v>0.1914</v>
+        <v>0.19139999999999999</v>
       </c>
       <c r="O160">
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="2:15">
+    <row r="161" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A161" t="s">
+        <v>485</v>
+      </c>
       <c r="B161" t="s">
         <v>174</v>
       </c>
@@ -8829,34 +9331,37 @@
         <v>479</v>
       </c>
       <c r="G161">
-        <v>-0.0146</v>
+        <v>-1.46E-2</v>
       </c>
       <c r="H161">
-        <v>0.0196</v>
+        <v>1.9599999999999999E-2</v>
       </c>
       <c r="I161">
-        <v>0.082</v>
+        <v>8.2000000000000003E-2</v>
       </c>
       <c r="J161" t="s">
         <v>481</v>
       </c>
       <c r="K161">
-        <v>0.0279</v>
+        <v>2.7900000000000001E-2</v>
       </c>
       <c r="L161" t="s">
         <v>483</v>
       </c>
       <c r="M161">
-        <v>0.2836</v>
+        <v>0.28360000000000002</v>
       </c>
       <c r="N161">
-        <v>-0.5155</v>
+        <v>-0.51549999999999996</v>
       </c>
       <c r="O161">
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="2:15">
+    <row r="162" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A162" t="s">
+        <v>484</v>
+      </c>
       <c r="B162" t="s">
         <v>175</v>
       </c>
@@ -8873,25 +9378,25 @@
         <v>479</v>
       </c>
       <c r="G162">
-        <v>0.0208</v>
+        <v>2.0799999999999999E-2</v>
       </c>
       <c r="H162">
-        <v>0.0536</v>
+        <v>5.3600000000000002E-2</v>
       </c>
       <c r="I162">
-        <v>0.001</v>
+        <v>1E-3</v>
       </c>
       <c r="J162" t="s">
         <v>481</v>
       </c>
       <c r="K162">
-        <v>0.0475</v>
+        <v>4.7500000000000001E-2</v>
       </c>
       <c r="L162" t="s">
         <v>483</v>
       </c>
       <c r="M162">
-        <v>0.09229999999999999</v>
+        <v>9.2299999999999993E-2</v>
       </c>
       <c r="N162">
         <v>-0.1077</v>
@@ -8900,7 +9405,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="2:15">
+    <row r="163" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A163" t="s">
+        <v>485</v>
+      </c>
       <c r="B163" t="s">
         <v>176</v>
       </c>
@@ -8917,34 +9425,37 @@
         <v>479</v>
       </c>
       <c r="G163">
-        <v>0.0203</v>
+        <v>2.0299999999999999E-2</v>
       </c>
       <c r="H163">
-        <v>0.0215</v>
+        <v>2.1499999999999998E-2</v>
       </c>
       <c r="I163">
-        <v>0.023</v>
+        <v>2.3E-2</v>
       </c>
       <c r="J163" t="s">
         <v>481</v>
       </c>
       <c r="K163">
-        <v>0.3385</v>
+        <v>0.33850000000000002</v>
       </c>
       <c r="L163" t="s">
         <v>482</v>
       </c>
       <c r="M163">
-        <v>0.3505</v>
+        <v>0.35049999999999998</v>
       </c>
       <c r="N163">
-        <v>-0.5237000000000001</v>
+        <v>-0.52370000000000005</v>
       </c>
       <c r="O163">
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="2:15">
+    <row r="164" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A164" t="s">
+        <v>484</v>
+      </c>
       <c r="B164" t="s">
         <v>177</v>
       </c>
@@ -8961,10 +9472,10 @@
         <v>479</v>
       </c>
       <c r="G164">
-        <v>-0.0066</v>
+        <v>-6.6E-3</v>
       </c>
       <c r="H164">
-        <v>0.0189</v>
+        <v>1.89E-2</v>
       </c>
       <c r="I164">
         <v>0.01</v>
@@ -8973,22 +9484,25 @@
         <v>481</v>
       </c>
       <c r="K164">
-        <v>0.2647</v>
+        <v>0.26469999999999999</v>
       </c>
       <c r="L164" t="s">
         <v>482</v>
       </c>
       <c r="M164">
-        <v>0.032</v>
+        <v>3.2000000000000001E-2</v>
       </c>
       <c r="N164">
-        <v>-0.1803</v>
+        <v>-0.18029999999999999</v>
       </c>
       <c r="O164">
-        <v>0.0036</v>
-      </c>
-    </row>
-    <row r="165" spans="2:15">
+        <v>3.5999999999999999E-3</v>
+      </c>
+    </row>
+    <row r="165" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A165" t="s">
+        <v>485</v>
+      </c>
       <c r="B165" t="s">
         <v>178</v>
       </c>
@@ -9005,10 +9519,10 @@
         <v>479</v>
       </c>
       <c r="G165">
-        <v>0.0028</v>
+        <v>2.8E-3</v>
       </c>
       <c r="H165">
-        <v>0.0193</v>
+        <v>1.9300000000000001E-2</v>
       </c>
       <c r="I165">
         <v>0</v>
@@ -9017,22 +9531,25 @@
         <v>481</v>
       </c>
       <c r="K165">
-        <v>0.037</v>
+        <v>3.6999999999999998E-2</v>
       </c>
       <c r="L165" t="s">
         <v>483</v>
       </c>
       <c r="M165">
-        <v>0.07530000000000001</v>
+        <v>7.5300000000000006E-2</v>
       </c>
       <c r="N165">
-        <v>-0.2706</v>
+        <v>-0.27060000000000001</v>
       </c>
       <c r="O165">
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="2:15">
+    <row r="166" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A166" t="s">
+        <v>484</v>
+      </c>
       <c r="B166" t="s">
         <v>179</v>
       </c>
@@ -9049,25 +9566,25 @@
         <v>479</v>
       </c>
       <c r="G166">
-        <v>0.0111</v>
+        <v>1.11E-2</v>
       </c>
       <c r="H166">
-        <v>0.0301</v>
+        <v>3.0099999999999998E-2</v>
       </c>
       <c r="I166">
-        <v>0.003</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="J166" t="s">
         <v>481</v>
       </c>
       <c r="K166">
-        <v>0.0267</v>
+        <v>2.6700000000000002E-2</v>
       </c>
       <c r="L166" t="s">
         <v>483</v>
       </c>
       <c r="M166">
-        <v>0.2396</v>
+        <v>0.23960000000000001</v>
       </c>
       <c r="N166">
         <v>-0.3085</v>
@@ -9076,7 +9593,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="2:15">
+    <row r="167" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A167" t="s">
+        <v>485</v>
+      </c>
       <c r="B167" t="s">
         <v>180</v>
       </c>
@@ -9090,34 +9610,37 @@
         <v>479</v>
       </c>
       <c r="G167">
-        <v>0.0094</v>
+        <v>9.4000000000000004E-3</v>
       </c>
       <c r="H167">
-        <v>0.0167</v>
+        <v>1.67E-2</v>
       </c>
       <c r="I167">
-        <v>0.031</v>
+        <v>3.1E-2</v>
       </c>
       <c r="J167" t="s">
         <v>481</v>
       </c>
       <c r="K167">
-        <v>0.1223</v>
+        <v>0.12230000000000001</v>
       </c>
       <c r="L167" t="s">
         <v>483</v>
       </c>
       <c r="M167">
-        <v>0.2037</v>
+        <v>0.20369999999999999</v>
       </c>
       <c r="N167">
-        <v>0.5135</v>
+        <v>0.51349999999999996</v>
       </c>
       <c r="O167">
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="2:15">
+    <row r="168" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A168" t="s">
+        <v>484</v>
+      </c>
       <c r="B168" t="s">
         <v>181</v>
       </c>
@@ -9131,10 +9654,10 @@
         <v>479</v>
       </c>
       <c r="G168">
-        <v>0.0215</v>
+        <v>2.1499999999999998E-2</v>
       </c>
       <c r="H168">
-        <v>0.0073</v>
+        <v>7.3000000000000001E-3</v>
       </c>
       <c r="I168">
         <v>0.253</v>
@@ -9143,22 +9666,25 @@
         <v>480</v>
       </c>
       <c r="K168">
-        <v>0.0242</v>
+        <v>2.4199999999999999E-2</v>
       </c>
       <c r="L168" t="s">
         <v>483</v>
       </c>
       <c r="M168">
-        <v>0.0356</v>
+        <v>3.56E-2</v>
       </c>
       <c r="N168">
-        <v>-0.4882</v>
+        <v>-0.48820000000000002</v>
       </c>
       <c r="O168">
-        <v>0.0022</v>
-      </c>
-    </row>
-    <row r="169" spans="2:15">
+        <v>2.2000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="169" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A169" t="s">
+        <v>485</v>
+      </c>
       <c r="B169" t="s">
         <v>182</v>
       </c>
@@ -9172,34 +9698,37 @@
         <v>479</v>
       </c>
       <c r="G169">
-        <v>0.0166</v>
+        <v>1.66E-2</v>
       </c>
       <c r="H169">
-        <v>0.008800000000000001</v>
+        <v>8.8000000000000005E-3</v>
       </c>
       <c r="I169">
-        <v>0.208</v>
+        <v>0.20799999999999999</v>
       </c>
       <c r="J169" t="s">
         <v>480</v>
       </c>
       <c r="K169">
-        <v>0.1912</v>
+        <v>0.19120000000000001</v>
       </c>
       <c r="L169" t="s">
         <v>482</v>
       </c>
       <c r="M169">
-        <v>0.041</v>
+        <v>4.1000000000000002E-2</v>
       </c>
       <c r="N169">
-        <v>0.4369</v>
+        <v>0.43690000000000001</v>
       </c>
       <c r="O169">
-        <v>0.001</v>
-      </c>
-    </row>
-    <row r="170" spans="2:15">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="170" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A170" t="s">
+        <v>484</v>
+      </c>
       <c r="B170" t="s">
         <v>183</v>
       </c>
@@ -9213,10 +9742,10 @@
         <v>479</v>
       </c>
       <c r="G170">
-        <v>0.0128</v>
+        <v>1.2800000000000001E-2</v>
       </c>
       <c r="H170">
-        <v>0.0077</v>
+        <v>7.7000000000000002E-3</v>
       </c>
       <c r="I170">
         <v>0.221</v>
@@ -9225,22 +9754,25 @@
         <v>480</v>
       </c>
       <c r="K170">
-        <v>0.2388</v>
+        <v>0.23880000000000001</v>
       </c>
       <c r="L170" t="s">
         <v>482</v>
       </c>
       <c r="M170">
-        <v>0.0027</v>
+        <v>2.7000000000000001E-3</v>
       </c>
       <c r="N170">
-        <v>0.1289</v>
+        <v>0.12889999999999999</v>
       </c>
       <c r="O170">
-        <v>0.3984</v>
-      </c>
-    </row>
-    <row r="171" spans="2:15">
+        <v>0.39839999999999998</v>
+      </c>
+    </row>
+    <row r="171" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A171" t="s">
+        <v>485</v>
+      </c>
       <c r="B171" t="s">
         <v>184</v>
       </c>
@@ -9254,10 +9786,10 @@
         <v>479</v>
       </c>
       <c r="G171">
-        <v>0.0205</v>
+        <v>2.0500000000000001E-2</v>
       </c>
       <c r="H171">
-        <v>0.0141</v>
+        <v>1.41E-2</v>
       </c>
       <c r="I171">
         <v>0.374</v>
@@ -9266,22 +9798,25 @@
         <v>480</v>
       </c>
       <c r="K171">
-        <v>0.0215</v>
+        <v>2.1499999999999998E-2</v>
       </c>
       <c r="L171" t="s">
         <v>483</v>
       </c>
       <c r="M171">
-        <v>0.0102</v>
+        <v>1.0200000000000001E-2</v>
       </c>
       <c r="N171">
-        <v>0.1362</v>
+        <v>0.13619999999999999</v>
       </c>
       <c r="O171">
         <v>0.1022</v>
       </c>
     </row>
-    <row r="172" spans="2:15">
+    <row r="172" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A172" t="s">
+        <v>484</v>
+      </c>
       <c r="B172" t="s">
         <v>185</v>
       </c>
@@ -9298,34 +9833,37 @@
         <v>479</v>
       </c>
       <c r="G172">
-        <v>0.026</v>
+        <v>2.5999999999999999E-2</v>
       </c>
       <c r="H172">
-        <v>0.0041</v>
+        <v>4.1000000000000003E-3</v>
       </c>
       <c r="I172">
-        <v>0.713</v>
+        <v>0.71299999999999997</v>
       </c>
       <c r="J172" t="s">
         <v>480</v>
       </c>
       <c r="K172">
-        <v>0.0076</v>
+        <v>7.6E-3</v>
       </c>
       <c r="L172" t="s">
         <v>483</v>
       </c>
       <c r="M172">
-        <v>0.0014</v>
+        <v>1.4E-3</v>
       </c>
       <c r="N172">
-        <v>0.1725</v>
+        <v>0.17249999999999999</v>
       </c>
       <c r="O172">
-        <v>0.5478</v>
-      </c>
-    </row>
-    <row r="173" spans="2:15">
+        <v>0.54779999999999995</v>
+      </c>
+    </row>
+    <row r="173" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A173" t="s">
+        <v>485</v>
+      </c>
       <c r="B173" t="s">
         <v>186</v>
       </c>
@@ -9342,10 +9880,10 @@
         <v>479</v>
       </c>
       <c r="G173">
-        <v>0.023</v>
+        <v>2.3E-2</v>
       </c>
       <c r="H173">
-        <v>0.0033</v>
+        <v>3.3E-3</v>
       </c>
       <c r="I173">
         <v>0.182</v>
@@ -9363,13 +9901,16 @@
         <v>0</v>
       </c>
       <c r="N173">
-        <v>0.0242</v>
+        <v>2.4199999999999999E-2</v>
       </c>
       <c r="O173">
-        <v>0.954</v>
-      </c>
-    </row>
-    <row r="174" spans="2:15">
+        <v>0.95399999999999996</v>
+      </c>
+    </row>
+    <row r="174" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A174" t="s">
+        <v>484</v>
+      </c>
       <c r="B174" t="s">
         <v>187</v>
       </c>
@@ -9386,13 +9927,13 @@
         <v>479</v>
       </c>
       <c r="G174">
-        <v>0.0234</v>
+        <v>2.3400000000000001E-2</v>
       </c>
       <c r="H174">
-        <v>0.0016</v>
+        <v>1.6000000000000001E-3</v>
       </c>
       <c r="I174">
-        <v>0.118</v>
+        <v>0.11799999999999999</v>
       </c>
       <c r="J174" t="s">
         <v>481</v>
@@ -9404,16 +9945,19 @@
         <v>482</v>
       </c>
       <c r="M174">
-        <v>0.0568</v>
+        <v>5.6800000000000003E-2</v>
       </c>
       <c r="N174">
-        <v>2.8258</v>
+        <v>2.8258000000000001</v>
       </c>
       <c r="O174">
-        <v>0.0001</v>
-      </c>
-    </row>
-    <row r="175" spans="2:15">
+        <v>1E-4</v>
+      </c>
+    </row>
+    <row r="175" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A175" t="s">
+        <v>485</v>
+      </c>
       <c r="B175" t="s">
         <v>188</v>
       </c>
@@ -9427,19 +9971,19 @@
         <v>479</v>
       </c>
       <c r="G175">
-        <v>0.0267</v>
+        <v>2.6700000000000002E-2</v>
       </c>
       <c r="H175">
-        <v>0.0077</v>
+        <v>7.7000000000000002E-3</v>
       </c>
       <c r="I175">
-        <v>0.004</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="J175" t="s">
         <v>481</v>
       </c>
       <c r="K175">
-        <v>0.0021</v>
+        <v>2.0999999999999999E-3</v>
       </c>
       <c r="L175" t="s">
         <v>483</v>
@@ -9448,13 +9992,16 @@
         <v>0.1613</v>
       </c>
       <c r="N175">
-        <v>-0.987</v>
+        <v>-0.98699999999999999</v>
       </c>
       <c r="O175">
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="2:15">
+    <row r="176" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A176" t="s">
+        <v>484</v>
+      </c>
       <c r="B176" t="s">
         <v>189</v>
       </c>
@@ -9471,34 +10018,37 @@
         <v>479</v>
       </c>
       <c r="G176">
-        <v>0.0072</v>
+        <v>7.1999999999999998E-3</v>
       </c>
       <c r="H176">
-        <v>0.0067</v>
+        <v>6.7000000000000002E-3</v>
       </c>
       <c r="I176">
-        <v>0.013</v>
+        <v>1.2999999999999999E-2</v>
       </c>
       <c r="J176" t="s">
         <v>481</v>
       </c>
       <c r="K176">
-        <v>0.238</v>
+        <v>0.23799999999999999</v>
       </c>
       <c r="L176" t="s">
         <v>482</v>
       </c>
       <c r="M176">
-        <v>0.0362</v>
+        <v>3.6200000000000003E-2</v>
       </c>
       <c r="N176">
-        <v>0.5545</v>
+        <v>0.55449999999999999</v>
       </c>
       <c r="O176">
-        <v>0.0031</v>
-      </c>
-    </row>
-    <row r="177" spans="2:15">
+        <v>3.0999999999999999E-3</v>
+      </c>
+    </row>
+    <row r="177" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A177" t="s">
+        <v>485</v>
+      </c>
       <c r="B177" t="s">
         <v>190</v>
       </c>
@@ -9515,13 +10065,13 @@
         <v>479</v>
       </c>
       <c r="G177">
-        <v>0.0166</v>
+        <v>1.66E-2</v>
       </c>
       <c r="H177">
-        <v>0.0068</v>
+        <v>6.7999999999999996E-3</v>
       </c>
       <c r="I177">
-        <v>0.005</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="J177" t="s">
         <v>481</v>
@@ -9533,16 +10083,19 @@
         <v>482</v>
       </c>
       <c r="M177">
-        <v>0.1063</v>
+        <v>0.10630000000000001</v>
       </c>
       <c r="N177">
-        <v>0.9091</v>
+        <v>0.90910000000000002</v>
       </c>
       <c r="O177">
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="2:15">
+    <row r="178" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A178" t="s">
+        <v>484</v>
+      </c>
       <c r="B178" t="s">
         <v>191</v>
       </c>
@@ -9559,25 +10112,25 @@
         <v>479</v>
       </c>
       <c r="G178">
-        <v>0.008399999999999999</v>
+        <v>8.3999999999999995E-3</v>
       </c>
       <c r="H178">
-        <v>0.0037</v>
+        <v>3.7000000000000002E-3</v>
       </c>
       <c r="I178">
-        <v>0.068</v>
+        <v>6.8000000000000005E-2</v>
       </c>
       <c r="J178" t="s">
         <v>481</v>
       </c>
       <c r="K178">
-        <v>0.0326</v>
+        <v>3.2599999999999997E-2</v>
       </c>
       <c r="L178" t="s">
         <v>483</v>
       </c>
       <c r="M178">
-        <v>0.0808</v>
+        <v>8.0799999999999997E-2</v>
       </c>
       <c r="N178">
         <v>1.4419</v>
@@ -9586,7 +10139,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="2:15">
+    <row r="179" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A179" t="s">
+        <v>485</v>
+      </c>
       <c r="B179" t="s">
         <v>192</v>
       </c>
@@ -9603,13 +10159,13 @@
         <v>479</v>
       </c>
       <c r="G179">
-        <v>0.0081</v>
+        <v>8.0999999999999996E-3</v>
       </c>
       <c r="H179">
-        <v>0.0048</v>
+        <v>4.7999999999999996E-3</v>
       </c>
       <c r="I179">
-        <v>0.032</v>
+        <v>3.2000000000000001E-2</v>
       </c>
       <c r="J179" t="s">
         <v>481</v>
@@ -9621,16 +10177,19 @@
         <v>482</v>
       </c>
       <c r="M179">
-        <v>0.0301</v>
+        <v>3.0099999999999998E-2</v>
       </c>
       <c r="N179">
-        <v>0.6922</v>
+        <v>0.69220000000000004</v>
       </c>
       <c r="O179">
-        <v>0.0049</v>
-      </c>
-    </row>
-    <row r="180" spans="2:15">
+        <v>4.8999999999999998E-3</v>
+      </c>
+    </row>
+    <row r="180" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A180" t="s">
+        <v>484</v>
+      </c>
       <c r="B180" t="s">
         <v>193</v>
       </c>
@@ -9647,13 +10206,13 @@
         <v>479</v>
       </c>
       <c r="G180">
-        <v>0.0286</v>
+        <v>2.86E-2</v>
       </c>
       <c r="H180">
-        <v>0.0115</v>
+        <v>1.15E-2</v>
       </c>
       <c r="I180">
-        <v>0.058</v>
+        <v>5.8000000000000003E-2</v>
       </c>
       <c r="J180" t="s">
         <v>481</v>
@@ -9668,13 +10227,16 @@
         <v>0.2898</v>
       </c>
       <c r="N180">
-        <v>0.8859</v>
+        <v>0.88590000000000002</v>
       </c>
       <c r="O180">
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="2:15">
+    <row r="181" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A181" t="s">
+        <v>485</v>
+      </c>
       <c r="B181" t="s">
         <v>194</v>
       </c>
@@ -9691,34 +10253,37 @@
         <v>479</v>
       </c>
       <c r="G181">
-        <v>0.0618</v>
+        <v>6.1800000000000001E-2</v>
       </c>
       <c r="H181">
-        <v>0.036</v>
+        <v>3.5999999999999997E-2</v>
       </c>
       <c r="I181">
-        <v>0.536</v>
+        <v>0.53600000000000003</v>
       </c>
       <c r="J181" t="s">
         <v>480</v>
       </c>
       <c r="K181">
-        <v>0.0803</v>
+        <v>8.0299999999999996E-2</v>
       </c>
       <c r="L181" t="s">
         <v>483</v>
       </c>
       <c r="M181">
-        <v>0.3325</v>
+        <v>0.33250000000000002</v>
       </c>
       <c r="N181">
-        <v>0.3041</v>
+        <v>0.30409999999999998</v>
       </c>
       <c r="O181">
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="2:15">
+    <row r="182" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A182" t="s">
+        <v>484</v>
+      </c>
       <c r="B182" t="s">
         <v>195</v>
       </c>
@@ -9735,10 +10300,10 @@
         <v>479</v>
       </c>
       <c r="G182">
-        <v>0.0049</v>
+        <v>4.8999999999999998E-3</v>
       </c>
       <c r="H182">
-        <v>0.0043</v>
+        <v>4.3E-3</v>
       </c>
       <c r="I182">
         <v>0.03</v>
@@ -9753,16 +10318,19 @@
         <v>482</v>
       </c>
       <c r="M182">
-        <v>0.0338</v>
+        <v>3.3799999999999997E-2</v>
       </c>
       <c r="N182">
         <v>0.8095</v>
       </c>
       <c r="O182">
-        <v>0.0028</v>
-      </c>
-    </row>
-    <row r="183" spans="2:15">
+        <v>2.8E-3</v>
+      </c>
+    </row>
+    <row r="183" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A183" t="s">
+        <v>485</v>
+      </c>
       <c r="B183" t="s">
         <v>196</v>
       </c>
@@ -9779,34 +10347,37 @@
         <v>479</v>
       </c>
       <c r="G183">
-        <v>0.0067</v>
+        <v>6.7000000000000002E-3</v>
       </c>
       <c r="H183">
-        <v>0.0021</v>
+        <v>2.0999999999999999E-3</v>
       </c>
       <c r="I183">
-        <v>0.262</v>
+        <v>0.26200000000000001</v>
       </c>
       <c r="J183" t="s">
         <v>480</v>
       </c>
       <c r="K183">
-        <v>0.0737</v>
+        <v>7.3700000000000002E-2</v>
       </c>
       <c r="L183" t="s">
         <v>483</v>
       </c>
       <c r="M183">
-        <v>0.2209</v>
+        <v>0.22090000000000001</v>
       </c>
       <c r="N183">
-        <v>4.3456</v>
+        <v>4.3456000000000001</v>
       </c>
       <c r="O183">
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="2:15">
+    <row r="184" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A184" t="s">
+        <v>484</v>
+      </c>
       <c r="B184" t="s">
         <v>197</v>
       </c>
@@ -9823,34 +10394,37 @@
         <v>479</v>
       </c>
       <c r="G184">
-        <v>0.0044</v>
+        <v>4.4000000000000003E-3</v>
       </c>
       <c r="H184">
-        <v>0.0014</v>
+        <v>1.4E-3</v>
       </c>
       <c r="I184">
-        <v>0.274</v>
+        <v>0.27400000000000002</v>
       </c>
       <c r="J184" t="s">
         <v>480</v>
       </c>
       <c r="K184">
-        <v>0.014</v>
+        <v>1.4E-2</v>
       </c>
       <c r="L184" t="s">
         <v>483</v>
       </c>
       <c r="M184">
-        <v>0.2899</v>
+        <v>0.28989999999999999</v>
       </c>
       <c r="N184">
-        <v>7.4515</v>
+        <v>7.4515000000000002</v>
       </c>
       <c r="O184">
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="2:15">
+    <row r="185" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A185" t="s">
+        <v>485</v>
+      </c>
       <c r="B185" t="s">
         <v>198</v>
       </c>
@@ -9867,10 +10441,10 @@
         <v>479</v>
       </c>
       <c r="G185">
-        <v>0.0167</v>
+        <v>1.67E-2</v>
       </c>
       <c r="H185">
-        <v>0.0054</v>
+        <v>5.4000000000000003E-3</v>
       </c>
       <c r="I185">
         <v>0.34</v>
@@ -9885,16 +10459,19 @@
         <v>482</v>
       </c>
       <c r="M185">
-        <v>0.0044</v>
+        <v>4.4000000000000003E-3</v>
       </c>
       <c r="N185">
         <v>0.2311</v>
       </c>
       <c r="O185">
-        <v>0.2855</v>
-      </c>
-    </row>
-    <row r="186" spans="2:15">
+        <v>0.28549999999999998</v>
+      </c>
+    </row>
+    <row r="186" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A186" t="s">
+        <v>484</v>
+      </c>
       <c r="B186" t="s">
         <v>199</v>
       </c>
@@ -9911,10 +10488,10 @@
         <v>479</v>
       </c>
       <c r="G186">
-        <v>0.0172</v>
+        <v>1.72E-2</v>
       </c>
       <c r="H186">
-        <v>0.0021</v>
+        <v>2.0999999999999999E-3</v>
       </c>
       <c r="I186">
         <v>0.441</v>
@@ -9929,16 +10506,19 @@
         <v>482</v>
       </c>
       <c r="M186">
-        <v>0.036</v>
+        <v>3.5999999999999997E-2</v>
       </c>
       <c r="N186">
-        <v>1.7531</v>
+        <v>1.7531000000000001</v>
       </c>
       <c r="O186">
-        <v>0.0021</v>
-      </c>
-    </row>
-    <row r="187" spans="2:15">
+        <v>2.0999999999999999E-3</v>
+      </c>
+    </row>
+    <row r="187" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A187" t="s">
+        <v>485</v>
+      </c>
       <c r="B187" t="s">
         <v>200</v>
       </c>
@@ -9955,19 +10535,19 @@
         <v>479</v>
       </c>
       <c r="G187">
-        <v>0.0148</v>
+        <v>1.4800000000000001E-2</v>
       </c>
       <c r="H187">
-        <v>0.0169</v>
+        <v>1.6899999999999998E-2</v>
       </c>
       <c r="I187">
-        <v>0.013</v>
+        <v>1.2999999999999999E-2</v>
       </c>
       <c r="J187" t="s">
         <v>481</v>
       </c>
       <c r="K187">
-        <v>0.1577</v>
+        <v>0.15770000000000001</v>
       </c>
       <c r="L187" t="s">
         <v>482</v>
@@ -9976,13 +10556,16 @@
         <v>0.1991</v>
       </c>
       <c r="N187">
-        <v>-0.5024</v>
+        <v>-0.50239999999999996</v>
       </c>
       <c r="O187">
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="2:15">
+    <row r="188" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A188" t="s">
+        <v>484</v>
+      </c>
       <c r="B188" t="s">
         <v>201</v>
       </c>
@@ -9999,34 +10582,37 @@
         <v>479</v>
       </c>
       <c r="G188">
-        <v>0.018</v>
+        <v>1.7999999999999999E-2</v>
       </c>
       <c r="H188">
-        <v>0.0044</v>
+        <v>4.4000000000000003E-3</v>
       </c>
       <c r="I188">
-        <v>0.013</v>
+        <v>1.2999999999999999E-2</v>
       </c>
       <c r="J188" t="s">
         <v>481</v>
       </c>
       <c r="K188">
-        <v>0.0584</v>
+        <v>5.8400000000000001E-2</v>
       </c>
       <c r="L188" t="s">
         <v>483</v>
       </c>
       <c r="M188">
-        <v>0.1098</v>
+        <v>0.10979999999999999</v>
       </c>
       <c r="N188">
-        <v>-1.4226</v>
+        <v>-1.4226000000000001</v>
       </c>
       <c r="O188">
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="2:15">
+    <row r="189" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A189" t="s">
+        <v>485</v>
+      </c>
       <c r="B189" t="s">
         <v>202</v>
       </c>
@@ -10043,10 +10629,10 @@
         <v>479</v>
       </c>
       <c r="G189">
-        <v>0.0862</v>
+        <v>8.6199999999999999E-2</v>
       </c>
       <c r="H189">
-        <v>0.0142</v>
+        <v>1.4200000000000001E-2</v>
       </c>
       <c r="I189">
         <v>0.501</v>
@@ -10061,16 +10647,19 @@
         <v>482</v>
       </c>
       <c r="M189">
-        <v>0.007</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="N189">
         <v>0.1119</v>
       </c>
       <c r="O189">
-        <v>0.1765</v>
-      </c>
-    </row>
-    <row r="190" spans="2:15">
+        <v>0.17649999999999999</v>
+      </c>
+    </row>
+    <row r="190" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A190" t="s">
+        <v>484</v>
+      </c>
       <c r="B190" t="s">
         <v>203</v>
       </c>
@@ -10087,34 +10676,37 @@
         <v>479</v>
       </c>
       <c r="G190">
-        <v>0.08359999999999999</v>
+        <v>8.3599999999999994E-2</v>
       </c>
       <c r="H190">
-        <v>0.0135</v>
+        <v>1.35E-2</v>
       </c>
       <c r="I190">
-        <v>0.482</v>
+        <v>0.48199999999999998</v>
       </c>
       <c r="J190" t="s">
         <v>480</v>
       </c>
       <c r="K190">
-        <v>0.2453</v>
+        <v>0.24529999999999999</v>
       </c>
       <c r="L190" t="s">
         <v>482</v>
       </c>
       <c r="M190">
-        <v>0.0182</v>
+        <v>1.8200000000000001E-2</v>
       </c>
       <c r="N190">
         <v>0.1893</v>
       </c>
       <c r="O190">
-        <v>0.0291</v>
-      </c>
-    </row>
-    <row r="191" spans="2:15">
+        <v>2.9100000000000001E-2</v>
+      </c>
+    </row>
+    <row r="191" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A191" t="s">
+        <v>485</v>
+      </c>
       <c r="B191" t="s">
         <v>204</v>
       </c>
@@ -10131,34 +10723,37 @@
         <v>479</v>
       </c>
       <c r="G191">
-        <v>0.0038</v>
+        <v>3.8E-3</v>
       </c>
       <c r="H191">
-        <v>0.0024</v>
+        <v>2.3999999999999998E-3</v>
       </c>
       <c r="I191">
-        <v>0.018</v>
+        <v>1.7999999999999999E-2</v>
       </c>
       <c r="J191" t="s">
         <v>481</v>
       </c>
       <c r="K191">
-        <v>0.1848</v>
+        <v>0.18479999999999999</v>
       </c>
       <c r="L191" t="s">
         <v>482</v>
       </c>
       <c r="M191">
-        <v>0.0892</v>
+        <v>8.9200000000000002E-2</v>
       </c>
       <c r="N191">
-        <v>2.3595</v>
+        <v>2.3595000000000002</v>
       </c>
       <c r="O191">
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="2:15">
+    <row r="192" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A192" t="s">
+        <v>484</v>
+      </c>
       <c r="B192" t="s">
         <v>205</v>
       </c>
@@ -10175,34 +10770,37 @@
         <v>479</v>
       </c>
       <c r="G192">
-        <v>0.0031</v>
+        <v>3.0999999999999999E-3</v>
       </c>
       <c r="H192">
-        <v>0.0013</v>
+        <v>1.2999999999999999E-3</v>
       </c>
       <c r="I192">
-        <v>0.012</v>
+        <v>1.2E-2</v>
       </c>
       <c r="J192" t="s">
         <v>481</v>
       </c>
       <c r="K192">
-        <v>0.0106</v>
+        <v>1.06E-2</v>
       </c>
       <c r="L192" t="s">
         <v>483</v>
       </c>
       <c r="M192">
-        <v>0.0186</v>
+        <v>1.8599999999999998E-2</v>
       </c>
       <c r="N192">
-        <v>1.9348</v>
+        <v>1.9348000000000001</v>
       </c>
       <c r="O192">
-        <v>0.0272</v>
-      </c>
-    </row>
-    <row r="193" spans="2:15">
+        <v>2.7199999999999998E-2</v>
+      </c>
+    </row>
+    <row r="193" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A193" t="s">
+        <v>485</v>
+      </c>
       <c r="B193" t="s">
         <v>206</v>
       </c>
@@ -10219,34 +10817,37 @@
         <v>479</v>
       </c>
       <c r="G193">
-        <v>0.0053</v>
+        <v>5.3E-3</v>
       </c>
       <c r="H193">
-        <v>0.0051</v>
+        <v>5.1000000000000004E-3</v>
       </c>
       <c r="I193">
-        <v>0.008</v>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="J193" t="s">
         <v>481</v>
       </c>
       <c r="K193">
-        <v>0.0402</v>
+        <v>4.02E-2</v>
       </c>
       <c r="L193" t="s">
         <v>483</v>
       </c>
       <c r="M193">
-        <v>0.0439</v>
+        <v>4.3900000000000002E-2</v>
       </c>
       <c r="N193">
-        <v>0.7876</v>
+        <v>0.78759999999999997</v>
       </c>
       <c r="O193">
-        <v>0.0005999999999999999</v>
-      </c>
-    </row>
-    <row r="194" spans="2:15">
+        <v>5.9999999999999995E-4</v>
+      </c>
+    </row>
+    <row r="194" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A194" t="s">
+        <v>484</v>
+      </c>
       <c r="B194" t="s">
         <v>207</v>
       </c>
@@ -10263,10 +10864,10 @@
         <v>479</v>
       </c>
       <c r="G194">
-        <v>0.0043</v>
+        <v>4.3E-3</v>
       </c>
       <c r="H194">
-        <v>0.0026</v>
+        <v>2.5999999999999999E-3</v>
       </c>
       <c r="I194">
         <v>0.02</v>
@@ -10281,16 +10882,19 @@
         <v>482</v>
       </c>
       <c r="M194">
-        <v>0.0279</v>
+        <v>2.7900000000000001E-2</v>
       </c>
       <c r="N194">
-        <v>1.2353</v>
+        <v>1.2353000000000001</v>
       </c>
       <c r="O194">
-        <v>0.0068</v>
-      </c>
-    </row>
-    <row r="195" spans="2:15">
+        <v>6.7999999999999996E-3</v>
+      </c>
+    </row>
+    <row r="195" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A195" t="s">
+        <v>485</v>
+      </c>
       <c r="B195" t="s">
         <v>208</v>
       </c>
@@ -10307,34 +10911,37 @@
         <v>479</v>
       </c>
       <c r="G195">
-        <v>0.0036</v>
+        <v>3.5999999999999999E-3</v>
       </c>
       <c r="H195">
-        <v>0.0021</v>
+        <v>2.0999999999999999E-3</v>
       </c>
       <c r="I195">
-        <v>0.003</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="J195" t="s">
         <v>481</v>
       </c>
       <c r="K195">
-        <v>0.0993</v>
+        <v>9.9299999999999999E-2</v>
       </c>
       <c r="L195" t="s">
         <v>483</v>
       </c>
       <c r="M195">
-        <v>0.1312</v>
+        <v>0.13120000000000001</v>
       </c>
       <c r="N195">
-        <v>3.3215</v>
+        <v>3.3214999999999999</v>
       </c>
       <c r="O195">
         <v>0</v>
       </c>
     </row>
-    <row r="196" spans="2:15">
+    <row r="196" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A196" t="s">
+        <v>484</v>
+      </c>
       <c r="B196" t="s">
         <v>209</v>
       </c>
@@ -10351,34 +10958,37 @@
         <v>479</v>
       </c>
       <c r="G196">
-        <v>0.0049</v>
+        <v>4.8999999999999998E-3</v>
       </c>
       <c r="H196">
-        <v>0.0021</v>
+        <v>2.0999999999999999E-3</v>
       </c>
       <c r="I196">
-        <v>0.003</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="J196" t="s">
         <v>481</v>
       </c>
       <c r="K196">
-        <v>0.06710000000000001</v>
+        <v>6.7100000000000007E-2</v>
       </c>
       <c r="L196" t="s">
         <v>483</v>
       </c>
       <c r="M196">
-        <v>0.3015</v>
+        <v>0.30149999999999999</v>
       </c>
       <c r="N196">
-        <v>5.0078</v>
+        <v>5.0077999999999996</v>
       </c>
       <c r="O196">
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="2:15">
+    <row r="197" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A197" t="s">
+        <v>485</v>
+      </c>
       <c r="B197" t="s">
         <v>210</v>
       </c>
@@ -10395,34 +11005,37 @@
         <v>479</v>
       </c>
       <c r="G197">
-        <v>-0.0083</v>
+        <v>-8.3000000000000001E-3</v>
       </c>
       <c r="H197">
-        <v>0.0107</v>
+        <v>1.0699999999999999E-2</v>
       </c>
       <c r="I197">
-        <v>0.079</v>
+        <v>7.9000000000000001E-2</v>
       </c>
       <c r="J197" t="s">
         <v>481</v>
       </c>
       <c r="K197">
-        <v>0.0785</v>
+        <v>7.85E-2</v>
       </c>
       <c r="L197" t="s">
         <v>483</v>
       </c>
       <c r="M197">
-        <v>0.1438</v>
+        <v>0.14380000000000001</v>
       </c>
       <c r="N197">
-        <v>-0.6731</v>
+        <v>-0.67310000000000003</v>
       </c>
       <c r="O197">
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="2:15">
+    <row r="198" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A198" t="s">
+        <v>484</v>
+      </c>
       <c r="B198" t="s">
         <v>211</v>
       </c>
@@ -10439,10 +11052,10 @@
         <v>479</v>
       </c>
       <c r="G198">
-        <v>-0.0078</v>
+        <v>-7.7999999999999996E-3</v>
       </c>
       <c r="H198">
-        <v>0.0089</v>
+        <v>8.8999999999999999E-3</v>
       </c>
       <c r="I198">
         <v>0.109</v>
@@ -10451,22 +11064,25 @@
         <v>481</v>
       </c>
       <c r="K198">
-        <v>0.0247</v>
+        <v>2.47E-2</v>
       </c>
       <c r="L198" t="s">
         <v>483</v>
       </c>
       <c r="M198">
-        <v>0.0425</v>
+        <v>4.2500000000000003E-2</v>
       </c>
       <c r="N198">
-        <v>-0.4392</v>
+        <v>-0.43919999999999998</v>
       </c>
       <c r="O198">
-        <v>0.0008</v>
-      </c>
-    </row>
-    <row r="199" spans="2:15">
+        <v>8.0000000000000004E-4</v>
+      </c>
+    </row>
+    <row r="199" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A199" t="s">
+        <v>485</v>
+      </c>
       <c r="B199" t="s">
         <v>212</v>
       </c>
@@ -10483,34 +11099,37 @@
         <v>479</v>
       </c>
       <c r="G199">
-        <v>-0.0078</v>
+        <v>-7.7999999999999996E-3</v>
       </c>
       <c r="H199">
-        <v>0.0133</v>
+        <v>1.3299999999999999E-2</v>
       </c>
       <c r="I199">
-        <v>0.101</v>
+        <v>0.10100000000000001</v>
       </c>
       <c r="J199" t="s">
         <v>481</v>
       </c>
       <c r="K199">
-        <v>0.0371</v>
+        <v>3.7100000000000001E-2</v>
       </c>
       <c r="L199" t="s">
         <v>483</v>
       </c>
       <c r="M199">
-        <v>0.0948</v>
+        <v>9.4799999999999995E-2</v>
       </c>
       <c r="N199">
-        <v>-0.4403</v>
+        <v>-0.44030000000000002</v>
       </c>
       <c r="O199">
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="2:15">
+    <row r="200" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A200" t="s">
+        <v>484</v>
+      </c>
       <c r="B200" t="s">
         <v>213</v>
       </c>
@@ -10524,34 +11143,37 @@
         <v>479</v>
       </c>
       <c r="G200">
-        <v>-0.0074</v>
+        <v>-7.4000000000000003E-3</v>
       </c>
       <c r="H200">
-        <v>0.009599999999999999</v>
+        <v>9.5999999999999992E-3</v>
       </c>
       <c r="I200">
-        <v>0.165</v>
+        <v>0.16500000000000001</v>
       </c>
       <c r="J200" t="s">
         <v>480</v>
       </c>
       <c r="K200">
-        <v>0.0261</v>
+        <v>2.6100000000000002E-2</v>
       </c>
       <c r="L200" t="s">
         <v>483</v>
       </c>
       <c r="M200">
-        <v>0.0428</v>
+        <v>4.2799999999999998E-2</v>
       </c>
       <c r="N200">
-        <v>-0.4112</v>
+        <v>-0.41120000000000001</v>
       </c>
       <c r="O200">
-        <v>0.0008</v>
-      </c>
-    </row>
-    <row r="201" spans="2:15">
+        <v>8.0000000000000004E-4</v>
+      </c>
+    </row>
+    <row r="201" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A201" t="s">
+        <v>485</v>
+      </c>
       <c r="B201" t="s">
         <v>214</v>
       </c>
@@ -10568,34 +11190,37 @@
         <v>479</v>
       </c>
       <c r="G201">
-        <v>0.608</v>
+        <v>0.60799999999999998</v>
       </c>
       <c r="H201">
-        <v>0.0441</v>
+        <v>4.41E-2</v>
       </c>
       <c r="I201">
-        <v>0.598</v>
+        <v>0.59799999999999998</v>
       </c>
       <c r="J201" t="s">
         <v>480</v>
       </c>
       <c r="K201">
-        <v>0.1548</v>
+        <v>0.15479999999999999</v>
       </c>
       <c r="L201" t="s">
         <v>482</v>
       </c>
       <c r="M201">
-        <v>0.141</v>
+        <v>0.14099999999999999</v>
       </c>
       <c r="N201">
-        <v>0.1616</v>
+        <v>0.16159999999999999</v>
       </c>
       <c r="O201">
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="2:15">
+    <row r="202" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A202" t="s">
+        <v>484</v>
+      </c>
       <c r="B202" t="s">
         <v>215</v>
       </c>
@@ -10612,25 +11237,25 @@
         <v>479</v>
       </c>
       <c r="G202">
-        <v>0.7422</v>
+        <v>0.74219999999999997</v>
       </c>
       <c r="H202">
-        <v>0.0595</v>
+        <v>5.9499999999999997E-2</v>
       </c>
       <c r="I202">
-        <v>0.795</v>
+        <v>0.79500000000000004</v>
       </c>
       <c r="J202" t="s">
         <v>480</v>
       </c>
       <c r="K202">
-        <v>0.0216</v>
+        <v>2.1600000000000001E-2</v>
       </c>
       <c r="L202" t="s">
         <v>483</v>
       </c>
       <c r="M202">
-        <v>0.1334</v>
+        <v>0.13339999999999999</v>
       </c>
       <c r="N202">
         <v>0.1166</v>
@@ -10639,7 +11264,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="2:15">
+    <row r="203" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A203" t="s">
+        <v>485</v>
+      </c>
       <c r="B203" t="s">
         <v>216</v>
       </c>
@@ -10656,34 +11284,37 @@
         <v>479</v>
       </c>
       <c r="G203">
-        <v>0.836</v>
+        <v>0.83599999999999997</v>
       </c>
       <c r="H203">
-        <v>0.0274</v>
+        <v>2.7400000000000001E-2</v>
       </c>
       <c r="I203">
-        <v>0.384</v>
+        <v>0.38400000000000001</v>
       </c>
       <c r="J203" t="s">
         <v>480</v>
       </c>
       <c r="K203">
-        <v>0.1642</v>
+        <v>0.16420000000000001</v>
       </c>
       <c r="L203" t="s">
         <v>482</v>
       </c>
       <c r="M203">
-        <v>0.163</v>
+        <v>0.16300000000000001</v>
       </c>
       <c r="N203">
-        <v>0.2799</v>
+        <v>0.27989999999999998</v>
       </c>
       <c r="O203">
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="2:15">
+    <row r="204" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A204" t="s">
+        <v>484</v>
+      </c>
       <c r="B204" t="s">
         <v>217</v>
       </c>
@@ -10700,34 +11331,37 @@
         <v>479</v>
       </c>
       <c r="G204">
-        <v>0.3845</v>
+        <v>0.38450000000000001</v>
       </c>
       <c r="H204">
-        <v>0.0267</v>
+        <v>2.6700000000000002E-2</v>
       </c>
       <c r="I204">
-        <v>0.741</v>
+        <v>0.74099999999999999</v>
       </c>
       <c r="J204" t="s">
         <v>480</v>
       </c>
       <c r="K204">
-        <v>0.2524</v>
+        <v>0.25240000000000001</v>
       </c>
       <c r="L204" t="s">
         <v>482</v>
       </c>
       <c r="M204">
-        <v>0.0149</v>
+        <v>1.49E-2</v>
       </c>
       <c r="N204">
-        <v>-0.08690000000000001</v>
+        <v>-8.6900000000000005E-2</v>
       </c>
       <c r="O204">
-        <v>0.0484</v>
-      </c>
-    </row>
-    <row r="205" spans="2:15">
+        <v>4.8399999999999999E-2</v>
+      </c>
+    </row>
+    <row r="205" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A205" t="s">
+        <v>485</v>
+      </c>
       <c r="B205" t="s">
         <v>218</v>
       </c>
@@ -10744,34 +11378,37 @@
         <v>479</v>
       </c>
       <c r="G205">
-        <v>0.6261</v>
+        <v>0.62609999999999999</v>
       </c>
       <c r="H205">
         <v>0.1198</v>
       </c>
       <c r="I205">
-        <v>0.651</v>
+        <v>0.65100000000000002</v>
       </c>
       <c r="J205" t="s">
         <v>480</v>
       </c>
       <c r="K205">
-        <v>0.0334</v>
+        <v>3.3399999999999999E-2</v>
       </c>
       <c r="L205" t="s">
         <v>483</v>
       </c>
       <c r="M205">
-        <v>0.0309</v>
+        <v>3.09E-2</v>
       </c>
       <c r="N205">
-        <v>-0.0279</v>
+        <v>-2.7900000000000001E-2</v>
       </c>
       <c r="O205">
-        <v>0.0043</v>
-      </c>
-    </row>
-    <row r="206" spans="2:15">
+        <v>4.3E-3</v>
+      </c>
+    </row>
+    <row r="206" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A206" t="s">
+        <v>484</v>
+      </c>
       <c r="B206" t="s">
         <v>219</v>
       </c>
@@ -10788,10 +11425,10 @@
         <v>479</v>
       </c>
       <c r="G206">
-        <v>0.577</v>
+        <v>0.57699999999999996</v>
       </c>
       <c r="H206">
-        <v>0.09370000000000001</v>
+        <v>9.3700000000000006E-2</v>
       </c>
       <c r="I206">
         <v>0.46</v>
@@ -10800,22 +11437,25 @@
         <v>480</v>
       </c>
       <c r="K206">
-        <v>0.0455</v>
+        <v>4.5499999999999999E-2</v>
       </c>
       <c r="L206" t="s">
         <v>483</v>
       </c>
       <c r="M206">
-        <v>0.015</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="N206">
-        <v>-0.0252</v>
+        <v>-2.52E-2</v>
       </c>
       <c r="O206">
-        <v>0.0519</v>
-      </c>
-    </row>
-    <row r="207" spans="2:15">
+        <v>5.1900000000000002E-2</v>
+      </c>
+    </row>
+    <row r="207" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A207" t="s">
+        <v>485</v>
+      </c>
       <c r="B207" t="s">
         <v>220</v>
       </c>
@@ -10829,25 +11469,25 @@
         <v>479</v>
       </c>
       <c r="G207">
-        <v>0.0116</v>
+        <v>1.1599999999999999E-2</v>
       </c>
       <c r="H207">
-        <v>0.0065</v>
+        <v>6.4999999999999997E-3</v>
       </c>
       <c r="I207">
-        <v>0.324</v>
+        <v>0.32400000000000001</v>
       </c>
       <c r="J207" t="s">
         <v>480</v>
       </c>
       <c r="K207">
-        <v>0.1093</v>
+        <v>0.10929999999999999</v>
       </c>
       <c r="L207" t="s">
         <v>483</v>
       </c>
       <c r="M207">
-        <v>0.1533</v>
+        <v>0.15329999999999999</v>
       </c>
       <c r="N207">
         <v>1.1435</v>
@@ -10856,7 +11496,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="2:15">
+    <row r="208" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A208" t="s">
+        <v>484</v>
+      </c>
       <c r="B208" t="s">
         <v>221</v>
       </c>
@@ -10870,13 +11513,13 @@
         <v>479</v>
       </c>
       <c r="G208">
-        <v>0.019</v>
+        <v>1.9E-2</v>
       </c>
       <c r="H208">
-        <v>0.0106</v>
+        <v>1.06E-2</v>
       </c>
       <c r="I208">
-        <v>0.328</v>
+        <v>0.32800000000000001</v>
       </c>
       <c r="J208" t="s">
         <v>480</v>
@@ -10891,7 +11534,7 @@
         <v>0.108</v>
       </c>
       <c r="N208">
-        <v>0.5911</v>
+        <v>0.59109999999999996</v>
       </c>
       <c r="O208">
         <v>0</v>
